--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA584"/>
+  <dimension ref="A1:AA592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -63018,6 +63018,750 @@
         </is>
       </c>
     </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>9WINES &amp; COMPANY, S.A.</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr"/>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>168648</t>
+        </is>
+      </c>
+      <c r="D585" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E585" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F585" s="2" t="inlineStr"/>
+      <c r="G585" s="2" t="inlineStr">
+        <is>
+          <t>Rua Engenheiro Ferreira Dias, 924</t>
+        </is>
+      </c>
+      <c r="H585" s="2" t="inlineStr">
+        <is>
+          <t>4100-246</t>
+        </is>
+      </c>
+      <c r="I585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ninewines.pt</t>
+        </is>
+      </c>
+      <c r="J585" s="2" t="inlineStr"/>
+      <c r="K585" s="2" t="inlineStr"/>
+      <c r="L585" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M585" s="2" t="inlineStr">
+        <is>
+          <t>812050</t>
+        </is>
+      </c>
+      <c r="N585" s="2" t="inlineStr">
+        <is>
+          <t>geral@ninewines.pt</t>
+        </is>
+      </c>
+      <c r="O585" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 118 0765</t>
+        </is>
+      </c>
+      <c r="P585" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q585" s="2" t="inlineStr">
+        <is>
+          <t>513703721</t>
+        </is>
+      </c>
+      <c r="R585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nine-wines</t>
+        </is>
+      </c>
+      <c r="S585" s="2" t="inlineStr"/>
+      <c r="T585" s="2" t="inlineStr"/>
+      <c r="U585" s="2" t="inlineStr"/>
+      <c r="V585" s="2" t="inlineStr"/>
+      <c r="W585" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Serra</t>
+        </is>
+      </c>
+      <c r="X585" s="2" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="Y585" s="2" t="inlineStr"/>
+      <c r="Z585" s="2" t="inlineStr"/>
+      <c r="AA585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-serra-34499522/</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>9WINES &amp; COMPANY, S.A.</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr"/>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>168648</t>
+        </is>
+      </c>
+      <c r="D586" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E586" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F586" s="2" t="inlineStr"/>
+      <c r="G586" s="2" t="inlineStr">
+        <is>
+          <t>Rua Engenheiro Ferreira Dias, 924</t>
+        </is>
+      </c>
+      <c r="H586" s="2" t="inlineStr">
+        <is>
+          <t>4100-246</t>
+        </is>
+      </c>
+      <c r="I586" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ninewines.pt</t>
+        </is>
+      </c>
+      <c r="J586" s="2" t="inlineStr"/>
+      <c r="K586" s="2" t="inlineStr"/>
+      <c r="L586" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M586" s="2" t="inlineStr">
+        <is>
+          <t>812050</t>
+        </is>
+      </c>
+      <c r="N586" s="2" t="inlineStr">
+        <is>
+          <t>geral@ninewines.pt</t>
+        </is>
+      </c>
+      <c r="O586" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 118 0765</t>
+        </is>
+      </c>
+      <c r="P586" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q586" s="2" t="inlineStr">
+        <is>
+          <t>513703721</t>
+        </is>
+      </c>
+      <c r="R586" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nine-wines</t>
+        </is>
+      </c>
+      <c r="S586" s="2" t="inlineStr"/>
+      <c r="T586" s="2" t="inlineStr"/>
+      <c r="U586" s="2" t="inlineStr"/>
+      <c r="V586" s="2" t="inlineStr"/>
+      <c r="W586" s="2" t="inlineStr">
+        <is>
+          <t>Helder Cambey</t>
+        </is>
+      </c>
+      <c r="X586" s="2" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="Y586" s="2" t="inlineStr"/>
+      <c r="Z586" s="2" t="inlineStr"/>
+      <c r="AA586" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/helder-cambey-6648a047/</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>KILÓLITRO, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr"/>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>168647</t>
+        </is>
+      </c>
+      <c r="D587" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E587" s="2" t="inlineStr">
+        <is>
+          <t>Barreiro</t>
+        </is>
+      </c>
+      <c r="F587" s="2" t="inlineStr"/>
+      <c r="G587" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cidade Da Beira, 1 R/C C</t>
+        </is>
+      </c>
+      <c r="H587" s="2" t="inlineStr">
+        <is>
+          <t>2830-567</t>
+        </is>
+      </c>
+      <c r="I587" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kilolitro.pt</t>
+        </is>
+      </c>
+      <c r="J587" s="2" t="inlineStr"/>
+      <c r="K587" s="2" t="inlineStr"/>
+      <c r="L587" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M587" s="2" t="inlineStr">
+        <is>
+          <t>148271</t>
+        </is>
+      </c>
+      <c r="N587" s="2" t="inlineStr">
+        <is>
+          <t>geral@kilolitro.pt</t>
+        </is>
+      </c>
+      <c r="O587" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 207 1158</t>
+        </is>
+      </c>
+      <c r="P587" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q587" s="2" t="inlineStr">
+        <is>
+          <t>514784750</t>
+        </is>
+      </c>
+      <c r="R587" s="2" t="inlineStr"/>
+      <c r="S587" s="2" t="inlineStr"/>
+      <c r="T587" s="2" t="inlineStr"/>
+      <c r="U587" s="2" t="inlineStr"/>
+      <c r="V587" s="2" t="inlineStr"/>
+      <c r="W587" s="2" t="inlineStr">
+        <is>
+          <t>António Gomes</t>
+        </is>
+      </c>
+      <c r="X587" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y587" s="2" t="inlineStr"/>
+      <c r="Z587" s="2" t="inlineStr"/>
+      <c r="AA587" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ant%C3%B3nio-gomes-099b7a21/</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>SABORES &amp; REQUINTES, LDA</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr"/>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>168646</t>
+        </is>
+      </c>
+      <c r="D588" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E588" s="2" t="inlineStr">
+        <is>
+          <t>Póvoa De Varzim</t>
+        </is>
+      </c>
+      <c r="F588" s="2" t="inlineStr"/>
+      <c r="G588" s="2" t="inlineStr">
+        <is>
+          <t>Praça Marquês De Pombal, Loja 51</t>
+        </is>
+      </c>
+      <c r="H588" s="2" t="inlineStr">
+        <is>
+          <t>4490-442</t>
+        </is>
+      </c>
+      <c r="I588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.saboreserequintes.pt</t>
+        </is>
+      </c>
+      <c r="J588" s="2" t="inlineStr"/>
+      <c r="K588" s="2" t="inlineStr"/>
+      <c r="L588" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M588" s="2" t="inlineStr">
+        <is>
+          <t>72236</t>
+        </is>
+      </c>
+      <c r="N588" s="2" t="inlineStr">
+        <is>
+          <t>sabores.requintes@hotmail.com</t>
+        </is>
+      </c>
+      <c r="O588" s="2" t="inlineStr">
+        <is>
+          <t>+351 252 627 260</t>
+        </is>
+      </c>
+      <c r="P588" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="Q588" s="2" t="inlineStr">
+        <is>
+          <t>501525866</t>
+        </is>
+      </c>
+      <c r="R588" s="2" t="inlineStr"/>
+      <c r="S588" s="2" t="inlineStr"/>
+      <c r="T588" s="2" t="inlineStr"/>
+      <c r="U588" s="2" t="inlineStr"/>
+      <c r="V588" s="2" t="inlineStr"/>
+      <c r="W588" s="2" t="inlineStr"/>
+      <c r="X588" s="2" t="inlineStr"/>
+      <c r="Y588" s="2" t="inlineStr"/>
+      <c r="Z588" s="2" t="inlineStr"/>
+      <c r="AA588" s="2" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>POR SABORES, LDA</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr"/>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>168645</t>
+        </is>
+      </c>
+      <c r="D589" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E589" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F589" s="2" t="inlineStr"/>
+      <c r="G589" s="2" t="inlineStr">
+        <is>
+          <t>Rua João De Freitas Branco, 34</t>
+        </is>
+      </c>
+      <c r="H589" s="2" t="inlineStr">
+        <is>
+          <t>1500-359</t>
+        </is>
+      </c>
+      <c r="I589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.porsabores.com</t>
+        </is>
+      </c>
+      <c r="J589" s="2" t="inlineStr"/>
+      <c r="K589" s="2" t="inlineStr"/>
+      <c r="L589" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M589" s="2" t="inlineStr">
+        <is>
+          <t>74997</t>
+        </is>
+      </c>
+      <c r="N589" s="2" t="inlineStr">
+        <is>
+          <t>porsaboresonline@gmail.com</t>
+        </is>
+      </c>
+      <c r="O589" s="2" t="inlineStr"/>
+      <c r="P589" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q589" s="2" t="inlineStr">
+        <is>
+          <t>513706950</t>
+        </is>
+      </c>
+      <c r="R589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/porsabores</t>
+        </is>
+      </c>
+      <c r="S589" s="2" t="inlineStr"/>
+      <c r="T589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/porsabores/</t>
+        </is>
+      </c>
+      <c r="U589" s="2" t="inlineStr"/>
+      <c r="V589" s="2" t="inlineStr"/>
+      <c r="W589" s="2" t="inlineStr">
+        <is>
+          <t>Diogo Alves</t>
+        </is>
+      </c>
+      <c r="X589" s="2" t="inlineStr">
+        <is>
+          <t>Operations and Logistics</t>
+        </is>
+      </c>
+      <c r="Y589" s="2" t="inlineStr"/>
+      <c r="Z589" s="2" t="inlineStr"/>
+      <c r="AA589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-alves-3b31051a7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>AJO FLAVOURS, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr"/>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>168644</t>
+        </is>
+      </c>
+      <c r="D590" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E590" s="2" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F590" s="2" t="inlineStr"/>
+      <c r="G590" s="2" t="inlineStr">
+        <is>
+          <t>Rua Doutor José Azevedo Ferreira, 38</t>
+        </is>
+      </c>
+      <c r="H590" s="2" t="inlineStr">
+        <is>
+          <t>4705-253</t>
+        </is>
+      </c>
+      <c r="I590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ajoflavours.com</t>
+        </is>
+      </c>
+      <c r="J590" s="2" t="inlineStr"/>
+      <c r="K590" s="2" t="inlineStr"/>
+      <c r="L590" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M590" s="2" t="inlineStr">
+        <is>
+          <t>159106</t>
+        </is>
+      </c>
+      <c r="N590" s="2" t="inlineStr">
+        <is>
+          <t>info@ajoflavours.com</t>
+        </is>
+      </c>
+      <c r="O590" s="2" t="inlineStr"/>
+      <c r="P590" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q590" s="2" t="inlineStr">
+        <is>
+          <t>517092620</t>
+        </is>
+      </c>
+      <c r="R590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ajo-flavours</t>
+        </is>
+      </c>
+      <c r="S590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ajoflavours</t>
+        </is>
+      </c>
+      <c r="T590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ajoflavours/</t>
+        </is>
+      </c>
+      <c r="U590" s="2" t="inlineStr"/>
+      <c r="V590" s="2" t="inlineStr"/>
+      <c r="W590" s="2" t="inlineStr"/>
+      <c r="X590" s="2" t="inlineStr"/>
+      <c r="Y590" s="2" t="inlineStr"/>
+      <c r="Z590" s="2" t="inlineStr"/>
+      <c r="AA590" s="2" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>SAVORIUM, LDA</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>Monte Da Torrinha</t>
+        </is>
+      </c>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>168643</t>
+        </is>
+      </c>
+      <c r="D591" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E591" s="2" t="inlineStr">
+        <is>
+          <t>Ovar</t>
+        </is>
+      </c>
+      <c r="F591" s="2" t="inlineStr"/>
+      <c r="G591" s="2" t="inlineStr">
+        <is>
+          <t>Rua Manuel Mendes Tarrafa, 101</t>
+        </is>
+      </c>
+      <c r="H591" s="2" t="inlineStr">
+        <is>
+          <t>3880-094</t>
+        </is>
+      </c>
+      <c r="I591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.montedatorrinha.pt</t>
+        </is>
+      </c>
+      <c r="J591" s="2" t="inlineStr"/>
+      <c r="K591" s="2" t="inlineStr"/>
+      <c r="L591" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M591" s="2" t="inlineStr">
+        <is>
+          <t>490132</t>
+        </is>
+      </c>
+      <c r="N591" s="2" t="inlineStr">
+        <is>
+          <t>info@montedatorrinha.pt</t>
+        </is>
+      </c>
+      <c r="O591" s="2" t="inlineStr"/>
+      <c r="P591" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q591" s="2" t="inlineStr">
+        <is>
+          <t>517786796</t>
+        </is>
+      </c>
+      <c r="R591" s="2" t="inlineStr"/>
+      <c r="S591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Monte-da-Torrinha-61555455593772/</t>
+        </is>
+      </c>
+      <c r="T591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/montedatorrinha/</t>
+        </is>
+      </c>
+      <c r="U591" s="2" t="inlineStr"/>
+      <c r="V591" s="2" t="inlineStr"/>
+      <c r="W591" s="2" t="inlineStr"/>
+      <c r="X591" s="2" t="inlineStr"/>
+      <c r="Y591" s="2" t="inlineStr"/>
+      <c r="Z591" s="2" t="inlineStr"/>
+      <c r="AA591" s="2" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>Roteiro de Sabores, Lda.</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr"/>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>168642</t>
+        </is>
+      </c>
+      <c r="D592" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E592" s="2" t="inlineStr">
+        <is>
+          <t>Pontinha</t>
+        </is>
+      </c>
+      <c r="F592" s="2" t="inlineStr"/>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>Avenida De São Sebastião, 39A</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="inlineStr">
+        <is>
+          <t>1675-052</t>
+        </is>
+      </c>
+      <c r="I592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.roteirodesabores.pt</t>
+        </is>
+      </c>
+      <c r="J592" s="2" t="inlineStr"/>
+      <c r="K592" s="2" t="inlineStr"/>
+      <c r="L592" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M592" s="2" t="inlineStr">
+        <is>
+          <t>947208</t>
+        </is>
+      </c>
+      <c r="N592" s="2" t="inlineStr">
+        <is>
+          <t>cabazes@roteirodesabores.pt</t>
+        </is>
+      </c>
+      <c r="O592" s="2" t="inlineStr"/>
+      <c r="P592" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q592" s="2" t="inlineStr">
+        <is>
+          <t>505261529</t>
+        </is>
+      </c>
+      <c r="R592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/roteiro-de-sabores</t>
+        </is>
+      </c>
+      <c r="S592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/roteirodesabores</t>
+        </is>
+      </c>
+      <c r="T592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/roteiro.de.sabores/</t>
+        </is>
+      </c>
+      <c r="U592" s="2" t="inlineStr"/>
+      <c r="V592" s="2" t="inlineStr"/>
+      <c r="W592" s="2" t="inlineStr">
+        <is>
+          <t>Vitor Cruz</t>
+        </is>
+      </c>
+      <c r="X592" s="2" t="inlineStr">
+        <is>
+          <t>Director General</t>
+        </is>
+      </c>
+      <c r="Y592" s="2" t="inlineStr"/>
+      <c r="Z592" s="2" t="inlineStr"/>
+      <c r="AA592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vitor-cruz-roteirodesabores/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA592"/>
+  <dimension ref="A1:AA673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -63762,6 +63762,7507 @@
         </is>
       </c>
     </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>Pecados do Alentejo</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr"/>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>168727</t>
+        </is>
+      </c>
+      <c r="D593" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E593" s="2" t="inlineStr">
+        <is>
+          <t>São Domingos</t>
+        </is>
+      </c>
+      <c r="F593" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G593" s="2" t="inlineStr">
+        <is>
+          <t>Rua da Liberdade, 54</t>
+        </is>
+      </c>
+      <c r="H593" s="2" t="inlineStr">
+        <is>
+          <t>7540-415</t>
+        </is>
+      </c>
+      <c r="I593" s="2" t="inlineStr">
+        <is>
+          <t>https://pecadosdoalentejo.pt</t>
+        </is>
+      </c>
+      <c r="J593" s="2" t="inlineStr"/>
+      <c r="K593" s="2" t="inlineStr"/>
+      <c r="L593" s="2" t="inlineStr"/>
+      <c r="M593" s="2" t="inlineStr"/>
+      <c r="N593" s="2" t="inlineStr">
+        <is>
+          <t>info@pecadosdoalentejo.pt</t>
+        </is>
+      </c>
+      <c r="O593" s="2" t="inlineStr"/>
+      <c r="P593" s="2" t="inlineStr"/>
+      <c r="Q593" s="2" t="inlineStr"/>
+      <c r="R593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pecados-do-alentejo/</t>
+        </is>
+      </c>
+      <c r="S593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pecadosalentejo</t>
+        </is>
+      </c>
+      <c r="T593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pecadosdoalentejo/</t>
+        </is>
+      </c>
+      <c r="U593" s="2" t="inlineStr"/>
+      <c r="V593" s="2" t="inlineStr"/>
+      <c r="W593" s="2" t="inlineStr"/>
+      <c r="X593" s="2" t="inlineStr"/>
+      <c r="Y593" s="2" t="inlineStr"/>
+      <c r="Z593" s="2" t="inlineStr"/>
+      <c r="AA593" s="2" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Pepe</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr"/>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>168726</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F594" s="2" t="inlineStr"/>
+      <c r="G594" s="2" t="inlineStr">
+        <is>
+          <t>R. Eng. Ferreira Dias 51</t>
+        </is>
+      </c>
+      <c r="H594" s="2" t="inlineStr">
+        <is>
+          <t>4100-247</t>
+        </is>
+      </c>
+      <c r="I594" s="2" t="inlineStr">
+        <is>
+          <t>https://garrafeirapepe.pt</t>
+        </is>
+      </c>
+      <c r="J594" s="2" t="inlineStr"/>
+      <c r="K594" s="2" t="inlineStr"/>
+      <c r="L594" s="2" t="inlineStr"/>
+      <c r="M594" s="2" t="inlineStr"/>
+      <c r="N594" s="2" t="inlineStr">
+        <is>
+          <t>clientes@garrafeirapepe.pt</t>
+        </is>
+      </c>
+      <c r="O594" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 618 4656</t>
+        </is>
+      </c>
+      <c r="P594" s="2" t="inlineStr"/>
+      <c r="Q594" s="2" t="inlineStr"/>
+      <c r="R594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/garrafeira-tio-pepe/</t>
+        </is>
+      </c>
+      <c r="S594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GarrafeiraPepe</t>
+        </is>
+      </c>
+      <c r="T594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeirapepe/</t>
+        </is>
+      </c>
+      <c r="U594" s="2" t="inlineStr"/>
+      <c r="V594" s="2" t="inlineStr"/>
+      <c r="W594" s="2" t="inlineStr">
+        <is>
+          <t>João Cândido Da Silva</t>
+        </is>
+      </c>
+      <c r="X594" s="2" t="inlineStr">
+        <is>
+          <t>Director of Services</t>
+        </is>
+      </c>
+      <c r="Y594" s="2" t="inlineStr"/>
+      <c r="Z594" s="2" t="inlineStr"/>
+      <c r="AA594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jo%C3%A3o-c%C3%A2ndido-da-silva-621702b8/</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Pepe</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr"/>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>168726</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F595" s="2" t="inlineStr"/>
+      <c r="G595" s="2" t="inlineStr">
+        <is>
+          <t>R. Eng. Ferreira Dias 51</t>
+        </is>
+      </c>
+      <c r="H595" s="2" t="inlineStr">
+        <is>
+          <t>4100-247</t>
+        </is>
+      </c>
+      <c r="I595" s="2" t="inlineStr">
+        <is>
+          <t>https://garrafeirapepe.pt</t>
+        </is>
+      </c>
+      <c r="J595" s="2" t="inlineStr"/>
+      <c r="K595" s="2" t="inlineStr"/>
+      <c r="L595" s="2" t="inlineStr"/>
+      <c r="M595" s="2" t="inlineStr"/>
+      <c r="N595" s="2" t="inlineStr">
+        <is>
+          <t>clientes@garrafeirapepe.pt</t>
+        </is>
+      </c>
+      <c r="O595" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 618 4656</t>
+        </is>
+      </c>
+      <c r="P595" s="2" t="inlineStr"/>
+      <c r="Q595" s="2" t="inlineStr"/>
+      <c r="R595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/garrafeira-tio-pepe/</t>
+        </is>
+      </c>
+      <c r="S595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GarrafeiraPepe</t>
+        </is>
+      </c>
+      <c r="T595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeirapepe/</t>
+        </is>
+      </c>
+      <c r="U595" s="2" t="inlineStr"/>
+      <c r="V595" s="2" t="inlineStr"/>
+      <c r="W595" s="2" t="inlineStr">
+        <is>
+          <t>Beatriz Ribeiro</t>
+        </is>
+      </c>
+      <c r="X595" s="2" t="inlineStr">
+        <is>
+          <t>Sales Assistant</t>
+        </is>
+      </c>
+      <c r="Y595" s="2" t="inlineStr"/>
+      <c r="Z595" s="2" t="inlineStr"/>
+      <c r="AA595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/beatriz-ribeiro-77a374300/</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira D'Alvalade</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr"/>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>168725</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F596" s="2" t="inlineStr"/>
+      <c r="G596" s="2" t="inlineStr">
+        <is>
+          <t>Avenida da Igreja, nr 3 C</t>
+        </is>
+      </c>
+      <c r="H596" s="2" t="inlineStr">
+        <is>
+          <t>1700-230</t>
+        </is>
+      </c>
+      <c r="I596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.garrafeiradalvalade.com</t>
+        </is>
+      </c>
+      <c r="J596" s="2" t="inlineStr"/>
+      <c r="K596" s="2" t="inlineStr"/>
+      <c r="L596" s="2" t="inlineStr"/>
+      <c r="M596" s="2" t="inlineStr"/>
+      <c r="N596" s="2" t="inlineStr">
+        <is>
+          <t>geral@garrafeiradalvalade.pt</t>
+        </is>
+      </c>
+      <c r="O596" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 157 6919</t>
+        </is>
+      </c>
+      <c r="P596" s="2" t="inlineStr"/>
+      <c r="Q596" s="2" t="inlineStr"/>
+      <c r="R596" s="2" t="inlineStr"/>
+      <c r="S596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/garrafeiradalvalade</t>
+        </is>
+      </c>
+      <c r="T596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeiradalvalade/</t>
+        </is>
+      </c>
+      <c r="U596" s="2" t="inlineStr"/>
+      <c r="V596" s="2" t="inlineStr"/>
+      <c r="W596" s="2" t="inlineStr"/>
+      <c r="X596" s="2" t="inlineStr"/>
+      <c r="Y596" s="2" t="inlineStr"/>
+      <c r="Z596" s="2" t="inlineStr"/>
+      <c r="AA596" s="2" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>BELITA SUPERMERCADOS, LDA</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr"/>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>168724</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="inlineStr">
+        <is>
+          <t>Delães</t>
+        </is>
+      </c>
+      <c r="F597" s="2" t="inlineStr"/>
+      <c r="G597" s="2" t="inlineStr">
+        <is>
+          <t>Rua Da Igreja</t>
+        </is>
+      </c>
+      <c r="H597" s="2" t="inlineStr">
+        <is>
+          <t>4765-623</t>
+        </is>
+      </c>
+      <c r="I597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.belita.pt</t>
+        </is>
+      </c>
+      <c r="J597" s="2" t="inlineStr"/>
+      <c r="K597" s="2" t="inlineStr"/>
+      <c r="L597" s="2" t="inlineStr"/>
+      <c r="M597" s="2" t="inlineStr">
+        <is>
+          <t>16042368</t>
+        </is>
+      </c>
+      <c r="N597" s="2" t="inlineStr">
+        <is>
+          <t>geral@belita.pt</t>
+        </is>
+      </c>
+      <c r="O597" s="2" t="inlineStr">
+        <is>
+          <t>+351 252 987 280</t>
+        </is>
+      </c>
+      <c r="P597" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q597" s="2" t="inlineStr">
+        <is>
+          <t>507937449</t>
+        </is>
+      </c>
+      <c r="R597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/belitasupermercados/</t>
+        </is>
+      </c>
+      <c r="S597" s="2" t="inlineStr"/>
+      <c r="T597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/belita_supermercados/</t>
+        </is>
+      </c>
+      <c r="U597" s="2" t="inlineStr"/>
+      <c r="V597" s="2" t="inlineStr"/>
+      <c r="W597" s="2" t="inlineStr">
+        <is>
+          <t>Luisa Abreu</t>
+        </is>
+      </c>
+      <c r="X597" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Assistant</t>
+        </is>
+      </c>
+      <c r="Y597" s="2" t="inlineStr"/>
+      <c r="Z597" s="2" t="inlineStr"/>
+      <c r="AA597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luisa-abreu-a9666232a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>LEITÕES DE NEGRAIS, LDA</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>AFONSO DOS LEITÕES</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>168720</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F598" s="2" t="inlineStr"/>
+      <c r="G598" s="2" t="inlineStr">
+        <is>
+          <t>Rua da Junqueira, 486</t>
+        </is>
+      </c>
+      <c r="H598" s="2" t="inlineStr">
+        <is>
+          <t>1300-598</t>
+        </is>
+      </c>
+      <c r="I598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.leitoesdenegrais.pt</t>
+        </is>
+      </c>
+      <c r="J598" s="2" t="inlineStr"/>
+      <c r="K598" s="2" t="inlineStr"/>
+      <c r="L598" s="2" t="inlineStr"/>
+      <c r="M598" s="2" t="inlineStr">
+        <is>
+          <t>12752373</t>
+        </is>
+      </c>
+      <c r="N598" s="2" t="inlineStr">
+        <is>
+          <t>geral@leitoesdenegrais.pt</t>
+        </is>
+      </c>
+      <c r="O598" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 362 0951</t>
+        </is>
+      </c>
+      <c r="P598" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q598" s="2" t="inlineStr">
+        <is>
+          <t>502824824</t>
+        </is>
+      </c>
+      <c r="R598" s="2" t="inlineStr"/>
+      <c r="S598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pages/Afonso-dos-Leit%C3%B5es/118731021547133</t>
+        </is>
+      </c>
+      <c r="T598" s="2" t="inlineStr"/>
+      <c r="U598" s="2" t="inlineStr"/>
+      <c r="V598" s="2" t="inlineStr"/>
+      <c r="W598" s="2" t="inlineStr"/>
+      <c r="X598" s="2" t="inlineStr"/>
+      <c r="Y598" s="2" t="inlineStr"/>
+      <c r="Z598" s="2" t="inlineStr"/>
+      <c r="AA598" s="2" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>BOLAMA SUPERMERCADOS, LDA</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr"/>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>168719</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="inlineStr">
+        <is>
+          <t>Guimarães</t>
+        </is>
+      </c>
+      <c r="F599" s="2" t="inlineStr"/>
+      <c r="G599" s="2" t="inlineStr">
+        <is>
+          <t>Rua Veiga De Fora</t>
+        </is>
+      </c>
+      <c r="H599" s="2" t="inlineStr">
+        <is>
+          <t>4800-101</t>
+        </is>
+      </c>
+      <c r="I599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bolama.pt</t>
+        </is>
+      </c>
+      <c r="J599" s="2" t="inlineStr"/>
+      <c r="K599" s="2" t="inlineStr"/>
+      <c r="L599" s="2" t="inlineStr"/>
+      <c r="M599" s="2" t="inlineStr">
+        <is>
+          <t>72887787</t>
+        </is>
+      </c>
+      <c r="N599" s="2" t="inlineStr">
+        <is>
+          <t>geral@bolama.pt</t>
+        </is>
+      </c>
+      <c r="O599" s="2" t="inlineStr">
+        <is>
+          <t>+351 253 093 100</t>
+        </is>
+      </c>
+      <c r="P599" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q599" s="2" t="inlineStr">
+        <is>
+          <t>503274496</t>
+        </is>
+      </c>
+      <c r="R599" s="2" t="inlineStr"/>
+      <c r="S599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bolamasupermercados/</t>
+        </is>
+      </c>
+      <c r="T599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bolama.supermercados/</t>
+        </is>
+      </c>
+      <c r="U599" s="2" t="inlineStr"/>
+      <c r="V599" s="2" t="inlineStr"/>
+      <c r="W599" s="2" t="inlineStr"/>
+      <c r="X599" s="2" t="inlineStr"/>
+      <c r="Y599" s="2" t="inlineStr"/>
+      <c r="Z599" s="2" t="inlineStr"/>
+      <c r="AA599" s="2" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>ARMAZÉNS DE MERCEARIA E AVÍCOLA MARVANEJO, LDA</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>ARMAZENS MARVANEJO</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>168718</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="inlineStr">
+        <is>
+          <t>Elvas</t>
+        </is>
+      </c>
+      <c r="F600" s="2" t="inlineStr"/>
+      <c r="G600" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Do Dia De Portugal - 10 De Junho De 2013, 63</t>
+        </is>
+      </c>
+      <c r="H600" s="2" t="inlineStr">
+        <is>
+          <t>7350-229</t>
+        </is>
+      </c>
+      <c r="I600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marvanejo.pt</t>
+        </is>
+      </c>
+      <c r="J600" s="2" t="inlineStr"/>
+      <c r="K600" s="2" t="inlineStr"/>
+      <c r="L600" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M600" s="2" t="inlineStr">
+        <is>
+          <t>23749802</t>
+        </is>
+      </c>
+      <c r="N600" s="2" t="inlineStr">
+        <is>
+          <t>geral@marvanejo.pt</t>
+        </is>
+      </c>
+      <c r="O600" s="2" t="inlineStr">
+        <is>
+          <t>+351 268 622 229</t>
+        </is>
+      </c>
+      <c r="P600" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="Q600" s="2" t="inlineStr">
+        <is>
+          <t>501265791</t>
+        </is>
+      </c>
+      <c r="R600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/armaz%C3%A9ns-marvanejo/</t>
+        </is>
+      </c>
+      <c r="S600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AMarvanejo</t>
+        </is>
+      </c>
+      <c r="T600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/marvanejo.armazens/</t>
+        </is>
+      </c>
+      <c r="U600" s="2" t="inlineStr"/>
+      <c r="V600" s="2" t="inlineStr"/>
+      <c r="W600" s="2" t="inlineStr">
+        <is>
+          <t>Luis Marvanejo</t>
+        </is>
+      </c>
+      <c r="X600" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y600" s="2" t="inlineStr"/>
+      <c r="Z600" s="2" t="inlineStr"/>
+      <c r="AA600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/luis-marvanejo-a2b1a750/</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>ARMAZÉNS DE MERCEARIA E AVÍCOLA MARVANEJO, LDA</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>ARMAZENS MARVANEJO</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>168718</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="inlineStr">
+        <is>
+          <t>Elvas</t>
+        </is>
+      </c>
+      <c r="F601" s="2" t="inlineStr"/>
+      <c r="G601" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Do Dia De Portugal - 10 De Junho De 2013, 63</t>
+        </is>
+      </c>
+      <c r="H601" s="2" t="inlineStr">
+        <is>
+          <t>7350-229</t>
+        </is>
+      </c>
+      <c r="I601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marvanejo.pt</t>
+        </is>
+      </c>
+      <c r="J601" s="2" t="inlineStr"/>
+      <c r="K601" s="2" t="inlineStr"/>
+      <c r="L601" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M601" s="2" t="inlineStr">
+        <is>
+          <t>23749802</t>
+        </is>
+      </c>
+      <c r="N601" s="2" t="inlineStr">
+        <is>
+          <t>geral@marvanejo.pt</t>
+        </is>
+      </c>
+      <c r="O601" s="2" t="inlineStr">
+        <is>
+          <t>+351 268 622 229</t>
+        </is>
+      </c>
+      <c r="P601" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="Q601" s="2" t="inlineStr">
+        <is>
+          <t>501265791</t>
+        </is>
+      </c>
+      <c r="R601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/armaz%C3%A9ns-marvanejo/</t>
+        </is>
+      </c>
+      <c r="S601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AMarvanejo</t>
+        </is>
+      </c>
+      <c r="T601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/marvanejo.armazens/</t>
+        </is>
+      </c>
+      <c r="U601" s="2" t="inlineStr"/>
+      <c r="V601" s="2" t="inlineStr"/>
+      <c r="W601" s="2" t="inlineStr">
+        <is>
+          <t>João Pedro Costa</t>
+        </is>
+      </c>
+      <c r="X601" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Department</t>
+        </is>
+      </c>
+      <c r="Y601" s="2" t="inlineStr"/>
+      <c r="Z601" s="2" t="inlineStr"/>
+      <c r="AA601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jo%C3%A3o-pedro-costa-7b23b5300/</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>SUPERFAFE - SUPERMERCADOS, LDA</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>INTERMARCHÉ FAFE</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>168717</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="inlineStr">
+        <is>
+          <t>Fafe</t>
+        </is>
+      </c>
+      <c r="F602" s="2" t="inlineStr"/>
+      <c r="G602" s="2" t="inlineStr">
+        <is>
+          <t>Bouça De Cavadas</t>
+        </is>
+      </c>
+      <c r="H602" s="2" t="inlineStr">
+        <is>
+          <t>4820-099</t>
+        </is>
+      </c>
+      <c r="I602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.intermarchedefafe.com</t>
+        </is>
+      </c>
+      <c r="J602" s="2" t="inlineStr"/>
+      <c r="K602" s="2" t="inlineStr"/>
+      <c r="L602" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M602" s="2" t="inlineStr">
+        <is>
+          <t>19522064</t>
+        </is>
+      </c>
+      <c r="N602" s="2" t="inlineStr">
+        <is>
+          <t>interfafe@intermarchedefafe.com</t>
+        </is>
+      </c>
+      <c r="O602" s="2" t="inlineStr">
+        <is>
+          <t>+351 253 590 808</t>
+        </is>
+      </c>
+      <c r="P602" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q602" s="2" t="inlineStr">
+        <is>
+          <t>503961159</t>
+        </is>
+      </c>
+      <c r="R602" s="2" t="inlineStr"/>
+      <c r="S602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/intermarche.fafe?ref=intermarche_de_fafe</t>
+        </is>
+      </c>
+      <c r="T602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/intermarchedefafe?ref=intermarche_de_fafe</t>
+        </is>
+      </c>
+      <c r="U602" s="2" t="inlineStr"/>
+      <c r="V602" s="2" t="inlineStr"/>
+      <c r="W602" s="2" t="inlineStr">
+        <is>
+          <t>Vera Ferreira</t>
+        </is>
+      </c>
+      <c r="X602" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Assistant</t>
+        </is>
+      </c>
+      <c r="Y602" s="2" t="inlineStr"/>
+      <c r="Z602" s="2" t="inlineStr"/>
+      <c r="AA602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vera-ferreira-322227214/</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>MUITO MENOS - COMÉRCIO E DISTRIBUIÇÃO, LDA</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr"/>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>168716</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="inlineStr">
+        <is>
+          <t>Paranhos Sei</t>
+        </is>
+      </c>
+      <c r="F603" s="2" t="inlineStr"/>
+      <c r="G603" s="2" t="inlineStr">
+        <is>
+          <t>Quinta Da Lavandeira</t>
+        </is>
+      </c>
+      <c r="H603" s="2" t="inlineStr">
+        <is>
+          <t>6270-133</t>
+        </is>
+      </c>
+      <c r="I603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.muitomenos.pt</t>
+        </is>
+      </c>
+      <c r="J603" s="2" t="inlineStr"/>
+      <c r="K603" s="2" t="inlineStr"/>
+      <c r="L603" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="M603" s="2" t="inlineStr">
+        <is>
+          <t>11915241</t>
+        </is>
+      </c>
+      <c r="N603" s="2" t="inlineStr">
+        <is>
+          <t>geral@muitomenos.pt</t>
+        </is>
+      </c>
+      <c r="O603" s="2" t="inlineStr">
+        <is>
+          <t>+351 238 976 108</t>
+        </is>
+      </c>
+      <c r="P603" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q603" s="2" t="inlineStr">
+        <is>
+          <t>509379990</t>
+        </is>
+      </c>
+      <c r="R603" s="2" t="inlineStr"/>
+      <c r="S603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100090212505536</t>
+        </is>
+      </c>
+      <c r="T603" s="2" t="inlineStr"/>
+      <c r="U603" s="2" t="inlineStr"/>
+      <c r="V603" s="2" t="inlineStr"/>
+      <c r="W603" s="2" t="inlineStr"/>
+      <c r="X603" s="2" t="inlineStr"/>
+      <c r="Y603" s="2" t="inlineStr"/>
+      <c r="Z603" s="2" t="inlineStr"/>
+      <c r="AA603" s="2" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>Batista &amp; Batista - Comércio Retalhista em Supermercados, Lda</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO BAPTISTA</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>168715</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>Luz Lgs</t>
+        </is>
+      </c>
+      <c r="F604" s="2" t="inlineStr"/>
+      <c r="G604" s="2" t="inlineStr">
+        <is>
+          <t>Urbanização Dos Montes Da Luz, Lote 58</t>
+        </is>
+      </c>
+      <c r="H604" s="2" t="inlineStr">
+        <is>
+          <t>8600-164</t>
+        </is>
+      </c>
+      <c r="I604" s="2" t="inlineStr">
+        <is>
+          <t>https://www.baptista.shop</t>
+        </is>
+      </c>
+      <c r="J604" s="2" t="inlineStr"/>
+      <c r="K604" s="2" t="inlineStr"/>
+      <c r="L604" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M604" s="2" t="inlineStr">
+        <is>
+          <t>5889151</t>
+        </is>
+      </c>
+      <c r="N604" s="2" t="inlineStr">
+        <is>
+          <t>info@baptista.shop</t>
+        </is>
+      </c>
+      <c r="O604" s="2" t="inlineStr"/>
+      <c r="P604" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q604" s="2" t="inlineStr">
+        <is>
+          <t>503701360</t>
+        </is>
+      </c>
+      <c r="R604" s="2" t="inlineStr"/>
+      <c r="S604" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/supermercadobaptista</t>
+        </is>
+      </c>
+      <c r="T604" s="2" t="inlineStr"/>
+      <c r="U604" s="2" t="inlineStr"/>
+      <c r="V604" s="2" t="inlineStr"/>
+      <c r="W604" s="2" t="inlineStr"/>
+      <c r="X604" s="2" t="inlineStr"/>
+      <c r="Y604" s="2" t="inlineStr"/>
+      <c r="Z604" s="2" t="inlineStr"/>
+      <c r="AA604" s="2" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>ALCAFER - COMÉRCIO E INDÚSTRIA DE PRODUTOS ALIMENTARES, LDA</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr"/>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>168714</t>
+        </is>
+      </c>
+      <c r="D605" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E605" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F605" s="2" t="inlineStr"/>
+      <c r="G605" s="2" t="inlineStr">
+        <is>
+          <t>Rua Fernando Farinha, 24A Bloco C</t>
+        </is>
+      </c>
+      <c r="H605" s="2" t="inlineStr">
+        <is>
+          <t>1950-448</t>
+        </is>
+      </c>
+      <c r="I605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alcafer.pt</t>
+        </is>
+      </c>
+      <c r="J605" s="2" t="inlineStr"/>
+      <c r="K605" s="2" t="inlineStr"/>
+      <c r="L605" s="2" t="inlineStr"/>
+      <c r="M605" s="2" t="inlineStr">
+        <is>
+          <t>16796455</t>
+        </is>
+      </c>
+      <c r="N605" s="2" t="inlineStr">
+        <is>
+          <t>alcafer@alcafer.pt</t>
+        </is>
+      </c>
+      <c r="O605" s="2" t="inlineStr">
+        <is>
+          <t>+351 263 516 109</t>
+        </is>
+      </c>
+      <c r="P605" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="Q605" s="2" t="inlineStr">
+        <is>
+          <t>500255024</t>
+        </is>
+      </c>
+      <c r="R605" s="2" t="inlineStr"/>
+      <c r="S605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/AlcaferLda/</t>
+        </is>
+      </c>
+      <c r="T605" s="2" t="inlineStr"/>
+      <c r="U605" s="2" t="inlineStr"/>
+      <c r="V605" s="2" t="inlineStr"/>
+      <c r="W605" s="2" t="inlineStr"/>
+      <c r="X605" s="2" t="inlineStr"/>
+      <c r="Y605" s="2" t="inlineStr"/>
+      <c r="Z605" s="2" t="inlineStr"/>
+      <c r="AA605" s="2" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>SOPREI - CASH AND CARRY, C.R.L.</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr"/>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>168713</t>
+        </is>
+      </c>
+      <c r="D606" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E606" s="2" t="inlineStr">
+        <is>
+          <t>Sertã</t>
+        </is>
+      </c>
+      <c r="F606" s="2" t="inlineStr"/>
+      <c r="G606" s="2" t="inlineStr">
+        <is>
+          <t>Rua J, 18</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="inlineStr">
+        <is>
+          <t>6100-607</t>
+        </is>
+      </c>
+      <c r="I606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.soprei.pt</t>
+        </is>
+      </c>
+      <c r="J606" s="2" t="inlineStr"/>
+      <c r="K606" s="2" t="inlineStr"/>
+      <c r="L606" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M606" s="2" t="inlineStr">
+        <is>
+          <t>7095327</t>
+        </is>
+      </c>
+      <c r="N606" s="2" t="inlineStr">
+        <is>
+          <t>geral@soprei.pt</t>
+        </is>
+      </c>
+      <c r="O606" s="2" t="inlineStr">
+        <is>
+          <t>+351 274 600 120</t>
+        </is>
+      </c>
+      <c r="P606" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="Q606" s="2" t="inlineStr">
+        <is>
+          <t>500274029</t>
+        </is>
+      </c>
+      <c r="R606" s="2" t="inlineStr"/>
+      <c r="S606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Soprei-Cash-Carry-109612010743313</t>
+        </is>
+      </c>
+      <c r="T606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sopreicashcarry/</t>
+        </is>
+      </c>
+      <c r="U606" s="2" t="inlineStr"/>
+      <c r="V606" s="2" t="inlineStr"/>
+      <c r="W606" s="2" t="inlineStr"/>
+      <c r="X606" s="2" t="inlineStr"/>
+      <c r="Y606" s="2" t="inlineStr"/>
+      <c r="Z606" s="2" t="inlineStr"/>
+      <c r="AA606" s="2" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>A.MARQUES, LDA</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr"/>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>168712</t>
+        </is>
+      </c>
+      <c r="D607" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E607" s="2" t="inlineStr">
+        <is>
+          <t>Caldas Da Rainha</t>
+        </is>
+      </c>
+      <c r="F607" s="2" t="inlineStr"/>
+      <c r="G607" s="2" t="inlineStr">
+        <is>
+          <t>Rua Carreira Do Gado, 20</t>
+        </is>
+      </c>
+      <c r="H607" s="2" t="inlineStr">
+        <is>
+          <t>2500-286</t>
+        </is>
+      </c>
+      <c r="I607" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amarques.pt</t>
+        </is>
+      </c>
+      <c r="J607" s="2" t="inlineStr"/>
+      <c r="K607" s="2" t="inlineStr"/>
+      <c r="L607" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M607" s="2" t="inlineStr">
+        <is>
+          <t>7768680</t>
+        </is>
+      </c>
+      <c r="N607" s="2" t="inlineStr">
+        <is>
+          <t>geral@amarques.pt</t>
+        </is>
+      </c>
+      <c r="O607" s="2" t="inlineStr">
+        <is>
+          <t>+351 262 841 005</t>
+        </is>
+      </c>
+      <c r="P607" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q607" s="2" t="inlineStr">
+        <is>
+          <t>502414529</t>
+        </is>
+      </c>
+      <c r="R607" s="2" t="inlineStr"/>
+      <c r="S607" s="2" t="inlineStr"/>
+      <c r="T607" s="2" t="inlineStr"/>
+      <c r="U607" s="2" t="inlineStr"/>
+      <c r="V607" s="2" t="inlineStr"/>
+      <c r="W607" s="2" t="inlineStr">
+        <is>
+          <t>Hernani Mendonça</t>
+        </is>
+      </c>
+      <c r="X607" s="2" t="inlineStr">
+        <is>
+          <t>Specialized Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y607" s="2" t="inlineStr"/>
+      <c r="Z607" s="2" t="inlineStr"/>
+      <c r="AA607" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hernani-mendon%C3%A7a-0ba66b33/</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>ANTIMAQUE - PROJECTOS E EQUIPAMENTOS, S.A.</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr"/>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>168711</t>
+        </is>
+      </c>
+      <c r="D608" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E608" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F608" s="2" t="inlineStr"/>
+      <c r="G608" s="2" t="inlineStr">
+        <is>
+          <t>Praça Das Flores, 54</t>
+        </is>
+      </c>
+      <c r="H608" s="2" t="inlineStr">
+        <is>
+          <t>4300-401</t>
+        </is>
+      </c>
+      <c r="I608" s="2" t="inlineStr">
+        <is>
+          <t>https://www.eupoupo.com</t>
+        </is>
+      </c>
+      <c r="J608" s="2" t="inlineStr"/>
+      <c r="K608" s="2" t="inlineStr"/>
+      <c r="L608" s="2" t="inlineStr"/>
+      <c r="M608" s="2" t="inlineStr">
+        <is>
+          <t>3295064</t>
+        </is>
+      </c>
+      <c r="N608" s="2" t="inlineStr">
+        <is>
+          <t>geral@eupoupo.com</t>
+        </is>
+      </c>
+      <c r="O608" s="2" t="inlineStr"/>
+      <c r="P608" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q608" s="2" t="inlineStr">
+        <is>
+          <t>503265721</t>
+        </is>
+      </c>
+      <c r="R608" s="2" t="inlineStr"/>
+      <c r="S608" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/eupoupo.pt</t>
+        </is>
+      </c>
+      <c r="T608" s="2" t="inlineStr">
+        <is>
+          <t>http://instagram.com/eupoupo</t>
+        </is>
+      </c>
+      <c r="U608" s="2" t="inlineStr"/>
+      <c r="V608" s="2" t="inlineStr"/>
+      <c r="W608" s="2" t="inlineStr"/>
+      <c r="X608" s="2" t="inlineStr"/>
+      <c r="Y608" s="2" t="inlineStr"/>
+      <c r="Z608" s="2" t="inlineStr"/>
+      <c r="AA608" s="2" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>MIRA RAMOS - SUPERMERCADO DE JOAQUIM FERNANDES RAMOS, LDA</t>
+        </is>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>MIRA RAMOS SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>168710</t>
+        </is>
+      </c>
+      <c r="D609" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E609" s="2" t="inlineStr">
+        <is>
+          <t>Arcozelo Vng</t>
+        </is>
+      </c>
+      <c r="F609" s="2" t="inlineStr"/>
+      <c r="G609" s="2" t="inlineStr">
+        <is>
+          <t>Rua Heróis Da Pátria, 956</t>
+        </is>
+      </c>
+      <c r="H609" s="2" t="inlineStr">
+        <is>
+          <t>4410-001</t>
+        </is>
+      </c>
+      <c r="I609" s="2" t="inlineStr">
+        <is>
+          <t>https://www.miraramos.com</t>
+        </is>
+      </c>
+      <c r="J609" s="2" t="inlineStr"/>
+      <c r="K609" s="2" t="inlineStr"/>
+      <c r="L609" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M609" s="2" t="inlineStr">
+        <is>
+          <t>7171821</t>
+        </is>
+      </c>
+      <c r="N609" s="2" t="inlineStr">
+        <is>
+          <t>geral@miraramos.com</t>
+        </is>
+      </c>
+      <c r="O609" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 762 3019</t>
+        </is>
+      </c>
+      <c r="P609" s="2" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="Q609" s="2" t="inlineStr">
+        <is>
+          <t>501247998</t>
+        </is>
+      </c>
+      <c r="R609" s="2" t="inlineStr"/>
+      <c r="S609" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/supermercadomiraramos</t>
+        </is>
+      </c>
+      <c r="T609" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermiraramos</t>
+        </is>
+      </c>
+      <c r="U609" s="2" t="inlineStr"/>
+      <c r="V609" s="2" t="inlineStr"/>
+      <c r="W609" s="2" t="inlineStr"/>
+      <c r="X609" s="2" t="inlineStr"/>
+      <c r="Y609" s="2" t="inlineStr"/>
+      <c r="Z609" s="2" t="inlineStr"/>
+      <c r="AA609" s="2" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>JOÃO, SILVA &amp; COELHO, LDA</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>Belpreço</t>
+        </is>
+      </c>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>168709</t>
+        </is>
+      </c>
+      <c r="D610" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E610" s="2" t="inlineStr">
+        <is>
+          <t>Vila Nova De Gaia</t>
+        </is>
+      </c>
+      <c r="F610" s="2" t="inlineStr"/>
+      <c r="G610" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Gomes Júnior, 88</t>
+        </is>
+      </c>
+      <c r="H610" s="2" t="inlineStr">
+        <is>
+          <t>4405-750</t>
+        </is>
+      </c>
+      <c r="I610" s="2" t="inlineStr">
+        <is>
+          <t>https://www.belpreco.pt</t>
+        </is>
+      </c>
+      <c r="J610" s="2" t="inlineStr"/>
+      <c r="K610" s="2" t="inlineStr"/>
+      <c r="L610" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M610" s="2" t="inlineStr">
+        <is>
+          <t>3336551</t>
+        </is>
+      </c>
+      <c r="N610" s="2" t="inlineStr">
+        <is>
+          <t>info@belpreco.pt</t>
+        </is>
+      </c>
+      <c r="O610" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 711 2651</t>
+        </is>
+      </c>
+      <c r="P610" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="Q610" s="2" t="inlineStr">
+        <is>
+          <t>500150729</t>
+        </is>
+      </c>
+      <c r="R610" s="2" t="inlineStr"/>
+      <c r="S610" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Supermercado-Belpreço-283515975040217</t>
+        </is>
+      </c>
+      <c r="T610" s="2" t="inlineStr"/>
+      <c r="U610" s="2" t="inlineStr"/>
+      <c r="V610" s="2" t="inlineStr"/>
+      <c r="W610" s="2" t="inlineStr"/>
+      <c r="X610" s="2" t="inlineStr"/>
+      <c r="Y610" s="2" t="inlineStr"/>
+      <c r="Z610" s="2" t="inlineStr"/>
+      <c r="AA610" s="2" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>ANTÓNIO CARVALHO FERREIRA CARLOS, ARMAZÉM DE MERCEARIAS, LDA</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>O Azeiteiro</t>
+        </is>
+      </c>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>168707</t>
+        </is>
+      </c>
+      <c r="D611" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E611" s="2" t="inlineStr">
+        <is>
+          <t>Montijo</t>
+        </is>
+      </c>
+      <c r="F611" s="2" t="inlineStr"/>
+      <c r="G611" s="2" t="inlineStr">
+        <is>
+          <t>R. Joaquim de Almeida nº1022</t>
+        </is>
+      </c>
+      <c r="H611" s="2" t="inlineStr">
+        <is>
+          <t>2870-339</t>
+        </is>
+      </c>
+      <c r="I611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oazeiteiro.com</t>
+        </is>
+      </c>
+      <c r="J611" s="2" t="inlineStr"/>
+      <c r="K611" s="2" t="inlineStr"/>
+      <c r="L611" s="2" t="inlineStr"/>
+      <c r="M611" s="2" t="inlineStr">
+        <is>
+          <t>13961654</t>
+        </is>
+      </c>
+      <c r="N611" s="2" t="inlineStr">
+        <is>
+          <t>clientes@oazeiteiro.com</t>
+        </is>
+      </c>
+      <c r="O611" s="2" t="inlineStr"/>
+      <c r="P611" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="Q611" s="2" t="inlineStr">
+        <is>
+          <t>502110872</t>
+        </is>
+      </c>
+      <c r="R611" s="2" t="inlineStr"/>
+      <c r="S611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/OAzeiteiroOficial/</t>
+        </is>
+      </c>
+      <c r="T611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oazeiteirocashandcarry/</t>
+        </is>
+      </c>
+      <c r="U611" s="2" t="inlineStr"/>
+      <c r="V611" s="2" t="inlineStr"/>
+      <c r="W611" s="2" t="inlineStr">
+        <is>
+          <t>Diogo Marques</t>
+        </is>
+      </c>
+      <c r="X611" s="2" t="inlineStr">
+        <is>
+          <t>Sales and Marketing Director</t>
+        </is>
+      </c>
+      <c r="Y611" s="2" t="inlineStr"/>
+      <c r="Z611" s="2" t="inlineStr"/>
+      <c r="AA611" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/diogo-marques-924844396</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>DREAM PLUS - COMÉRCIO E DISTRIBUIÇÃO DE PRODUTOS ALIMENTARES, LDA</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>DREAM PLUS</t>
+        </is>
+      </c>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>168706</t>
+        </is>
+      </c>
+      <c r="D612" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E612" s="2" t="inlineStr">
+        <is>
+          <t>Oeiras</t>
+        </is>
+      </c>
+      <c r="F612" s="2" t="inlineStr"/>
+      <c r="G612" s="2" t="inlineStr">
+        <is>
+          <t>Rua De Santa Cruz, 7 1ºesq.</t>
+        </is>
+      </c>
+      <c r="H612" s="2" t="inlineStr">
+        <is>
+          <t>2780-356</t>
+        </is>
+      </c>
+      <c r="I612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dreamplus.pt</t>
+        </is>
+      </c>
+      <c r="J612" s="2" t="inlineStr"/>
+      <c r="K612" s="2" t="inlineStr"/>
+      <c r="L612" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="M612" s="2" t="inlineStr">
+        <is>
+          <t>27133293</t>
+        </is>
+      </c>
+      <c r="N612" s="2" t="inlineStr">
+        <is>
+          <t>encomendas@dreamplus.pt</t>
+        </is>
+      </c>
+      <c r="O612" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 445 2369</t>
+        </is>
+      </c>
+      <c r="P612" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q612" s="2" t="inlineStr">
+        <is>
+          <t>506006794</t>
+        </is>
+      </c>
+      <c r="R612" s="2" t="inlineStr"/>
+      <c r="S612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Dr3amPlus/</t>
+        </is>
+      </c>
+      <c r="T612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dreamplus.pt/</t>
+        </is>
+      </c>
+      <c r="U612" s="2" t="inlineStr"/>
+      <c r="V612" s="2" t="inlineStr"/>
+      <c r="W612" s="2" t="inlineStr"/>
+      <c r="X612" s="2" t="inlineStr"/>
+      <c r="Y612" s="2" t="inlineStr"/>
+      <c r="Z612" s="2" t="inlineStr"/>
+      <c r="AA612" s="2" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>AMARAL &amp; FILHOS - DISTRIBUIÇÃO, S.A.</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>POUPANÇA - CASH &amp; CARRY</t>
+        </is>
+      </c>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>168705</t>
+        </is>
+      </c>
+      <c r="D613" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="inlineStr">
+        <is>
+          <t>Sintra</t>
+        </is>
+      </c>
+      <c r="F613" s="2" t="inlineStr"/>
+      <c r="G613" s="2" t="inlineStr">
+        <is>
+          <t>Rua Fontes Pereira De Melo, 18</t>
+        </is>
+      </c>
+      <c r="H613" s="2" t="inlineStr">
+        <is>
+          <t>2714-506</t>
+        </is>
+      </c>
+      <c r="I613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.poupanca.pt</t>
+        </is>
+      </c>
+      <c r="J613" s="2" t="inlineStr"/>
+      <c r="K613" s="2" t="inlineStr"/>
+      <c r="L613" s="2" t="inlineStr"/>
+      <c r="M613" s="2" t="inlineStr">
+        <is>
+          <t>107758060</t>
+        </is>
+      </c>
+      <c r="N613" s="2" t="inlineStr">
+        <is>
+          <t>geral@poupanca.pt</t>
+        </is>
+      </c>
+      <c r="O613" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 915 6540</t>
+        </is>
+      </c>
+      <c r="P613" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q613" s="2" t="inlineStr">
+        <is>
+          <t>512038694</t>
+        </is>
+      </c>
+      <c r="R613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/poupan%C3%A7a-cash-carry/</t>
+        </is>
+      </c>
+      <c r="S613" s="2" t="inlineStr"/>
+      <c r="T613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/poupanca_cashandcarry/</t>
+        </is>
+      </c>
+      <c r="U613" s="2" t="inlineStr"/>
+      <c r="V613" s="2" t="inlineStr"/>
+      <c r="W613" s="2" t="inlineStr">
+        <is>
+          <t>Diogo Garcia</t>
+        </is>
+      </c>
+      <c r="X613" s="2" t="inlineStr">
+        <is>
+          <t>Operations Supervisor</t>
+        </is>
+      </c>
+      <c r="Y613" s="2" t="inlineStr"/>
+      <c r="Z613" s="2" t="inlineStr"/>
+      <c r="AA613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/diogo-garcia-9691b1ba/</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>AMARAL &amp; FILHOS - DISTRIBUIÇÃO, S.A.</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>POUPANÇA - CASH &amp; CARRY</t>
+        </is>
+      </c>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>168705</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>Sintra</t>
+        </is>
+      </c>
+      <c r="F614" s="2" t="inlineStr"/>
+      <c r="G614" s="2" t="inlineStr">
+        <is>
+          <t>Rua Fontes Pereira De Melo, 18</t>
+        </is>
+      </c>
+      <c r="H614" s="2" t="inlineStr">
+        <is>
+          <t>2714-506</t>
+        </is>
+      </c>
+      <c r="I614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.poupanca.pt</t>
+        </is>
+      </c>
+      <c r="J614" s="2" t="inlineStr"/>
+      <c r="K614" s="2" t="inlineStr"/>
+      <c r="L614" s="2" t="inlineStr"/>
+      <c r="M614" s="2" t="inlineStr">
+        <is>
+          <t>107758060</t>
+        </is>
+      </c>
+      <c r="N614" s="2" t="inlineStr">
+        <is>
+          <t>geral@poupanca.pt</t>
+        </is>
+      </c>
+      <c r="O614" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 915 6540</t>
+        </is>
+      </c>
+      <c r="P614" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q614" s="2" t="inlineStr">
+        <is>
+          <t>512038694</t>
+        </is>
+      </c>
+      <c r="R614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/poupan%C3%A7a-cash-carry/</t>
+        </is>
+      </c>
+      <c r="S614" s="2" t="inlineStr"/>
+      <c r="T614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/poupanca_cashandcarry/</t>
+        </is>
+      </c>
+      <c r="U614" s="2" t="inlineStr"/>
+      <c r="V614" s="2" t="inlineStr"/>
+      <c r="W614" s="2" t="inlineStr">
+        <is>
+          <t>Catarina Conde</t>
+        </is>
+      </c>
+      <c r="X614" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Officer</t>
+        </is>
+      </c>
+      <c r="Y614" s="2" t="inlineStr"/>
+      <c r="Z614" s="2" t="inlineStr"/>
+      <c r="AA614" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/catarina-conde-7562161bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>NEOMÁQUINA - SUPERMERCADOS, LDA</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr"/>
+      <c r="C615" s="2" t="inlineStr">
+        <is>
+          <t>168704</t>
+        </is>
+      </c>
+      <c r="D615" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="inlineStr">
+        <is>
+          <t>Benedita</t>
+        </is>
+      </c>
+      <c r="F615" s="2" t="inlineStr"/>
+      <c r="G615" s="2" t="inlineStr">
+        <is>
+          <t>Rua Dos Monges De Cister, S/N</t>
+        </is>
+      </c>
+      <c r="H615" s="2" t="inlineStr">
+        <is>
+          <t>2475-130</t>
+        </is>
+      </c>
+      <c r="I615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.neomaquina.pt</t>
+        </is>
+      </c>
+      <c r="J615" s="2" t="inlineStr"/>
+      <c r="K615" s="2" t="inlineStr"/>
+      <c r="L615" s="2" t="inlineStr"/>
+      <c r="M615" s="2" t="inlineStr">
+        <is>
+          <t>21327265</t>
+        </is>
+      </c>
+      <c r="N615" s="2" t="inlineStr">
+        <is>
+          <t>geral@neomaquina.pt</t>
+        </is>
+      </c>
+      <c r="O615" s="2" t="inlineStr">
+        <is>
+          <t>+351 236 209 980</t>
+        </is>
+      </c>
+      <c r="P615" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="Q615" s="2" t="inlineStr">
+        <is>
+          <t>502526130</t>
+        </is>
+      </c>
+      <c r="R615" s="2" t="inlineStr"/>
+      <c r="S615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/neomaquina/</t>
+        </is>
+      </c>
+      <c r="T615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/neomaquina/</t>
+        </is>
+      </c>
+      <c r="U615" s="2" t="inlineStr"/>
+      <c r="V615" s="2" t="inlineStr"/>
+      <c r="W615" s="2" t="inlineStr"/>
+      <c r="X615" s="2" t="inlineStr"/>
+      <c r="Y615" s="2" t="inlineStr"/>
+      <c r="Z615" s="2" t="inlineStr"/>
+      <c r="AA615" s="2" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>MALAQUIAS - DISTRIBUIÇÃO ALIMENTAR, LDA</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>MALAQUIAS CASH AND CARRY</t>
+        </is>
+      </c>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>168703</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>Ovar</t>
+        </is>
+      </c>
+      <c r="F616" s="2" t="inlineStr"/>
+      <c r="G616" s="2" t="inlineStr">
+        <is>
+          <t>Avenida 16 De Maio</t>
+        </is>
+      </c>
+      <c r="H616" s="2" t="inlineStr">
+        <is>
+          <t>3880-102</t>
+        </is>
+      </c>
+      <c r="I616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.malaquias.pt</t>
+        </is>
+      </c>
+      <c r="J616" s="2" t="inlineStr"/>
+      <c r="K616" s="2" t="inlineStr"/>
+      <c r="L616" s="2" t="inlineStr"/>
+      <c r="M616" s="2" t="inlineStr">
+        <is>
+          <t>58701344</t>
+        </is>
+      </c>
+      <c r="N616" s="2" t="inlineStr">
+        <is>
+          <t>malaquias@malaquias.pt</t>
+        </is>
+      </c>
+      <c r="O616" s="2" t="inlineStr">
+        <is>
+          <t>+351 256 580 200</t>
+        </is>
+      </c>
+      <c r="P616" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="Q616" s="2" t="inlineStr">
+        <is>
+          <t>500221510</t>
+        </is>
+      </c>
+      <c r="R616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/malaquias-distribui-o-alimentar/</t>
+        </is>
+      </c>
+      <c r="S616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/malaquiascashandcarry/</t>
+        </is>
+      </c>
+      <c r="T616" s="2" t="inlineStr"/>
+      <c r="U616" s="2" t="inlineStr"/>
+      <c r="V616" s="2" t="inlineStr"/>
+      <c r="W616" s="2" t="inlineStr">
+        <is>
+          <t>Faustino Azevedo</t>
+        </is>
+      </c>
+      <c r="X616" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y616" s="2" t="inlineStr"/>
+      <c r="Z616" s="2" t="inlineStr"/>
+      <c r="AA616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/faustino-azevedo-14405427b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>MALAQUIAS - DISTRIBUIÇÃO ALIMENTAR, LDA</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>MALAQUIAS CASH AND CARRY</t>
+        </is>
+      </c>
+      <c r="C617" s="2" t="inlineStr">
+        <is>
+          <t>168703</t>
+        </is>
+      </c>
+      <c r="D617" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="inlineStr">
+        <is>
+          <t>Ovar</t>
+        </is>
+      </c>
+      <c r="F617" s="2" t="inlineStr"/>
+      <c r="G617" s="2" t="inlineStr">
+        <is>
+          <t>Avenida 16 De Maio</t>
+        </is>
+      </c>
+      <c r="H617" s="2" t="inlineStr">
+        <is>
+          <t>3880-102</t>
+        </is>
+      </c>
+      <c r="I617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.malaquias.pt</t>
+        </is>
+      </c>
+      <c r="J617" s="2" t="inlineStr"/>
+      <c r="K617" s="2" t="inlineStr"/>
+      <c r="L617" s="2" t="inlineStr"/>
+      <c r="M617" s="2" t="inlineStr">
+        <is>
+          <t>58701344</t>
+        </is>
+      </c>
+      <c r="N617" s="2" t="inlineStr">
+        <is>
+          <t>malaquias@malaquias.pt</t>
+        </is>
+      </c>
+      <c r="O617" s="2" t="inlineStr">
+        <is>
+          <t>+351 256 580 200</t>
+        </is>
+      </c>
+      <c r="P617" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="Q617" s="2" t="inlineStr">
+        <is>
+          <t>500221510</t>
+        </is>
+      </c>
+      <c r="R617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/malaquias-distribui-o-alimentar/</t>
+        </is>
+      </c>
+      <c r="S617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/malaquiascashandcarry/</t>
+        </is>
+      </c>
+      <c r="T617" s="2" t="inlineStr"/>
+      <c r="U617" s="2" t="inlineStr"/>
+      <c r="V617" s="2" t="inlineStr"/>
+      <c r="W617" s="2" t="inlineStr">
+        <is>
+          <t>Paulo Delgado</t>
+        </is>
+      </c>
+      <c r="X617" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y617" s="2" t="inlineStr"/>
+      <c r="Z617" s="2" t="inlineStr"/>
+      <c r="AA617" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/paulo-jorge-martins-delgado-325136123</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>MALAQUIAS - DISTRIBUIÇÃO ALIMENTAR, LDA</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>MALAQUIAS CASH AND CARRY</t>
+        </is>
+      </c>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>168703</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>Ovar</t>
+        </is>
+      </c>
+      <c r="F618" s="2" t="inlineStr"/>
+      <c r="G618" s="2" t="inlineStr">
+        <is>
+          <t>Avenida 16 De Maio</t>
+        </is>
+      </c>
+      <c r="H618" s="2" t="inlineStr">
+        <is>
+          <t>3880-102</t>
+        </is>
+      </c>
+      <c r="I618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.malaquias.pt</t>
+        </is>
+      </c>
+      <c r="J618" s="2" t="inlineStr"/>
+      <c r="K618" s="2" t="inlineStr"/>
+      <c r="L618" s="2" t="inlineStr"/>
+      <c r="M618" s="2" t="inlineStr">
+        <is>
+          <t>58701344</t>
+        </is>
+      </c>
+      <c r="N618" s="2" t="inlineStr">
+        <is>
+          <t>malaquias@malaquias.pt</t>
+        </is>
+      </c>
+      <c r="O618" s="2" t="inlineStr">
+        <is>
+          <t>+351 256 580 200</t>
+        </is>
+      </c>
+      <c r="P618" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="Q618" s="2" t="inlineStr">
+        <is>
+          <t>500221510</t>
+        </is>
+      </c>
+      <c r="R618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/malaquias-distribui-o-alimentar/</t>
+        </is>
+      </c>
+      <c r="S618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/malaquiascashandcarry/</t>
+        </is>
+      </c>
+      <c r="T618" s="2" t="inlineStr"/>
+      <c r="U618" s="2" t="inlineStr"/>
+      <c r="V618" s="2" t="inlineStr"/>
+      <c r="W618" s="2" t="inlineStr">
+        <is>
+          <t>Rui Ribeiro</t>
+        </is>
+      </c>
+      <c r="X618" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y618" s="2" t="inlineStr"/>
+      <c r="Z618" s="2" t="inlineStr"/>
+      <c r="AA618" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/rui-ribeiro-a148b8287</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>MALAQUIAS - DISTRIBUIÇÃO ALIMENTAR, LDA</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>MALAQUIAS CASH AND CARRY</t>
+        </is>
+      </c>
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>168703</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="inlineStr">
+        <is>
+          <t>Ovar</t>
+        </is>
+      </c>
+      <c r="F619" s="2" t="inlineStr"/>
+      <c r="G619" s="2" t="inlineStr">
+        <is>
+          <t>Avenida 16 De Maio</t>
+        </is>
+      </c>
+      <c r="H619" s="2" t="inlineStr">
+        <is>
+          <t>3880-102</t>
+        </is>
+      </c>
+      <c r="I619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.malaquias.pt</t>
+        </is>
+      </c>
+      <c r="J619" s="2" t="inlineStr"/>
+      <c r="K619" s="2" t="inlineStr"/>
+      <c r="L619" s="2" t="inlineStr"/>
+      <c r="M619" s="2" t="inlineStr">
+        <is>
+          <t>58701344</t>
+        </is>
+      </c>
+      <c r="N619" s="2" t="inlineStr">
+        <is>
+          <t>malaquias@malaquias.pt</t>
+        </is>
+      </c>
+      <c r="O619" s="2" t="inlineStr">
+        <is>
+          <t>+351 256 580 200</t>
+        </is>
+      </c>
+      <c r="P619" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="Q619" s="2" t="inlineStr">
+        <is>
+          <t>500221510</t>
+        </is>
+      </c>
+      <c r="R619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/malaquias-distribui-o-alimentar/</t>
+        </is>
+      </c>
+      <c r="S619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/malaquiascashandcarry/</t>
+        </is>
+      </c>
+      <c r="T619" s="2" t="inlineStr"/>
+      <c r="U619" s="2" t="inlineStr"/>
+      <c r="V619" s="2" t="inlineStr"/>
+      <c r="W619" s="2" t="inlineStr">
+        <is>
+          <t>Julia Peixoto</t>
+        </is>
+      </c>
+      <c r="X619" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commercial </t>
+        </is>
+      </c>
+      <c r="Y619" s="2" t="inlineStr"/>
+      <c r="Z619" s="2" t="inlineStr"/>
+      <c r="AA619" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/julia-peixoto-1b0328281</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>CASH ULTRAMAR - COMÉRCIO PRODUTOS ALIMENTARES, LDA</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>CENCOMARK – Cash &amp; Carry.</t>
+        </is>
+      </c>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>168702</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="inlineStr">
+        <is>
+          <t>Sacavém</t>
+        </is>
+      </c>
+      <c r="F620" s="2" t="inlineStr"/>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>Rua Marechal Gomes Da Costa, 86</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="inlineStr">
+        <is>
+          <t>2685-871</t>
+        </is>
+      </c>
+      <c r="I620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cencomark.com</t>
+        </is>
+      </c>
+      <c r="J620" s="2" t="inlineStr"/>
+      <c r="K620" s="2" t="inlineStr"/>
+      <c r="L620" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M620" s="2" t="inlineStr">
+        <is>
+          <t>3523603</t>
+        </is>
+      </c>
+      <c r="N620" s="2" t="inlineStr">
+        <is>
+          <t>geral@cencomark.com</t>
+        </is>
+      </c>
+      <c r="O620" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 942 8171</t>
+        </is>
+      </c>
+      <c r="P620" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q620" s="2" t="inlineStr">
+        <is>
+          <t>505464250</t>
+        </is>
+      </c>
+      <c r="R620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cencomark/</t>
+        </is>
+      </c>
+      <c r="S620" s="2" t="inlineStr"/>
+      <c r="T620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cencomark_/</t>
+        </is>
+      </c>
+      <c r="U620" s="2" t="inlineStr"/>
+      <c r="V620" s="2" t="inlineStr"/>
+      <c r="W620" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Manuel Carmo Costa</t>
+        </is>
+      </c>
+      <c r="X620" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y620" s="2" t="inlineStr"/>
+      <c r="Z620" s="2" t="inlineStr"/>
+      <c r="AA620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jorge-manuel-carmo-costa-54673355/</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>Telbac Teixeira &amp; Leite Bacalhau e Congelados Lda.</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>Telbac</t>
+        </is>
+      </c>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>168701</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="inlineStr">
+        <is>
+          <t>Lufrei</t>
+        </is>
+      </c>
+      <c r="F621" s="2" t="inlineStr"/>
+      <c r="G621" s="2" t="inlineStr">
+        <is>
+          <t>Rua Das Marginhas, 169</t>
+        </is>
+      </c>
+      <c r="H621" s="2" t="inlineStr">
+        <is>
+          <t>4600-683</t>
+        </is>
+      </c>
+      <c r="I621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.telbac.pt</t>
+        </is>
+      </c>
+      <c r="J621" s="2" t="inlineStr"/>
+      <c r="K621" s="2" t="inlineStr"/>
+      <c r="L621" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M621" s="2" t="inlineStr">
+        <is>
+          <t>11219274</t>
+        </is>
+      </c>
+      <c r="N621" s="2" t="inlineStr">
+        <is>
+          <t>geral@telbac.pt</t>
+        </is>
+      </c>
+      <c r="O621" s="2" t="inlineStr">
+        <is>
+          <t>+351 255 424 272</t>
+        </is>
+      </c>
+      <c r="P621" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q621" s="2" t="inlineStr">
+        <is>
+          <t>503161608</t>
+        </is>
+      </c>
+      <c r="R621" s="2" t="inlineStr"/>
+      <c r="S621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/telbacbacalhauecongelados</t>
+        </is>
+      </c>
+      <c r="T621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/telbaclda/</t>
+        </is>
+      </c>
+      <c r="U621" s="2" t="inlineStr"/>
+      <c r="V621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@Telbac</t>
+        </is>
+      </c>
+      <c r="W621" s="2" t="inlineStr"/>
+      <c r="X621" s="2" t="inlineStr"/>
+      <c r="Y621" s="2" t="inlineStr"/>
+      <c r="Z621" s="2" t="inlineStr"/>
+      <c r="AA621" s="2" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>GANILHO - SUPERMERCADOS, LDA</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>CASA GANILHO SUPERMERCADOS</t>
+        </is>
+      </c>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>168700</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr">
+        <is>
+          <t>São Felix Da Marinha</t>
+        </is>
+      </c>
+      <c r="F622" s="2" t="inlineStr"/>
+      <c r="G622" s="2" t="inlineStr">
+        <is>
+          <t>Rua Combatentes Do Ultramar, 181</t>
+        </is>
+      </c>
+      <c r="H622" s="2" t="inlineStr">
+        <is>
+          <t>4410-198</t>
+        </is>
+      </c>
+      <c r="I622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.casaganilho.com</t>
+        </is>
+      </c>
+      <c r="J622" s="2" t="inlineStr"/>
+      <c r="K622" s="2" t="inlineStr"/>
+      <c r="L622" s="2" t="inlineStr"/>
+      <c r="M622" s="2" t="inlineStr">
+        <is>
+          <t>2482393</t>
+        </is>
+      </c>
+      <c r="N622" s="2" t="inlineStr">
+        <is>
+          <t>geral@casaganilho.com</t>
+        </is>
+      </c>
+      <c r="O622" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 753 8986</t>
+        </is>
+      </c>
+      <c r="P622" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q622" s="2" t="inlineStr">
+        <is>
+          <t>507869362</t>
+        </is>
+      </c>
+      <c r="R622" s="2" t="inlineStr"/>
+      <c r="S622" s="2" t="inlineStr"/>
+      <c r="T622" s="2" t="inlineStr"/>
+      <c r="U622" s="2" t="inlineStr"/>
+      <c r="V622" s="2" t="inlineStr"/>
+      <c r="W622" s="2" t="inlineStr"/>
+      <c r="X622" s="2" t="inlineStr"/>
+      <c r="Y622" s="2" t="inlineStr"/>
+      <c r="Z622" s="2" t="inlineStr"/>
+      <c r="AA622" s="2" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>SOQUERMAR - COMÉRCIO DE PRODUTOS ALIMENTARES, LDA</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>SOQUERMAR</t>
+        </is>
+      </c>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>168699</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr">
+        <is>
+          <t>Serzedo Vng</t>
+        </is>
+      </c>
+      <c r="F623" s="2" t="inlineStr"/>
+      <c r="G623" s="2" t="inlineStr">
+        <is>
+          <t>Rua Norton De Matos, 688/690</t>
+        </is>
+      </c>
+      <c r="H623" s="2" t="inlineStr">
+        <is>
+          <t>4410-537</t>
+        </is>
+      </c>
+      <c r="I623" s="2" t="inlineStr">
+        <is>
+          <t>https://www.soquermar.com</t>
+        </is>
+      </c>
+      <c r="J623" s="2" t="inlineStr"/>
+      <c r="K623" s="2" t="inlineStr"/>
+      <c r="L623" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M623" s="2" t="inlineStr">
+        <is>
+          <t>1336456</t>
+        </is>
+      </c>
+      <c r="N623" s="2" t="inlineStr">
+        <is>
+          <t>geral@soquermar.com</t>
+        </is>
+      </c>
+      <c r="O623" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 480 7427</t>
+        </is>
+      </c>
+      <c r="P623" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="Q623" s="2" t="inlineStr">
+        <is>
+          <t>503394548</t>
+        </is>
+      </c>
+      <c r="R623" s="2" t="inlineStr"/>
+      <c r="S623" s="2" t="inlineStr"/>
+      <c r="T623" s="2" t="inlineStr"/>
+      <c r="U623" s="2" t="inlineStr"/>
+      <c r="V623" s="2" t="inlineStr"/>
+      <c r="W623" s="2" t="inlineStr"/>
+      <c r="X623" s="2" t="inlineStr"/>
+      <c r="Y623" s="2" t="inlineStr"/>
+      <c r="Z623" s="2" t="inlineStr"/>
+      <c r="AA623" s="2" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>José Alberto Tavares Lda</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr"/>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>168697</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="inlineStr">
+        <is>
+          <t>Flamengos</t>
+        </is>
+      </c>
+      <c r="F624" s="2" t="inlineStr"/>
+      <c r="G624" s="2" t="inlineStr">
+        <is>
+          <t>Rua Do Cantinho, 1</t>
+        </is>
+      </c>
+      <c r="H624" s="2" t="inlineStr">
+        <is>
+          <t>9900-401</t>
+        </is>
+      </c>
+      <c r="I624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.josealbertotavares.pt</t>
+        </is>
+      </c>
+      <c r="J624" s="2" t="inlineStr"/>
+      <c r="K624" s="2" t="inlineStr"/>
+      <c r="L624" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M624" s="2" t="inlineStr">
+        <is>
+          <t>3029120</t>
+        </is>
+      </c>
+      <c r="N624" s="2" t="inlineStr">
+        <is>
+          <t>geral@josealbertotavares.pt</t>
+        </is>
+      </c>
+      <c r="O624" s="2" t="inlineStr">
+        <is>
+          <t>+351 292 948 361</t>
+        </is>
+      </c>
+      <c r="P624" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q624" s="2" t="inlineStr">
+        <is>
+          <t>512102988</t>
+        </is>
+      </c>
+      <c r="R624" s="2" t="inlineStr"/>
+      <c r="S624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/josealbertotavares.pt</t>
+        </is>
+      </c>
+      <c r="T624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/josealbertotavares.pt</t>
+        </is>
+      </c>
+      <c r="U624" s="2" t="inlineStr"/>
+      <c r="V624" s="2" t="inlineStr"/>
+      <c r="W624" s="2" t="inlineStr">
+        <is>
+          <t>José Alberto Tavares</t>
+        </is>
+      </c>
+      <c r="X624" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y624" s="2" t="inlineStr"/>
+      <c r="Z624" s="2" t="inlineStr"/>
+      <c r="AA624" s="2" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>HUMBERTO MARQUES - CASH AND CARRY, LDA</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>Humberto Marques</t>
+        </is>
+      </c>
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>168696</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="inlineStr">
+        <is>
+          <t>São Mamede</t>
+        </is>
+      </c>
+      <c r="F625" s="2" t="inlineStr"/>
+      <c r="G625" s="2" t="inlineStr">
+        <is>
+          <t>Estrada De Fátima</t>
+        </is>
+      </c>
+      <c r="H625" s="2" t="inlineStr">
+        <is>
+          <t>2495-036</t>
+        </is>
+      </c>
+      <c r="I625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.humbertomarques.pt</t>
+        </is>
+      </c>
+      <c r="J625" s="2" t="inlineStr"/>
+      <c r="K625" s="2" t="inlineStr"/>
+      <c r="L625" s="2" t="inlineStr"/>
+      <c r="M625" s="2" t="inlineStr">
+        <is>
+          <t>4954878</t>
+        </is>
+      </c>
+      <c r="N625" s="2" t="inlineStr">
+        <is>
+          <t>encomendas@humbertomarques.pt</t>
+        </is>
+      </c>
+      <c r="O625" s="2" t="inlineStr">
+        <is>
+          <t>+351 244 704 445</t>
+        </is>
+      </c>
+      <c r="P625" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q625" s="2" t="inlineStr">
+        <is>
+          <t>505404923</t>
+        </is>
+      </c>
+      <c r="R625" s="2" t="inlineStr"/>
+      <c r="S625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/humbertomarquesprodutos/</t>
+        </is>
+      </c>
+      <c r="T625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/humbertomarqueslda/</t>
+        </is>
+      </c>
+      <c r="U625" s="2" t="inlineStr"/>
+      <c r="V625" s="2" t="inlineStr"/>
+      <c r="W625" s="2" t="inlineStr">
+        <is>
+          <t>Humberto Marques</t>
+        </is>
+      </c>
+      <c r="X625" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y625" s="2" t="inlineStr"/>
+      <c r="Z625" s="2" t="inlineStr"/>
+      <c r="AA625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/humbertomarques78/</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>VAGALIMENTAR - DISTRIBUIÇÃO PRODUTOS ALIMENTARES, LDA</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr"/>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>168695</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="inlineStr">
+        <is>
+          <t>Vagos</t>
+        </is>
+      </c>
+      <c r="F626" s="2" t="inlineStr"/>
+      <c r="G626" s="2" t="inlineStr">
+        <is>
+          <t>Zona Industrial De Vagos, Lote 8</t>
+        </is>
+      </c>
+      <c r="H626" s="2" t="inlineStr">
+        <is>
+          <t>3840-385</t>
+        </is>
+      </c>
+      <c r="I626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vagalimentar.pt</t>
+        </is>
+      </c>
+      <c r="J626" s="2" t="inlineStr"/>
+      <c r="K626" s="2" t="inlineStr"/>
+      <c r="L626" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M626" s="2" t="inlineStr">
+        <is>
+          <t>2367844</t>
+        </is>
+      </c>
+      <c r="N626" s="2" t="inlineStr">
+        <is>
+          <t>geral@vagalimentar.pt</t>
+        </is>
+      </c>
+      <c r="O626" s="2" t="inlineStr">
+        <is>
+          <t>+351 234 783 097</t>
+        </is>
+      </c>
+      <c r="P626" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q626" s="2" t="inlineStr">
+        <is>
+          <t>507134958</t>
+        </is>
+      </c>
+      <c r="R626" s="2" t="inlineStr"/>
+      <c r="S626" s="2" t="inlineStr"/>
+      <c r="T626" s="2" t="inlineStr"/>
+      <c r="U626" s="2" t="inlineStr"/>
+      <c r="V626" s="2" t="inlineStr"/>
+      <c r="W626" s="2" t="inlineStr"/>
+      <c r="X626" s="2" t="inlineStr"/>
+      <c r="Y626" s="2" t="inlineStr"/>
+      <c r="Z626" s="2" t="inlineStr"/>
+      <c r="AA626" s="2" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>DISTRIROTA - DISTRIBUIÇÃO ALIMENTAR, LDA</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr"/>
+      <c r="C627" s="2" t="inlineStr">
+        <is>
+          <t>168694</t>
+        </is>
+      </c>
+      <c r="D627" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="inlineStr">
+        <is>
+          <t>Horta</t>
+        </is>
+      </c>
+      <c r="F627" s="2" t="inlineStr"/>
+      <c r="G627" s="2" t="inlineStr">
+        <is>
+          <t>Rua D, 3C</t>
+        </is>
+      </c>
+      <c r="H627" s="2" t="inlineStr">
+        <is>
+          <t>9900-046</t>
+        </is>
+      </c>
+      <c r="I627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.distrirota.pt</t>
+        </is>
+      </c>
+      <c r="J627" s="2" t="inlineStr"/>
+      <c r="K627" s="2" t="inlineStr"/>
+      <c r="L627" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M627" s="2" t="inlineStr">
+        <is>
+          <t>3017645</t>
+        </is>
+      </c>
+      <c r="N627" s="2" t="inlineStr">
+        <is>
+          <t>geral@distrirota.pt</t>
+        </is>
+      </c>
+      <c r="O627" s="2" t="inlineStr">
+        <is>
+          <t>+351 292 945 040</t>
+        </is>
+      </c>
+      <c r="P627" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q627" s="2" t="inlineStr">
+        <is>
+          <t>507806689</t>
+        </is>
+      </c>
+      <c r="R627" s="2" t="inlineStr"/>
+      <c r="S627" s="2" t="inlineStr"/>
+      <c r="T627" s="2" t="inlineStr"/>
+      <c r="U627" s="2" t="inlineStr"/>
+      <c r="V627" s="2" t="inlineStr"/>
+      <c r="W627" s="2" t="inlineStr"/>
+      <c r="X627" s="2" t="inlineStr"/>
+      <c r="Y627" s="2" t="inlineStr"/>
+      <c r="Z627" s="2" t="inlineStr"/>
+      <c r="AA627" s="2" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>ILÍDIO FRAGOSO &amp; FILHOS, LDA</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr"/>
+      <c r="C628" s="2" t="inlineStr">
+        <is>
+          <t>168693</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="inlineStr">
+        <is>
+          <t>Boavista Dos Pinheiros</t>
+        </is>
+      </c>
+      <c r="F628" s="2" t="inlineStr"/>
+      <c r="G628" s="2" t="inlineStr">
+        <is>
+          <t>Parque Industrial, Lote 4</t>
+        </is>
+      </c>
+      <c r="H628" s="2" t="inlineStr">
+        <is>
+          <t>7630-033</t>
+        </is>
+      </c>
+      <c r="I628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ilidiofragoso.com</t>
+        </is>
+      </c>
+      <c r="J628" s="2" t="inlineStr"/>
+      <c r="K628" s="2" t="inlineStr"/>
+      <c r="L628" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M628" s="2" t="inlineStr">
+        <is>
+          <t>7692573</t>
+        </is>
+      </c>
+      <c r="N628" s="2" t="inlineStr">
+        <is>
+          <t>geral@ilidiofragoso.com</t>
+        </is>
+      </c>
+      <c r="O628" s="2" t="inlineStr">
+        <is>
+          <t>+351 283 386 669</t>
+        </is>
+      </c>
+      <c r="P628" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q628" s="2" t="inlineStr">
+        <is>
+          <t>506944204</t>
+        </is>
+      </c>
+      <c r="R628" s="2" t="inlineStr"/>
+      <c r="S628" s="2" t="inlineStr"/>
+      <c r="T628" s="2" t="inlineStr"/>
+      <c r="U628" s="2" t="inlineStr"/>
+      <c r="V628" s="2" t="inlineStr"/>
+      <c r="W628" s="2" t="inlineStr"/>
+      <c r="X628" s="2" t="inlineStr"/>
+      <c r="Y628" s="2" t="inlineStr"/>
+      <c r="Z628" s="2" t="inlineStr"/>
+      <c r="AA628" s="2" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>TROVIDOCE - PRODUTOS DE CONFEITARIA, LDA</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr"/>
+      <c r="C629" s="2" t="inlineStr">
+        <is>
+          <t>168692</t>
+        </is>
+      </c>
+      <c r="D629" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="inlineStr">
+        <is>
+          <t>Amendoeira</t>
+        </is>
+      </c>
+      <c r="F629" s="2" t="inlineStr"/>
+      <c r="G629" s="2" t="inlineStr">
+        <is>
+          <t>Zona Industrial, Lote 63</t>
+        </is>
+      </c>
+      <c r="H629" s="2" t="inlineStr">
+        <is>
+          <t>5340-021</t>
+        </is>
+      </c>
+      <c r="I629" s="2" t="inlineStr">
+        <is>
+          <t>https://www.trovidoce.pt</t>
+        </is>
+      </c>
+      <c r="J629" s="2" t="inlineStr"/>
+      <c r="K629" s="2" t="inlineStr"/>
+      <c r="L629" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M629" s="2" t="inlineStr">
+        <is>
+          <t>3158380</t>
+        </is>
+      </c>
+      <c r="N629" s="2" t="inlineStr">
+        <is>
+          <t>geral@trovidoce.pt</t>
+        </is>
+      </c>
+      <c r="O629" s="2" t="inlineStr">
+        <is>
+          <t>+351 278 425 770</t>
+        </is>
+      </c>
+      <c r="P629" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="Q629" s="2" t="inlineStr">
+        <is>
+          <t>500238545</t>
+        </is>
+      </c>
+      <c r="R629" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/trovidoce-lda/</t>
+        </is>
+      </c>
+      <c r="S629" s="2" t="inlineStr"/>
+      <c r="T629" s="2" t="inlineStr"/>
+      <c r="U629" s="2" t="inlineStr"/>
+      <c r="V629" s="2" t="inlineStr"/>
+      <c r="W629" s="2" t="inlineStr">
+        <is>
+          <t>Cláudio Trovisco</t>
+        </is>
+      </c>
+      <c r="X629" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y629" s="2" t="inlineStr"/>
+      <c r="Z629" s="2" t="inlineStr"/>
+      <c r="AA629" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/claudiotrovisco/</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>MAMMAFIORE PORTUGAL, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B630" s="2" t="inlineStr"/>
+      <c r="C630" s="2" t="inlineStr">
+        <is>
+          <t>168691</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="inlineStr">
+        <is>
+          <t>Sintra</t>
+        </is>
+      </c>
+      <c r="F630" s="2" t="inlineStr"/>
+      <c r="G630" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Doutor Luís Sá, 9 Armazém H</t>
+        </is>
+      </c>
+      <c r="H630" s="2" t="inlineStr">
+        <is>
+          <t>2710-022</t>
+        </is>
+      </c>
+      <c r="I630" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mammafiore.pt</t>
+        </is>
+      </c>
+      <c r="J630" s="2" t="inlineStr"/>
+      <c r="K630" s="2" t="inlineStr"/>
+      <c r="L630" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M630" s="2" t="inlineStr">
+        <is>
+          <t>2412578</t>
+        </is>
+      </c>
+      <c r="N630" s="2" t="inlineStr">
+        <is>
+          <t>geral@mammafiore.eu</t>
+        </is>
+      </c>
+      <c r="O630" s="2" t="inlineStr"/>
+      <c r="P630" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q630" s="2" t="inlineStr">
+        <is>
+          <t>517034573</t>
+        </is>
+      </c>
+      <c r="R630" s="2" t="inlineStr"/>
+      <c r="S630" s="2" t="inlineStr"/>
+      <c r="T630" s="2" t="inlineStr"/>
+      <c r="U630" s="2" t="inlineStr"/>
+      <c r="V630" s="2" t="inlineStr"/>
+      <c r="W630" s="2" t="inlineStr"/>
+      <c r="X630" s="2" t="inlineStr"/>
+      <c r="Y630" s="2" t="inlineStr"/>
+      <c r="Z630" s="2" t="inlineStr"/>
+      <c r="AA630" s="2" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>MERCADINHO DA AJUDA - PRODUTOS ALIMENTARES, LDA</t>
+        </is>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>Mercadinho</t>
+        </is>
+      </c>
+      <c r="C631" s="2" t="inlineStr">
+        <is>
+          <t>168690</t>
+        </is>
+      </c>
+      <c r="D631" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="inlineStr">
+        <is>
+          <t>Funchal</t>
+        </is>
+      </c>
+      <c r="F631" s="2" t="inlineStr"/>
+      <c r="G631" s="2" t="inlineStr">
+        <is>
+          <t>Estrada Monumental, 186</t>
+        </is>
+      </c>
+      <c r="H631" s="2" t="inlineStr">
+        <is>
+          <t>9000-098</t>
+        </is>
+      </c>
+      <c r="I631" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mercadinhoonline.pt</t>
+        </is>
+      </c>
+      <c r="J631" s="2" t="inlineStr"/>
+      <c r="K631" s="2" t="inlineStr"/>
+      <c r="L631" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M631" s="2" t="inlineStr">
+        <is>
+          <t>1848157</t>
+        </is>
+      </c>
+      <c r="N631" s="2" t="inlineStr">
+        <is>
+          <t>geral@mercadinhoonline.pt</t>
+        </is>
+      </c>
+      <c r="O631" s="2" t="inlineStr">
+        <is>
+          <t>+351 291 626 317</t>
+        </is>
+      </c>
+      <c r="P631" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q631" s="2" t="inlineStr">
+        <is>
+          <t>511096445</t>
+        </is>
+      </c>
+      <c r="R631" s="2" t="inlineStr"/>
+      <c r="S631" s="2" t="inlineStr"/>
+      <c r="T631" s="2" t="inlineStr"/>
+      <c r="U631" s="2" t="inlineStr"/>
+      <c r="V631" s="2" t="inlineStr"/>
+      <c r="W631" s="2" t="inlineStr"/>
+      <c r="X631" s="2" t="inlineStr"/>
+      <c r="Y631" s="2" t="inlineStr"/>
+      <c r="Z631" s="2" t="inlineStr"/>
+      <c r="AA631" s="2" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>MANTEIGARIA SILVA, LDA</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr"/>
+      <c r="C632" s="2" t="inlineStr">
+        <is>
+          <t>168689</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F632" s="2" t="inlineStr"/>
+      <c r="G632" s="2" t="inlineStr">
+        <is>
+          <t>Rua Dom Antão De Almada, 1C/D</t>
+        </is>
+      </c>
+      <c r="H632" s="2" t="inlineStr">
+        <is>
+          <t>1100-197</t>
+        </is>
+      </c>
+      <c r="I632" s="2" t="inlineStr">
+        <is>
+          <t>https://loja.manteigariasilva.pt, https://www.manteigariasilva.pt</t>
+        </is>
+      </c>
+      <c r="J632" s="2" t="inlineStr"/>
+      <c r="K632" s="2" t="inlineStr"/>
+      <c r="L632" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M632" s="2" t="inlineStr">
+        <is>
+          <t>2364329</t>
+        </is>
+      </c>
+      <c r="N632" s="2" t="inlineStr">
+        <is>
+          <t>geral@manteigariasilva.pt</t>
+        </is>
+      </c>
+      <c r="O632" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 342 4905</t>
+        </is>
+      </c>
+      <c r="P632" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="Q632" s="2" t="inlineStr">
+        <is>
+          <t>500842221</t>
+        </is>
+      </c>
+      <c r="R632" s="2" t="inlineStr"/>
+      <c r="S632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/manteigaria.silva</t>
+        </is>
+      </c>
+      <c r="T632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/manteigariasilva1890/?hl=en</t>
+        </is>
+      </c>
+      <c r="U632" s="2" t="inlineStr"/>
+      <c r="V632" s="2" t="inlineStr"/>
+      <c r="W632" s="2" t="inlineStr"/>
+      <c r="X632" s="2" t="inlineStr"/>
+      <c r="Y632" s="2" t="inlineStr"/>
+      <c r="Z632" s="2" t="inlineStr"/>
+      <c r="AA632" s="2" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>COMPANHIA DOS CABAZES, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B633" s="2" t="inlineStr"/>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>168688</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="inlineStr">
+        <is>
+          <t>Beja</t>
+        </is>
+      </c>
+      <c r="F633" s="2" t="inlineStr"/>
+      <c r="G633" s="2" t="inlineStr">
+        <is>
+          <t>Largo Dos Correios, 21A 1ºdto.</t>
+        </is>
+      </c>
+      <c r="H633" s="2" t="inlineStr">
+        <is>
+          <t>7800-419</t>
+        </is>
+      </c>
+      <c r="I633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.companhiadoscabazes.pt</t>
+        </is>
+      </c>
+      <c r="J633" s="2" t="inlineStr"/>
+      <c r="K633" s="2" t="inlineStr"/>
+      <c r="L633" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M633" s="2" t="inlineStr">
+        <is>
+          <t>2462350</t>
+        </is>
+      </c>
+      <c r="N633" s="2" t="inlineStr">
+        <is>
+          <t>geral@companhiadoscabazes.pt</t>
+        </is>
+      </c>
+      <c r="O633" s="2" t="inlineStr"/>
+      <c r="P633" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q633" s="2" t="inlineStr">
+        <is>
+          <t>515343242</t>
+        </is>
+      </c>
+      <c r="R633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/companhia-dos-cabazes/</t>
+        </is>
+      </c>
+      <c r="S633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/companhiadoscabazes/</t>
+        </is>
+      </c>
+      <c r="T633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/companhiadoscabazes</t>
+        </is>
+      </c>
+      <c r="U633" s="2" t="inlineStr"/>
+      <c r="V633" s="2" t="inlineStr"/>
+      <c r="W633" s="2" t="inlineStr"/>
+      <c r="X633" s="2" t="inlineStr"/>
+      <c r="Y633" s="2" t="inlineStr"/>
+      <c r="Z633" s="2" t="inlineStr"/>
+      <c r="AA633" s="2" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>COVISERRA - COMÉRCIO E DISTRIBUIÇÃO DE PRODUTOS REGIONAIS, LDA</t>
+        </is>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>COVISERRA</t>
+        </is>
+      </c>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>168687</t>
+        </is>
+      </c>
+      <c r="D634" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="inlineStr">
+        <is>
+          <t>Covilhã</t>
+        </is>
+      </c>
+      <c r="F634" s="2" t="inlineStr">
+        <is>
+          <t>Castelo Branco</t>
+        </is>
+      </c>
+      <c r="G634" s="2" t="inlineStr">
+        <is>
+          <t>Parque Industrial do Tortosendo, Lote 101</t>
+        </is>
+      </c>
+      <c r="H634" s="2" t="inlineStr">
+        <is>
+          <t>6200-823</t>
+        </is>
+      </c>
+      <c r="I634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coviserra.pt</t>
+        </is>
+      </c>
+      <c r="J634" s="2" t="inlineStr"/>
+      <c r="K634" s="2" t="inlineStr"/>
+      <c r="L634" s="2" t="inlineStr"/>
+      <c r="M634" s="2" t="inlineStr">
+        <is>
+          <t>3072870</t>
+        </is>
+      </c>
+      <c r="N634" s="2" t="inlineStr">
+        <is>
+          <t>geral@coviserra.pt</t>
+        </is>
+      </c>
+      <c r="O634" s="2" t="inlineStr">
+        <is>
+          <t>+351 275 327 031</t>
+        </is>
+      </c>
+      <c r="P634" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q634" s="2" t="inlineStr">
+        <is>
+          <t>502353066</t>
+        </is>
+      </c>
+      <c r="R634" s="2" t="inlineStr"/>
+      <c r="S634" s="2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/coviserra</t>
+        </is>
+      </c>
+      <c r="T634" s="2" t="inlineStr"/>
+      <c r="U634" s="2" t="inlineStr"/>
+      <c r="V634" s="2" t="inlineStr"/>
+      <c r="W634" s="2" t="inlineStr">
+        <is>
+          <t>Paulo Jorge Tourais</t>
+        </is>
+      </c>
+      <c r="X634" s="2" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="Y634" s="2" t="inlineStr"/>
+      <c r="Z634" s="2" t="inlineStr"/>
+      <c r="AA634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paulo-jorge-tourais-723b3135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>FERSUMOS, LDA</t>
+        </is>
+      </c>
+      <c r="B635" s="2" t="inlineStr"/>
+      <c r="C635" s="2" t="inlineStr">
+        <is>
+          <t>168686</t>
+        </is>
+      </c>
+      <c r="D635" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="inlineStr">
+        <is>
+          <t>São João Da Pesqueira</t>
+        </is>
+      </c>
+      <c r="F635" s="2" t="inlineStr"/>
+      <c r="G635" s="2" t="inlineStr">
+        <is>
+          <t>Parque Industrial Do Lameirão, Lote 6</t>
+        </is>
+      </c>
+      <c r="H635" s="2" t="inlineStr">
+        <is>
+          <t>5130-301</t>
+        </is>
+      </c>
+      <c r="I635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fersumos.pt</t>
+        </is>
+      </c>
+      <c r="J635" s="2" t="inlineStr"/>
+      <c r="K635" s="2" t="inlineStr"/>
+      <c r="L635" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M635" s="2" t="inlineStr">
+        <is>
+          <t>2011203</t>
+        </is>
+      </c>
+      <c r="N635" s="2" t="inlineStr">
+        <is>
+          <t>fersumos@fersumos.pt</t>
+        </is>
+      </c>
+      <c r="O635" s="2" t="inlineStr">
+        <is>
+          <t>+351 254 481 477</t>
+        </is>
+      </c>
+      <c r="P635" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q635" s="2" t="inlineStr">
+        <is>
+          <t>517478536</t>
+        </is>
+      </c>
+      <c r="R635" s="2" t="inlineStr"/>
+      <c r="S635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fersumos/</t>
+        </is>
+      </c>
+      <c r="T635" s="2" t="inlineStr"/>
+      <c r="U635" s="2" t="inlineStr"/>
+      <c r="V635" s="2" t="inlineStr"/>
+      <c r="W635" s="2" t="inlineStr">
+        <is>
+          <t>Flávio Pires</t>
+        </is>
+      </c>
+      <c r="X635" s="2" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="Y635" s="2" t="inlineStr"/>
+      <c r="Z635" s="2" t="inlineStr"/>
+      <c r="AA635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fl%C3%A1viopires/</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>MERCEARIA PÉROLA DO ARSENAL, LDA</t>
+        </is>
+      </c>
+      <c r="B636" s="2" t="inlineStr"/>
+      <c r="C636" s="2" t="inlineStr">
+        <is>
+          <t>168685</t>
+        </is>
+      </c>
+      <c r="D636" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F636" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G636" s="2" t="inlineStr">
+        <is>
+          <t>Rua do Arsenal 94</t>
+        </is>
+      </c>
+      <c r="H636" s="2" t="inlineStr">
+        <is>
+          <t>1100-040</t>
+        </is>
+      </c>
+      <c r="I636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.peroladoarsenal.com</t>
+        </is>
+      </c>
+      <c r="J636" s="2" t="inlineStr"/>
+      <c r="K636" s="2" t="inlineStr"/>
+      <c r="L636" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M636" s="2" t="inlineStr">
+        <is>
+          <t>462273</t>
+        </is>
+      </c>
+      <c r="N636" s="2" t="inlineStr">
+        <is>
+          <t>peroladoarsenal4@gmail.com</t>
+        </is>
+      </c>
+      <c r="O636" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 342 7938</t>
+        </is>
+      </c>
+      <c r="P636" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="Q636" s="2" t="inlineStr">
+        <is>
+          <t>500191182</t>
+        </is>
+      </c>
+      <c r="R636" s="2" t="inlineStr"/>
+      <c r="S636" s="2" t="inlineStr"/>
+      <c r="T636" s="2" t="inlineStr"/>
+      <c r="U636" s="2" t="inlineStr"/>
+      <c r="V636" s="2" t="inlineStr"/>
+      <c r="W636" s="2" t="inlineStr"/>
+      <c r="X636" s="2" t="inlineStr"/>
+      <c r="Y636" s="2" t="inlineStr"/>
+      <c r="Z636" s="2" t="inlineStr"/>
+      <c r="AA636" s="2" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>IRMÃOS NORINHO, LDA</t>
+        </is>
+      </c>
+      <c r="B637" s="2" t="inlineStr"/>
+      <c r="C637" s="2" t="inlineStr">
+        <is>
+          <t>168684</t>
+        </is>
+      </c>
+      <c r="D637" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="inlineStr">
+        <is>
+          <t>Figueira Da Foz</t>
+        </is>
+      </c>
+      <c r="F637" s="2" t="inlineStr"/>
+      <c r="G637" s="2" t="inlineStr">
+        <is>
+          <t>Porto Liceia</t>
+        </is>
+      </c>
+      <c r="H637" s="2" t="inlineStr">
+        <is>
+          <t>3090-423</t>
+        </is>
+      </c>
+      <c r="I637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.irmaosnorinho.com</t>
+        </is>
+      </c>
+      <c r="J637" s="2" t="inlineStr"/>
+      <c r="K637" s="2" t="inlineStr"/>
+      <c r="L637" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M637" s="2" t="inlineStr">
+        <is>
+          <t>3199942</t>
+        </is>
+      </c>
+      <c r="N637" s="2" t="inlineStr">
+        <is>
+          <t>geral@irmaosnorinho.com</t>
+        </is>
+      </c>
+      <c r="O637" s="2" t="inlineStr">
+        <is>
+          <t>+351 233 939 867</t>
+        </is>
+      </c>
+      <c r="P637" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q637" s="2" t="inlineStr">
+        <is>
+          <t>505272601</t>
+        </is>
+      </c>
+      <c r="R637" s="2" t="inlineStr"/>
+      <c r="S637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100015887264537</t>
+        </is>
+      </c>
+      <c r="T637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/irmaosnorinho/</t>
+        </is>
+      </c>
+      <c r="U637" s="2" t="inlineStr"/>
+      <c r="V637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@Irm%C3%A3osNorinho</t>
+        </is>
+      </c>
+      <c r="W637" s="2" t="inlineStr"/>
+      <c r="X637" s="2" t="inlineStr"/>
+      <c r="Y637" s="2" t="inlineStr"/>
+      <c r="Z637" s="2" t="inlineStr"/>
+      <c r="AA637" s="2" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>BAIA &amp; CARVALHO, LDA</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr"/>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>168683</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="inlineStr">
+        <is>
+          <t>Cantanhede</t>
+        </is>
+      </c>
+      <c r="F638" s="2" t="inlineStr">
+        <is>
+          <t>Coimbra</t>
+        </is>
+      </c>
+      <c r="G638" s="2" t="inlineStr">
+        <is>
+          <t>Largo do Freixo, 2</t>
+        </is>
+      </c>
+      <c r="H638" s="2" t="inlineStr">
+        <is>
+          <t>3060-491</t>
+        </is>
+      </c>
+      <c r="I638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.baiacarvalho.pt</t>
+        </is>
+      </c>
+      <c r="J638" s="2" t="inlineStr"/>
+      <c r="K638" s="2" t="inlineStr"/>
+      <c r="L638" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M638" s="2" t="inlineStr">
+        <is>
+          <t>855309</t>
+        </is>
+      </c>
+      <c r="N638" s="2" t="inlineStr">
+        <is>
+          <t>info@baiacarvalho.pt</t>
+        </is>
+      </c>
+      <c r="O638" s="2" t="inlineStr">
+        <is>
+          <t>+351 231 422 793</t>
+        </is>
+      </c>
+      <c r="P638" s="2" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="Q638" s="2" t="inlineStr">
+        <is>
+          <t>500987963</t>
+        </is>
+      </c>
+      <c r="R638" s="2" t="inlineStr"/>
+      <c r="S638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/BA%C3%8DA-CARVALHO-LDA-100064086665628/</t>
+        </is>
+      </c>
+      <c r="T638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/baiacarvalho1/</t>
+        </is>
+      </c>
+      <c r="U638" s="2" t="inlineStr"/>
+      <c r="V638" s="2" t="inlineStr"/>
+      <c r="W638" s="2" t="inlineStr">
+        <is>
+          <t>Susana Batista</t>
+        </is>
+      </c>
+      <c r="X638" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Management</t>
+        </is>
+      </c>
+      <c r="Y638" s="2" t="inlineStr"/>
+      <c r="Z638" s="2" t="inlineStr"/>
+      <c r="AA638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/susana-batista-18586790/</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>SPLENDOUR PLANET, LDA</t>
+        </is>
+      </c>
+      <c r="B639" s="2" t="inlineStr"/>
+      <c r="C639" s="2" t="inlineStr">
+        <is>
+          <t>168682</t>
+        </is>
+      </c>
+      <c r="D639" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="inlineStr">
+        <is>
+          <t>São Domingos de Rana</t>
+        </is>
+      </c>
+      <c r="F639" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G639" s="2" t="inlineStr">
+        <is>
+          <t>Av. Salgueiro Maia, N.1025, 14B</t>
+        </is>
+      </c>
+      <c r="H639" s="2" t="inlineStr">
+        <is>
+          <t>2785-501</t>
+        </is>
+      </c>
+      <c r="I639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glood.pt, https://www.splendour.pt</t>
+        </is>
+      </c>
+      <c r="J639" s="2" t="inlineStr"/>
+      <c r="K639" s="2" t="inlineStr"/>
+      <c r="L639" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M639" s="2" t="inlineStr">
+        <is>
+          <t>317533</t>
+        </is>
+      </c>
+      <c r="N639" s="2" t="inlineStr">
+        <is>
+          <t>info@glood.pt</t>
+        </is>
+      </c>
+      <c r="O639" s="2" t="inlineStr"/>
+      <c r="P639" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q639" s="2" t="inlineStr">
+        <is>
+          <t>509900143</t>
+        </is>
+      </c>
+      <c r="R639" s="2" t="inlineStr"/>
+      <c r="S639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/glood.pt</t>
+        </is>
+      </c>
+      <c r="T639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gloodstore/</t>
+        </is>
+      </c>
+      <c r="U639" s="2" t="inlineStr"/>
+      <c r="V639" s="2" t="inlineStr"/>
+      <c r="W639" s="2" t="inlineStr">
+        <is>
+          <t>Cátia Ferreira</t>
+        </is>
+      </c>
+      <c r="X639" s="2" t="inlineStr">
+        <is>
+          <t>Administrative Assistant</t>
+        </is>
+      </c>
+      <c r="Y639" s="2" t="inlineStr"/>
+      <c r="Z639" s="2" t="inlineStr"/>
+      <c r="AA639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/c%C3%A1tia-ferreira-969ab11b3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>TALHOS SANTOS, LDA</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr"/>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>168681</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="inlineStr">
+        <is>
+          <t>Corroios</t>
+        </is>
+      </c>
+      <c r="F640" s="2" t="inlineStr"/>
+      <c r="G640" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cidade Tomar, 1 R/C C</t>
+        </is>
+      </c>
+      <c r="H640" s="2" t="inlineStr">
+        <is>
+          <t>2855-136</t>
+        </is>
+      </c>
+      <c r="I640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.talhonline.com</t>
+        </is>
+      </c>
+      <c r="J640" s="2" t="inlineStr"/>
+      <c r="K640" s="2" t="inlineStr"/>
+      <c r="L640" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M640" s="2" t="inlineStr">
+        <is>
+          <t>18486</t>
+        </is>
+      </c>
+      <c r="N640" s="2" t="inlineStr">
+        <is>
+          <t>geral@talhonline.com</t>
+        </is>
+      </c>
+      <c r="O640" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 253 2041</t>
+        </is>
+      </c>
+      <c r="P640" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="Q640" s="2" t="inlineStr">
+        <is>
+          <t>501752749</t>
+        </is>
+      </c>
+      <c r="R640" s="2" t="inlineStr"/>
+      <c r="S640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/talhonline/</t>
+        </is>
+      </c>
+      <c r="T640" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/talhonline/</t>
+        </is>
+      </c>
+      <c r="U640" s="2" t="inlineStr"/>
+      <c r="V640" s="2" t="inlineStr"/>
+      <c r="W640" s="2" t="inlineStr"/>
+      <c r="X640" s="2" t="inlineStr"/>
+      <c r="Y640" s="2" t="inlineStr"/>
+      <c r="Z640" s="2" t="inlineStr"/>
+      <c r="AA640" s="2" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>ANTÓNIO PIRES &amp; FILHO, LDA</t>
+        </is>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>MINIMERCADO PIRES</t>
+        </is>
+      </c>
+      <c r="C641" s="2" t="inlineStr">
+        <is>
+          <t>168680</t>
+        </is>
+      </c>
+      <c r="D641" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="inlineStr">
+        <is>
+          <t>Terrugem Elv</t>
+        </is>
+      </c>
+      <c r="F641" s="2" t="inlineStr"/>
+      <c r="G641" s="2" t="inlineStr">
+        <is>
+          <t>Rua Da Igreja, 127</t>
+        </is>
+      </c>
+      <c r="H641" s="2" t="inlineStr">
+        <is>
+          <t>7350-491</t>
+        </is>
+      </c>
+      <c r="I641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.antoniopires.pt</t>
+        </is>
+      </c>
+      <c r="J641" s="2" t="inlineStr"/>
+      <c r="K641" s="2" t="inlineStr"/>
+      <c r="L641" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M641" s="2" t="inlineStr">
+        <is>
+          <t>912885</t>
+        </is>
+      </c>
+      <c r="N641" s="2" t="inlineStr">
+        <is>
+          <t>piresterrugem@sapo.pt</t>
+        </is>
+      </c>
+      <c r="O641" s="2" t="inlineStr">
+        <is>
+          <t>+351 268 657 449</t>
+        </is>
+      </c>
+      <c r="P641" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q641" s="2" t="inlineStr">
+        <is>
+          <t>516720538</t>
+        </is>
+      </c>
+      <c r="R641" s="2" t="inlineStr"/>
+      <c r="S641" s="2" t="inlineStr"/>
+      <c r="T641" s="2" t="inlineStr"/>
+      <c r="U641" s="2" t="inlineStr"/>
+      <c r="V641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCGqxGEwfVvP0nov7fqTlKvg</t>
+        </is>
+      </c>
+      <c r="W641" s="2" t="inlineStr">
+        <is>
+          <t>Antonio Pires</t>
+        </is>
+      </c>
+      <c r="X641" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y641" s="2" t="inlineStr"/>
+      <c r="Z641" s="2" t="inlineStr"/>
+      <c r="AA641" s="2" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>ANTÓNIO PIRES &amp; FILHO, LDA</t>
+        </is>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>MINIMERCADO PIRES</t>
+        </is>
+      </c>
+      <c r="C642" s="2" t="inlineStr">
+        <is>
+          <t>168680</t>
+        </is>
+      </c>
+      <c r="D642" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="inlineStr">
+        <is>
+          <t>Terrugem Elv</t>
+        </is>
+      </c>
+      <c r="F642" s="2" t="inlineStr"/>
+      <c r="G642" s="2" t="inlineStr">
+        <is>
+          <t>Rua Da Igreja, 127</t>
+        </is>
+      </c>
+      <c r="H642" s="2" t="inlineStr">
+        <is>
+          <t>7350-491</t>
+        </is>
+      </c>
+      <c r="I642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.antoniopires.pt</t>
+        </is>
+      </c>
+      <c r="J642" s="2" t="inlineStr"/>
+      <c r="K642" s="2" t="inlineStr"/>
+      <c r="L642" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M642" s="2" t="inlineStr">
+        <is>
+          <t>912885</t>
+        </is>
+      </c>
+      <c r="N642" s="2" t="inlineStr">
+        <is>
+          <t>piresterrugem@sapo.pt</t>
+        </is>
+      </c>
+      <c r="O642" s="2" t="inlineStr">
+        <is>
+          <t>+351 268 657 449</t>
+        </is>
+      </c>
+      <c r="P642" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q642" s="2" t="inlineStr">
+        <is>
+          <t>516720538</t>
+        </is>
+      </c>
+      <c r="R642" s="2" t="inlineStr"/>
+      <c r="S642" s="2" t="inlineStr"/>
+      <c r="T642" s="2" t="inlineStr"/>
+      <c r="U642" s="2" t="inlineStr"/>
+      <c r="V642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCGqxGEwfVvP0nov7fqTlKvg</t>
+        </is>
+      </c>
+      <c r="W642" s="2" t="inlineStr">
+        <is>
+          <t>Vitor Pires</t>
+        </is>
+      </c>
+      <c r="X642" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y642" s="2" t="inlineStr"/>
+      <c r="Z642" s="2" t="inlineStr"/>
+      <c r="AA642" s="2" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
+          <t>DISALTO - DISTRIBUIÇÃO ALIMENTAR, LDA</t>
+        </is>
+      </c>
+      <c r="B643" s="2" t="inlineStr"/>
+      <c r="C643" s="2" t="inlineStr">
+        <is>
+          <t>168679</t>
+        </is>
+      </c>
+      <c r="D643" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E643" s="2" t="inlineStr">
+        <is>
+          <t>Entroncamento</t>
+        </is>
+      </c>
+      <c r="F643" s="2" t="inlineStr"/>
+      <c r="G643" s="2" t="inlineStr">
+        <is>
+          <t>Rua Casal Do Melão</t>
+        </is>
+      </c>
+      <c r="H643" s="2" t="inlineStr">
+        <is>
+          <t>2330-106</t>
+        </is>
+      </c>
+      <c r="I643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.disalto.pt</t>
+        </is>
+      </c>
+      <c r="J643" s="2" t="inlineStr"/>
+      <c r="K643" s="2" t="inlineStr"/>
+      <c r="L643" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M643" s="2" t="inlineStr">
+        <is>
+          <t>1438617</t>
+        </is>
+      </c>
+      <c r="N643" s="2" t="inlineStr">
+        <is>
+          <t>comercial@disalto.pt</t>
+        </is>
+      </c>
+      <c r="O643" s="2" t="inlineStr">
+        <is>
+          <t>+351 249 720 290</t>
+        </is>
+      </c>
+      <c r="P643" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q643" s="2" t="inlineStr">
+        <is>
+          <t>509549837</t>
+        </is>
+      </c>
+      <c r="R643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/disalto/</t>
+        </is>
+      </c>
+      <c r="S643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/disaltowines</t>
+        </is>
+      </c>
+      <c r="T643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/disaltowines/</t>
+        </is>
+      </c>
+      <c r="U643" s="2" t="inlineStr"/>
+      <c r="V643" s="2" t="inlineStr"/>
+      <c r="W643" s="2" t="inlineStr">
+        <is>
+          <t>Carla Sequeira</t>
+        </is>
+      </c>
+      <c r="X643" s="2" t="inlineStr">
+        <is>
+          <t>Brand Ambassador</t>
+        </is>
+      </c>
+      <c r="Y643" s="2" t="inlineStr"/>
+      <c r="Z643" s="2" t="inlineStr"/>
+      <c r="AA643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carla-sequeira-254229153/</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>DISALTO - DISTRIBUIÇÃO ALIMENTAR, LDA</t>
+        </is>
+      </c>
+      <c r="B644" s="2" t="inlineStr"/>
+      <c r="C644" s="2" t="inlineStr">
+        <is>
+          <t>168679</t>
+        </is>
+      </c>
+      <c r="D644" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="inlineStr">
+        <is>
+          <t>Entroncamento</t>
+        </is>
+      </c>
+      <c r="F644" s="2" t="inlineStr"/>
+      <c r="G644" s="2" t="inlineStr">
+        <is>
+          <t>Rua Casal Do Melão</t>
+        </is>
+      </c>
+      <c r="H644" s="2" t="inlineStr">
+        <is>
+          <t>2330-106</t>
+        </is>
+      </c>
+      <c r="I644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.disalto.pt</t>
+        </is>
+      </c>
+      <c r="J644" s="2" t="inlineStr"/>
+      <c r="K644" s="2" t="inlineStr"/>
+      <c r="L644" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M644" s="2" t="inlineStr">
+        <is>
+          <t>1438617</t>
+        </is>
+      </c>
+      <c r="N644" s="2" t="inlineStr">
+        <is>
+          <t>comercial@disalto.pt</t>
+        </is>
+      </c>
+      <c r="O644" s="2" t="inlineStr">
+        <is>
+          <t>+351 249 720 290</t>
+        </is>
+      </c>
+      <c r="P644" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q644" s="2" t="inlineStr">
+        <is>
+          <t>509549837</t>
+        </is>
+      </c>
+      <c r="R644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/disalto/</t>
+        </is>
+      </c>
+      <c r="S644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/disaltowines</t>
+        </is>
+      </c>
+      <c r="T644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/disaltowines/</t>
+        </is>
+      </c>
+      <c r="U644" s="2" t="inlineStr"/>
+      <c r="V644" s="2" t="inlineStr"/>
+      <c r="W644" s="2" t="inlineStr">
+        <is>
+          <t>Iolanda Esteves</t>
+        </is>
+      </c>
+      <c r="X644" s="2" t="inlineStr">
+        <is>
+          <t>Brand Representative</t>
+        </is>
+      </c>
+      <c r="Y644" s="2" t="inlineStr"/>
+      <c r="Z644" s="2" t="inlineStr"/>
+      <c r="AA644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/iolanda-esteves-0285b4122/</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>DISALTO - DISTRIBUIÇÃO ALIMENTAR, LDA</t>
+        </is>
+      </c>
+      <c r="B645" s="2" t="inlineStr"/>
+      <c r="C645" s="2" t="inlineStr">
+        <is>
+          <t>168679</t>
+        </is>
+      </c>
+      <c r="D645" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E645" s="2" t="inlineStr">
+        <is>
+          <t>Entroncamento</t>
+        </is>
+      </c>
+      <c r="F645" s="2" t="inlineStr"/>
+      <c r="G645" s="2" t="inlineStr">
+        <is>
+          <t>Rua Casal Do Melão</t>
+        </is>
+      </c>
+      <c r="H645" s="2" t="inlineStr">
+        <is>
+          <t>2330-106</t>
+        </is>
+      </c>
+      <c r="I645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.disalto.pt</t>
+        </is>
+      </c>
+      <c r="J645" s="2" t="inlineStr"/>
+      <c r="K645" s="2" t="inlineStr"/>
+      <c r="L645" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M645" s="2" t="inlineStr">
+        <is>
+          <t>1438617</t>
+        </is>
+      </c>
+      <c r="N645" s="2" t="inlineStr">
+        <is>
+          <t>comercial@disalto.pt</t>
+        </is>
+      </c>
+      <c r="O645" s="2" t="inlineStr">
+        <is>
+          <t>+351 249 720 290</t>
+        </is>
+      </c>
+      <c r="P645" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q645" s="2" t="inlineStr">
+        <is>
+          <t>509549837</t>
+        </is>
+      </c>
+      <c r="R645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/disalto/</t>
+        </is>
+      </c>
+      <c r="S645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/disaltowines</t>
+        </is>
+      </c>
+      <c r="T645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/disaltowines/</t>
+        </is>
+      </c>
+      <c r="U645" s="2" t="inlineStr"/>
+      <c r="V645" s="2" t="inlineStr"/>
+      <c r="W645" s="2" t="inlineStr">
+        <is>
+          <t>João Filipe Neves</t>
+        </is>
+      </c>
+      <c r="X645" s="2" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="Y645" s="2" t="inlineStr"/>
+      <c r="Z645" s="2" t="inlineStr"/>
+      <c r="AA645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jo%C3%A3o-filipe-neves-68167912b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>DISALTO - DISTRIBUIÇÃO ALIMENTAR, LDA</t>
+        </is>
+      </c>
+      <c r="B646" s="2" t="inlineStr"/>
+      <c r="C646" s="2" t="inlineStr">
+        <is>
+          <t>168679</t>
+        </is>
+      </c>
+      <c r="D646" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="inlineStr">
+        <is>
+          <t>Entroncamento</t>
+        </is>
+      </c>
+      <c r="F646" s="2" t="inlineStr"/>
+      <c r="G646" s="2" t="inlineStr">
+        <is>
+          <t>Rua Casal Do Melão</t>
+        </is>
+      </c>
+      <c r="H646" s="2" t="inlineStr">
+        <is>
+          <t>2330-106</t>
+        </is>
+      </c>
+      <c r="I646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.disalto.pt</t>
+        </is>
+      </c>
+      <c r="J646" s="2" t="inlineStr"/>
+      <c r="K646" s="2" t="inlineStr"/>
+      <c r="L646" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M646" s="2" t="inlineStr">
+        <is>
+          <t>1438617</t>
+        </is>
+      </c>
+      <c r="N646" s="2" t="inlineStr">
+        <is>
+          <t>comercial@disalto.pt</t>
+        </is>
+      </c>
+      <c r="O646" s="2" t="inlineStr">
+        <is>
+          <t>+351 249 720 290</t>
+        </is>
+      </c>
+      <c r="P646" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q646" s="2" t="inlineStr">
+        <is>
+          <t>509549837</t>
+        </is>
+      </c>
+      <c r="R646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/disalto/</t>
+        </is>
+      </c>
+      <c r="S646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/disaltowines</t>
+        </is>
+      </c>
+      <c r="T646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/disaltowines/</t>
+        </is>
+      </c>
+      <c r="U646" s="2" t="inlineStr"/>
+      <c r="V646" s="2" t="inlineStr"/>
+      <c r="W646" s="2" t="inlineStr">
+        <is>
+          <t>Sandra Neves</t>
+        </is>
+      </c>
+      <c r="X646" s="2" t="inlineStr">
+        <is>
+          <t>Sales Consultant</t>
+        </is>
+      </c>
+      <c r="Y646" s="2" t="inlineStr"/>
+      <c r="Z646" s="2" t="inlineStr"/>
+      <c r="AA646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sandra-neves-b94810ba/</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>DISALTO - DISTRIBUIÇÃO ALIMENTAR, LDA</t>
+        </is>
+      </c>
+      <c r="B647" s="2" t="inlineStr"/>
+      <c r="C647" s="2" t="inlineStr">
+        <is>
+          <t>168679</t>
+        </is>
+      </c>
+      <c r="D647" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E647" s="2" t="inlineStr">
+        <is>
+          <t>Entroncamento</t>
+        </is>
+      </c>
+      <c r="F647" s="2" t="inlineStr"/>
+      <c r="G647" s="2" t="inlineStr">
+        <is>
+          <t>Rua Casal Do Melão</t>
+        </is>
+      </c>
+      <c r="H647" s="2" t="inlineStr">
+        <is>
+          <t>2330-106</t>
+        </is>
+      </c>
+      <c r="I647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.disalto.pt</t>
+        </is>
+      </c>
+      <c r="J647" s="2" t="inlineStr"/>
+      <c r="K647" s="2" t="inlineStr"/>
+      <c r="L647" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M647" s="2" t="inlineStr">
+        <is>
+          <t>1438617</t>
+        </is>
+      </c>
+      <c r="N647" s="2" t="inlineStr">
+        <is>
+          <t>comercial@disalto.pt</t>
+        </is>
+      </c>
+      <c r="O647" s="2" t="inlineStr">
+        <is>
+          <t>+351 249 720 290</t>
+        </is>
+      </c>
+      <c r="P647" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q647" s="2" t="inlineStr">
+        <is>
+          <t>509549837</t>
+        </is>
+      </c>
+      <c r="R647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/disalto/</t>
+        </is>
+      </c>
+      <c r="S647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/disaltowines</t>
+        </is>
+      </c>
+      <c r="T647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/disaltowines/</t>
+        </is>
+      </c>
+      <c r="U647" s="2" t="inlineStr"/>
+      <c r="V647" s="2" t="inlineStr"/>
+      <c r="W647" s="2" t="inlineStr">
+        <is>
+          <t>Ricardo Nogueira</t>
+        </is>
+      </c>
+      <c r="X647" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y647" s="2" t="inlineStr"/>
+      <c r="Z647" s="2" t="inlineStr"/>
+      <c r="AA647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ricardo-nogueira-53a22a346/</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>MONDOROSO - IMPORT EXPORT, LDA</t>
+        </is>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>MONDOROSO</t>
+        </is>
+      </c>
+      <c r="C648" s="2" t="inlineStr">
+        <is>
+          <t>168678</t>
+        </is>
+      </c>
+      <c r="D648" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E648" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F648" s="2" t="inlineStr"/>
+      <c r="G648" s="2" t="inlineStr">
+        <is>
+          <t>Rua Professor Alfredo De Sousa, 6A</t>
+        </is>
+      </c>
+      <c r="H648" s="2" t="inlineStr">
+        <is>
+          <t>1600-188</t>
+        </is>
+      </c>
+      <c r="I648" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mondoroso.com</t>
+        </is>
+      </c>
+      <c r="J648" s="2" t="inlineStr"/>
+      <c r="K648" s="2" t="inlineStr"/>
+      <c r="L648" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M648" s="2" t="inlineStr">
+        <is>
+          <t>671561</t>
+        </is>
+      </c>
+      <c r="N648" s="2" t="inlineStr">
+        <is>
+          <t>roso@mondoroso.com</t>
+        </is>
+      </c>
+      <c r="O648" s="2" t="inlineStr"/>
+      <c r="P648" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q648" s="2" t="inlineStr">
+        <is>
+          <t>518648737</t>
+        </is>
+      </c>
+      <c r="R648" s="2" t="inlineStr"/>
+      <c r="S648" s="2" t="inlineStr"/>
+      <c r="T648" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mondo_roso/</t>
+        </is>
+      </c>
+      <c r="U648" s="2" t="inlineStr"/>
+      <c r="V648" s="2" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/UCqfYIV1bMAFBclBpAIjA6_g/videos/upload?filter=%5B%5D&amp;sort=%7B%22columnType%22%3A%22date%22%2C%22sortOrder%22%3A%22DESCENDING%22%7D</t>
+        </is>
+      </c>
+      <c r="W648" s="2" t="inlineStr"/>
+      <c r="X648" s="2" t="inlineStr"/>
+      <c r="Y648" s="2" t="inlineStr"/>
+      <c r="Z648" s="2" t="inlineStr"/>
+      <c r="AA648" s="2" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="inlineStr">
+        <is>
+          <t>PLANETA AMISTOSO, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B649" s="2" t="inlineStr">
+        <is>
+          <t>Tonsai Mercearia Bio</t>
+        </is>
+      </c>
+      <c r="C649" s="2" t="inlineStr">
+        <is>
+          <t>168677</t>
+        </is>
+      </c>
+      <c r="D649" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E649" s="2" t="inlineStr">
+        <is>
+          <t>Fátima</t>
+        </is>
+      </c>
+      <c r="F649" s="2" t="inlineStr"/>
+      <c r="G649" s="2" t="inlineStr">
+        <is>
+          <t>Rua Tenente Santana Lopes, Edifício Concorde Bloco B 4º Porta 5</t>
+        </is>
+      </c>
+      <c r="H649" s="2" t="inlineStr">
+        <is>
+          <t>2495-414</t>
+        </is>
+      </c>
+      <c r="I649" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tonsai.pt</t>
+        </is>
+      </c>
+      <c r="J649" s="2" t="inlineStr"/>
+      <c r="K649" s="2" t="inlineStr"/>
+      <c r="L649" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M649" s="2" t="inlineStr">
+        <is>
+          <t>355306</t>
+        </is>
+      </c>
+      <c r="N649" s="2" t="inlineStr">
+        <is>
+          <t>encomendas@tonsai.pt</t>
+        </is>
+      </c>
+      <c r="O649" s="2" t="inlineStr">
+        <is>
+          <t>+351 249 144 280</t>
+        </is>
+      </c>
+      <c r="P649" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q649" s="2" t="inlineStr">
+        <is>
+          <t>513459138</t>
+        </is>
+      </c>
+      <c r="R649" s="2" t="inlineStr"/>
+      <c r="S649" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/tonsai.bio/?locale=pt_PT</t>
+        </is>
+      </c>
+      <c r="T649" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tonsai.bio/</t>
+        </is>
+      </c>
+      <c r="U649" s="2" t="inlineStr"/>
+      <c r="V649" s="2" t="inlineStr"/>
+      <c r="W649" s="2" t="inlineStr"/>
+      <c r="X649" s="2" t="inlineStr"/>
+      <c r="Y649" s="2" t="inlineStr"/>
+      <c r="Z649" s="2" t="inlineStr"/>
+      <c r="AA649" s="2" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="inlineStr">
+        <is>
+          <t>MERCEARIA M TORRES, LDA</t>
+        </is>
+      </c>
+      <c r="B650" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mercearia Torres </t>
+        </is>
+      </c>
+      <c r="C650" s="2" t="inlineStr">
+        <is>
+          <t>168676</t>
+        </is>
+      </c>
+      <c r="D650" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E650" s="2" t="inlineStr">
+        <is>
+          <t>Vila Do Conde</t>
+        </is>
+      </c>
+      <c r="F650" s="2" t="inlineStr"/>
+      <c r="G650" s="2" t="inlineStr">
+        <is>
+          <t>Rua Sónia E Robert Delaunay, 125 1ºdto.</t>
+        </is>
+      </c>
+      <c r="H650" s="2" t="inlineStr">
+        <is>
+          <t>4480-838</t>
+        </is>
+      </c>
+      <c r="I650" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mtorresnetwine.com</t>
+        </is>
+      </c>
+      <c r="J650" s="2" t="inlineStr"/>
+      <c r="K650" s="2" t="inlineStr"/>
+      <c r="L650" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M650" s="2" t="inlineStr">
+        <is>
+          <t>37300</t>
+        </is>
+      </c>
+      <c r="N650" s="2" t="inlineStr">
+        <is>
+          <t>info@mtorresnetwine.com</t>
+        </is>
+      </c>
+      <c r="O650" s="2" t="inlineStr"/>
+      <c r="P650" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q650" s="2" t="inlineStr">
+        <is>
+          <t>508877580</t>
+        </is>
+      </c>
+      <c r="R650" s="2" t="inlineStr"/>
+      <c r="S650" s="2" t="inlineStr"/>
+      <c r="T650" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mtorresnetwine/</t>
+        </is>
+      </c>
+      <c r="U650" s="2" t="inlineStr"/>
+      <c r="V650" s="2" t="inlineStr"/>
+      <c r="W650" s="2" t="inlineStr"/>
+      <c r="X650" s="2" t="inlineStr"/>
+      <c r="Y650" s="2" t="inlineStr"/>
+      <c r="Z650" s="2" t="inlineStr"/>
+      <c r="AA650" s="2" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="inlineStr">
+        <is>
+          <t>PETALVELVET, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B651" s="2" t="inlineStr"/>
+      <c r="C651" s="2" t="inlineStr">
+        <is>
+          <t>168675</t>
+        </is>
+      </c>
+      <c r="D651" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E651" s="2" t="inlineStr">
+        <is>
+          <t>Belas</t>
+        </is>
+      </c>
+      <c r="F651" s="2" t="inlineStr"/>
+      <c r="G651" s="2" t="inlineStr">
+        <is>
+          <t>Avenida João De Belas, 37A</t>
+        </is>
+      </c>
+      <c r="H651" s="2" t="inlineStr">
+        <is>
+          <t>2605-203</t>
+        </is>
+      </c>
+      <c r="I651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.petalvelvet.com</t>
+        </is>
+      </c>
+      <c r="J651" s="2" t="inlineStr"/>
+      <c r="K651" s="2" t="inlineStr"/>
+      <c r="L651" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M651" s="2" t="inlineStr">
+        <is>
+          <t>46684349</t>
+        </is>
+      </c>
+      <c r="N651" s="2" t="inlineStr">
+        <is>
+          <t>info@petalvelvet.com</t>
+        </is>
+      </c>
+      <c r="O651" s="2" t="inlineStr"/>
+      <c r="P651" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q651" s="2" t="inlineStr">
+        <is>
+          <t>514762098</t>
+        </is>
+      </c>
+      <c r="R651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/petalvelvet-lda/</t>
+        </is>
+      </c>
+      <c r="S651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sublimepetalvelvet</t>
+        </is>
+      </c>
+      <c r="T651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sublimeurope/</t>
+        </is>
+      </c>
+      <c r="U651" s="2" t="inlineStr"/>
+      <c r="V651" s="2" t="inlineStr"/>
+      <c r="W651" s="2" t="inlineStr"/>
+      <c r="X651" s="2" t="inlineStr"/>
+      <c r="Y651" s="2" t="inlineStr"/>
+      <c r="Z651" s="2" t="inlineStr"/>
+      <c r="AA651" s="2" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>BWT, LDA</t>
+        </is>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
+        <is>
+          <t>Best Wine Team</t>
+        </is>
+      </c>
+      <c r="C652" s="2" t="inlineStr">
+        <is>
+          <t>168674</t>
+        </is>
+      </c>
+      <c r="D652" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E652" s="2" t="inlineStr">
+        <is>
+          <t>Serrazes</t>
+        </is>
+      </c>
+      <c r="F652" s="2" t="inlineStr"/>
+      <c r="G652" s="2" t="inlineStr">
+        <is>
+          <t>Rua Principal, 101</t>
+        </is>
+      </c>
+      <c r="H652" s="2" t="inlineStr">
+        <is>
+          <t>3660-603</t>
+        </is>
+      </c>
+      <c r="I652" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bestwineteam.com</t>
+        </is>
+      </c>
+      <c r="J652" s="2" t="inlineStr"/>
+      <c r="K652" s="2" t="inlineStr"/>
+      <c r="L652" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M652" s="2" t="inlineStr">
+        <is>
+          <t>490141</t>
+        </is>
+      </c>
+      <c r="N652" s="2" t="inlineStr">
+        <is>
+          <t>hello@bestwineteam.pt</t>
+        </is>
+      </c>
+      <c r="O652" s="2" t="inlineStr"/>
+      <c r="P652" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q652" s="2" t="inlineStr">
+        <is>
+          <t>513519807</t>
+        </is>
+      </c>
+      <c r="R652" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/best-wine-team/</t>
+        </is>
+      </c>
+      <c r="S652" s="2" t="inlineStr">
+        <is>
+          <t>https://pt-pt.facebook.com/bestwineteam/</t>
+        </is>
+      </c>
+      <c r="T652" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bestwineteam/</t>
+        </is>
+      </c>
+      <c r="U652" s="2" t="inlineStr"/>
+      <c r="V652" s="2" t="inlineStr"/>
+      <c r="W652" s="2" t="inlineStr">
+        <is>
+          <t>David Codeço</t>
+        </is>
+      </c>
+      <c r="X652" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Managing Director</t>
+        </is>
+      </c>
+      <c r="Y652" s="2" t="inlineStr"/>
+      <c r="Z652" s="2" t="inlineStr"/>
+      <c r="AA652" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-code%C3%A7o-60325a10/</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="inlineStr">
+        <is>
+          <t>BWT, LDA</t>
+        </is>
+      </c>
+      <c r="B653" s="2" t="inlineStr">
+        <is>
+          <t>Best Wine Team</t>
+        </is>
+      </c>
+      <c r="C653" s="2" t="inlineStr">
+        <is>
+          <t>168674</t>
+        </is>
+      </c>
+      <c r="D653" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E653" s="2" t="inlineStr">
+        <is>
+          <t>Serrazes</t>
+        </is>
+      </c>
+      <c r="F653" s="2" t="inlineStr"/>
+      <c r="G653" s="2" t="inlineStr">
+        <is>
+          <t>Rua Principal, 101</t>
+        </is>
+      </c>
+      <c r="H653" s="2" t="inlineStr">
+        <is>
+          <t>3660-603</t>
+        </is>
+      </c>
+      <c r="I653" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bestwineteam.com</t>
+        </is>
+      </c>
+      <c r="J653" s="2" t="inlineStr"/>
+      <c r="K653" s="2" t="inlineStr"/>
+      <c r="L653" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M653" s="2" t="inlineStr">
+        <is>
+          <t>490141</t>
+        </is>
+      </c>
+      <c r="N653" s="2" t="inlineStr">
+        <is>
+          <t>hello@bestwineteam.pt</t>
+        </is>
+      </c>
+      <c r="O653" s="2" t="inlineStr"/>
+      <c r="P653" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q653" s="2" t="inlineStr">
+        <is>
+          <t>513519807</t>
+        </is>
+      </c>
+      <c r="R653" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/best-wine-team/</t>
+        </is>
+      </c>
+      <c r="S653" s="2" t="inlineStr">
+        <is>
+          <t>https://pt-pt.facebook.com/bestwineteam/</t>
+        </is>
+      </c>
+      <c r="T653" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bestwineteam/</t>
+        </is>
+      </c>
+      <c r="U653" s="2" t="inlineStr"/>
+      <c r="V653" s="2" t="inlineStr"/>
+      <c r="W653" s="2" t="inlineStr">
+        <is>
+          <t>Bruno Feliz</t>
+        </is>
+      </c>
+      <c r="X653" s="2" t="inlineStr">
+        <is>
+          <t>Director Comercial</t>
+        </is>
+      </c>
+      <c r="Y653" s="2" t="inlineStr"/>
+      <c r="Z653" s="2" t="inlineStr"/>
+      <c r="AA653" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bruno-feliz-670b96aa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="inlineStr">
+        <is>
+          <t>BATATAS SALEIRO</t>
+        </is>
+      </c>
+      <c r="B654" s="2" t="inlineStr"/>
+      <c r="C654" s="2" t="inlineStr">
+        <is>
+          <t>168673</t>
+        </is>
+      </c>
+      <c r="D654" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E654" s="2" t="inlineStr">
+        <is>
+          <t>Fonte De Angeão</t>
+        </is>
+      </c>
+      <c r="F654" s="2" t="inlineStr"/>
+      <c r="G654" s="2" t="inlineStr">
+        <is>
+          <t>Rua Doutor João Rocha, 55</t>
+        </is>
+      </c>
+      <c r="H654" s="2" t="inlineStr">
+        <is>
+          <t>3840-171</t>
+        </is>
+      </c>
+      <c r="I654" s="2" t="inlineStr">
+        <is>
+          <t>https://www.saleiros.pt</t>
+        </is>
+      </c>
+      <c r="J654" s="2" t="inlineStr"/>
+      <c r="K654" s="2" t="inlineStr"/>
+      <c r="L654" s="2" t="inlineStr"/>
+      <c r="M654" s="2" t="inlineStr">
+        <is>
+          <t>547218</t>
+        </is>
+      </c>
+      <c r="N654" s="2" t="inlineStr">
+        <is>
+          <t>info@saleiros.pt</t>
+        </is>
+      </c>
+      <c r="O654" s="2" t="inlineStr">
+        <is>
+          <t>+351 234 781 971</t>
+        </is>
+      </c>
+      <c r="P654" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q654" s="2" t="inlineStr">
+        <is>
+          <t>193417073</t>
+        </is>
+      </c>
+      <c r="R654" s="2" t="inlineStr"/>
+      <c r="S654" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ossaleirospt</t>
+        </is>
+      </c>
+      <c r="T654" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/os_saleiros/</t>
+        </is>
+      </c>
+      <c r="U654" s="2" t="inlineStr"/>
+      <c r="V654" s="2" t="inlineStr"/>
+      <c r="W654" s="2" t="inlineStr"/>
+      <c r="X654" s="2" t="inlineStr"/>
+      <c r="Y654" s="2" t="inlineStr"/>
+      <c r="Z654" s="2" t="inlineStr"/>
+      <c r="AA654" s="2" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="inlineStr">
+        <is>
+          <t>FERNANDES &amp; PEREIRA, LDA</t>
+        </is>
+      </c>
+      <c r="B655" s="2" t="inlineStr"/>
+      <c r="C655" s="2" t="inlineStr">
+        <is>
+          <t>168672</t>
+        </is>
+      </c>
+      <c r="D655" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E655" s="2" t="inlineStr">
+        <is>
+          <t>Loulé</t>
+        </is>
+      </c>
+      <c r="F655" s="2" t="inlineStr"/>
+      <c r="G655" s="2" t="inlineStr">
+        <is>
+          <t>Rua Afonso De Albuquerque, R/C</t>
+        </is>
+      </c>
+      <c r="H655" s="2" t="inlineStr">
+        <is>
+          <t>8100-532</t>
+        </is>
+      </c>
+      <c r="I655" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fernandespereira.pt</t>
+        </is>
+      </c>
+      <c r="J655" s="2" t="inlineStr"/>
+      <c r="K655" s="2" t="inlineStr"/>
+      <c r="L655" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M655" s="2" t="inlineStr">
+        <is>
+          <t>820815</t>
+        </is>
+      </c>
+      <c r="N655" s="2" t="inlineStr">
+        <is>
+          <t>fpereira@fpereira.pt</t>
+        </is>
+      </c>
+      <c r="O655" s="2" t="inlineStr">
+        <is>
+          <t>+351 289 462 893</t>
+        </is>
+      </c>
+      <c r="P655" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="Q655" s="2" t="inlineStr">
+        <is>
+          <t>500753520</t>
+        </is>
+      </c>
+      <c r="R655" s="2" t="inlineStr"/>
+      <c r="S655" s="2" t="inlineStr"/>
+      <c r="T655" s="2" t="inlineStr"/>
+      <c r="U655" s="2" t="inlineStr"/>
+      <c r="V655" s="2" t="inlineStr"/>
+      <c r="W655" s="2" t="inlineStr"/>
+      <c r="X655" s="2" t="inlineStr"/>
+      <c r="Y655" s="2" t="inlineStr"/>
+      <c r="Z655" s="2" t="inlineStr"/>
+      <c r="AA655" s="2" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="inlineStr">
+        <is>
+          <t>COOLCHOICE - COMÉRCIO ALIMENTAR, LDA</t>
+        </is>
+      </c>
+      <c r="B656" s="2" t="inlineStr">
+        <is>
+          <t>Coolchoice Premium Foods</t>
+        </is>
+      </c>
+      <c r="C656" s="2" t="inlineStr">
+        <is>
+          <t>168670</t>
+        </is>
+      </c>
+      <c r="D656" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E656" s="2" t="inlineStr">
+        <is>
+          <t>Almancil</t>
+        </is>
+      </c>
+      <c r="F656" s="2" t="inlineStr"/>
+      <c r="G656" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cristóvão Pires Norte, 141 2ºdto.</t>
+        </is>
+      </c>
+      <c r="H656" s="2" t="inlineStr">
+        <is>
+          <t>8135-117</t>
+        </is>
+      </c>
+      <c r="I656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.coolchoice.pt</t>
+        </is>
+      </c>
+      <c r="J656" s="2" t="inlineStr"/>
+      <c r="K656" s="2" t="inlineStr"/>
+      <c r="L656" s="2" t="inlineStr"/>
+      <c r="M656" s="2" t="inlineStr">
+        <is>
+          <t>1132283</t>
+        </is>
+      </c>
+      <c r="N656" s="2" t="inlineStr">
+        <is>
+          <t>geral@coolchoice.pt</t>
+        </is>
+      </c>
+      <c r="O656" s="2" t="inlineStr"/>
+      <c r="P656" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q656" s="2" t="inlineStr">
+        <is>
+          <t>509375111</t>
+        </is>
+      </c>
+      <c r="R656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/coolchoice-lda/</t>
+        </is>
+      </c>
+      <c r="S656" s="2" t="inlineStr"/>
+      <c r="T656" s="2" t="inlineStr"/>
+      <c r="U656" s="2" t="inlineStr"/>
+      <c r="V656" s="2" t="inlineStr"/>
+      <c r="W656" s="2" t="inlineStr">
+        <is>
+          <t>Cédric Marcelino</t>
+        </is>
+      </c>
+      <c r="X656" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y656" s="2" t="inlineStr"/>
+      <c r="Z656" s="2" t="inlineStr"/>
+      <c r="AA656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/c%C3%A9dric-marcelino-938908228/</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="inlineStr">
+        <is>
+          <t>WAVEPOWER, LDA</t>
+        </is>
+      </c>
+      <c r="B657" s="2" t="inlineStr">
+        <is>
+          <t>GB SUPER STORE</t>
+        </is>
+      </c>
+      <c r="C657" s="2" t="inlineStr">
+        <is>
+          <t>168669</t>
+        </is>
+      </c>
+      <c r="D657" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E657" s="2" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="F657" s="2" t="inlineStr"/>
+      <c r="G657" s="2" t="inlineStr">
+        <is>
+          <t>Rua Monte Leite, Bloco A 3 R/C Dto.</t>
+        </is>
+      </c>
+      <c r="H657" s="2" t="inlineStr">
+        <is>
+          <t>2765-496</t>
+        </is>
+      </c>
+      <c r="I657" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gb-superstore.pt</t>
+        </is>
+      </c>
+      <c r="J657" s="2" t="inlineStr"/>
+      <c r="K657" s="2" t="inlineStr"/>
+      <c r="L657" s="2" t="inlineStr"/>
+      <c r="M657" s="2" t="inlineStr">
+        <is>
+          <t>570837</t>
+        </is>
+      </c>
+      <c r="N657" s="2" t="inlineStr">
+        <is>
+          <t>gbstore.cascais@gmail.com</t>
+        </is>
+      </c>
+      <c r="O657" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 466 2453</t>
+        </is>
+      </c>
+      <c r="P657" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q657" s="2" t="inlineStr">
+        <is>
+          <t>508415837</t>
+        </is>
+      </c>
+      <c r="R657" s="2" t="inlineStr"/>
+      <c r="S657" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gbstore.cascais/</t>
+        </is>
+      </c>
+      <c r="T657" s="2" t="inlineStr"/>
+      <c r="U657" s="2" t="inlineStr"/>
+      <c r="V657" s="2" t="inlineStr"/>
+      <c r="W657" s="2" t="inlineStr"/>
+      <c r="X657" s="2" t="inlineStr"/>
+      <c r="Y657" s="2" t="inlineStr"/>
+      <c r="Z657" s="2" t="inlineStr"/>
+      <c r="AA657" s="2" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="inlineStr">
+        <is>
+          <t>ALVES DA SILVA, TEIXEIRA &amp; CUNHA, LDA</t>
+        </is>
+      </c>
+      <c r="B658" s="2" t="inlineStr">
+        <is>
+          <t>CASA LOURENÇO</t>
+        </is>
+      </c>
+      <c r="C658" s="2" t="inlineStr">
+        <is>
+          <t>168665</t>
+        </is>
+      </c>
+      <c r="D658" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E658" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F658" s="2" t="inlineStr"/>
+      <c r="G658" s="2" t="inlineStr">
+        <is>
+          <t>Rua Do Bonjardim, 417</t>
+        </is>
+      </c>
+      <c r="H658" s="2" t="inlineStr">
+        <is>
+          <t>4000-125</t>
+        </is>
+      </c>
+      <c r="I658" s="2" t="inlineStr">
+        <is>
+          <t>https://www.casalourenco.com.pt</t>
+        </is>
+      </c>
+      <c r="J658" s="2" t="inlineStr"/>
+      <c r="K658" s="2" t="inlineStr"/>
+      <c r="L658" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M658" s="2" t="inlineStr">
+        <is>
+          <t>447760</t>
+        </is>
+      </c>
+      <c r="N658" s="2" t="inlineStr">
+        <is>
+          <t>clqueijaria@hotmail.com</t>
+        </is>
+      </c>
+      <c r="O658" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 200 6462</t>
+        </is>
+      </c>
+      <c r="P658" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="Q658" s="2" t="inlineStr">
+        <is>
+          <t>501432060</t>
+        </is>
+      </c>
+      <c r="R658" s="2" t="inlineStr"/>
+      <c r="S658" s="2" t="inlineStr"/>
+      <c r="T658" s="2" t="inlineStr"/>
+      <c r="U658" s="2" t="inlineStr"/>
+      <c r="V658" s="2" t="inlineStr"/>
+      <c r="W658" s="2" t="inlineStr">
+        <is>
+          <t>João Alves da Cunha</t>
+        </is>
+      </c>
+      <c r="X658" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y658" s="2" t="inlineStr"/>
+      <c r="Z658" s="2" t="inlineStr"/>
+      <c r="AA658" s="2" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="inlineStr">
+        <is>
+          <t>TALHO DO TÚNEL - SOCIEDADE UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B659" s="2" t="inlineStr">
+        <is>
+          <t>Talho do Tunel</t>
+        </is>
+      </c>
+      <c r="C659" s="2" t="inlineStr">
+        <is>
+          <t>168664</t>
+        </is>
+      </c>
+      <c r="D659" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E659" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F659" s="2" t="inlineStr"/>
+      <c r="G659" s="2" t="inlineStr">
+        <is>
+          <t>Rua Cândida Sá De Albergaria, 202/204</t>
+        </is>
+      </c>
+      <c r="H659" s="2" t="inlineStr">
+        <is>
+          <t>4150-183</t>
+        </is>
+      </c>
+      <c r="I659" s="2" t="inlineStr">
+        <is>
+          <t>https://www.talhodotunel.pt</t>
+        </is>
+      </c>
+      <c r="J659" s="2" t="inlineStr"/>
+      <c r="K659" s="2" t="inlineStr"/>
+      <c r="L659" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M659" s="2" t="inlineStr">
+        <is>
+          <t>473506</t>
+        </is>
+      </c>
+      <c r="N659" s="2" t="inlineStr">
+        <is>
+          <t>talhodotunel@sapo.pt</t>
+        </is>
+      </c>
+      <c r="O659" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 618 0071</t>
+        </is>
+      </c>
+      <c r="P659" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q659" s="2" t="inlineStr">
+        <is>
+          <t>509261876</t>
+        </is>
+      </c>
+      <c r="R659" s="2" t="inlineStr"/>
+      <c r="S659" s="2" t="inlineStr"/>
+      <c r="T659" s="2" t="inlineStr"/>
+      <c r="U659" s="2" t="inlineStr"/>
+      <c r="V659" s="2" t="inlineStr"/>
+      <c r="W659" s="2" t="inlineStr">
+        <is>
+          <t>José Nunes Pinto da Silva</t>
+        </is>
+      </c>
+      <c r="X659" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y659" s="2" t="inlineStr"/>
+      <c r="Z659" s="2" t="inlineStr"/>
+      <c r="AA659" s="2" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="inlineStr">
+        <is>
+          <t>CARNES SABOROSAS, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B660" s="2" t="inlineStr">
+        <is>
+          <t>TALHO CONFIANÇA</t>
+        </is>
+      </c>
+      <c r="C660" s="2" t="inlineStr">
+        <is>
+          <t>168663</t>
+        </is>
+      </c>
+      <c r="D660" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E660" s="2" t="inlineStr">
+        <is>
+          <t>Mogadouro</t>
+        </is>
+      </c>
+      <c r="F660" s="2" t="inlineStr"/>
+      <c r="G660" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Do Sabor, 18 R/C Dto.</t>
+        </is>
+      </c>
+      <c r="H660" s="2" t="inlineStr">
+        <is>
+          <t>5200-288</t>
+        </is>
+      </c>
+      <c r="I660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.talhosconfianca.pt</t>
+        </is>
+      </c>
+      <c r="J660" s="2" t="inlineStr"/>
+      <c r="K660" s="2" t="inlineStr"/>
+      <c r="L660" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M660" s="2" t="inlineStr">
+        <is>
+          <t>1782565</t>
+        </is>
+      </c>
+      <c r="N660" s="2" t="inlineStr">
+        <is>
+          <t>geral@talhosconfianca.pt</t>
+        </is>
+      </c>
+      <c r="O660" s="2" t="inlineStr">
+        <is>
+          <t>+351 279 341 267</t>
+        </is>
+      </c>
+      <c r="P660" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q660" s="2" t="inlineStr">
+        <is>
+          <t>515938912</t>
+        </is>
+      </c>
+      <c r="R660" s="2" t="inlineStr"/>
+      <c r="S660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/talhosconfianca</t>
+        </is>
+      </c>
+      <c r="T660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/talhos.confianca/</t>
+        </is>
+      </c>
+      <c r="U660" s="2" t="inlineStr"/>
+      <c r="V660" s="2" t="inlineStr"/>
+      <c r="W660" s="2" t="inlineStr"/>
+      <c r="X660" s="2" t="inlineStr"/>
+      <c r="Y660" s="2" t="inlineStr"/>
+      <c r="Z660" s="2" t="inlineStr"/>
+      <c r="AA660" s="2" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="inlineStr">
+        <is>
+          <t>GAPO VAG, LDA</t>
+        </is>
+      </c>
+      <c r="B661" s="2" t="inlineStr"/>
+      <c r="C661" s="2" t="inlineStr">
+        <is>
+          <t>168662</t>
+        </is>
+      </c>
+      <c r="D661" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E661" s="2" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="F661" s="2" t="inlineStr"/>
+      <c r="G661" s="2" t="inlineStr">
+        <is>
+          <t>Rua António Rodrigues Oliveira, 10/12 Fração I</t>
+        </is>
+      </c>
+      <c r="H661" s="2" t="inlineStr">
+        <is>
+          <t>3800-043</t>
+        </is>
+      </c>
+      <c r="I661" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gapo.pt</t>
+        </is>
+      </c>
+      <c r="J661" s="2" t="inlineStr"/>
+      <c r="K661" s="2" t="inlineStr"/>
+      <c r="L661" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M661" s="2" t="inlineStr">
+        <is>
+          <t>3325625</t>
+        </is>
+      </c>
+      <c r="N661" s="2" t="inlineStr">
+        <is>
+          <t>geral@gapo.pt</t>
+        </is>
+      </c>
+      <c r="O661" s="2" t="inlineStr">
+        <is>
+          <t>+351 234 109 406</t>
+        </is>
+      </c>
+      <c r="P661" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q661" s="2" t="inlineStr">
+        <is>
+          <t>513048456</t>
+        </is>
+      </c>
+      <c r="R661" s="2" t="inlineStr"/>
+      <c r="S661" s="2" t="inlineStr"/>
+      <c r="T661" s="2" t="inlineStr"/>
+      <c r="U661" s="2" t="inlineStr"/>
+      <c r="V661" s="2" t="inlineStr"/>
+      <c r="W661" s="2" t="inlineStr">
+        <is>
+          <t>Goncalo Valdez Vicente</t>
+        </is>
+      </c>
+      <c r="X661" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y661" s="2" t="inlineStr"/>
+      <c r="Z661" s="2" t="inlineStr"/>
+      <c r="AA661" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/goncalo-valdez-vicente-37b04916/</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="inlineStr">
+        <is>
+          <t>CAULIS, LOJA DAS COUVES E PRODUTOS REGIONAIS, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B662" s="2" t="inlineStr">
+        <is>
+          <t>Loja das Couves</t>
+        </is>
+      </c>
+      <c r="C662" s="2" t="inlineStr">
+        <is>
+          <t>168661</t>
+        </is>
+      </c>
+      <c r="D662" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E662" s="2" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F662" s="2" t="inlineStr"/>
+      <c r="G662" s="2" t="inlineStr">
+        <is>
+          <t>Praça Doutor Francisco Araújo Malheiro, 88</t>
+        </is>
+      </c>
+      <c r="H662" s="2" t="inlineStr">
+        <is>
+          <t>4715-016</t>
+        </is>
+      </c>
+      <c r="I662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lojadascouves.pt</t>
+        </is>
+      </c>
+      <c r="J662" s="2" t="inlineStr"/>
+      <c r="K662" s="2" t="inlineStr"/>
+      <c r="L662" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M662" s="2" t="inlineStr">
+        <is>
+          <t>147139</t>
+        </is>
+      </c>
+      <c r="N662" s="2" t="inlineStr">
+        <is>
+          <t>correio@lojadascouves.pt</t>
+        </is>
+      </c>
+      <c r="O662" s="2" t="inlineStr"/>
+      <c r="P662" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q662" s="2" t="inlineStr">
+        <is>
+          <t>516038290</t>
+        </is>
+      </c>
+      <c r="R662" s="2" t="inlineStr"/>
+      <c r="S662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lojadascouves/</t>
+        </is>
+      </c>
+      <c r="T662" s="2" t="inlineStr"/>
+      <c r="U662" s="2" t="inlineStr"/>
+      <c r="V662" s="2" t="inlineStr"/>
+      <c r="W662" s="2" t="inlineStr">
+        <is>
+          <t>Débora Raquel Samba Pereira</t>
+        </is>
+      </c>
+      <c r="X662" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y662" s="2" t="inlineStr"/>
+      <c r="Z662" s="2" t="inlineStr"/>
+      <c r="AA662" s="2" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="inlineStr">
+        <is>
+          <t>ATLASGATE, LDA</t>
+        </is>
+      </c>
+      <c r="B663" s="2" t="inlineStr"/>
+      <c r="C663" s="2" t="inlineStr">
+        <is>
+          <t>168660</t>
+        </is>
+      </c>
+      <c r="D663" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E663" s="2" t="inlineStr">
+        <is>
+          <t>Barcelos</t>
+        </is>
+      </c>
+      <c r="F663" s="2" t="inlineStr"/>
+      <c r="G663" s="2" t="inlineStr">
+        <is>
+          <t>Avenida De São José, 380</t>
+        </is>
+      </c>
+      <c r="H663" s="2" t="inlineStr">
+        <is>
+          <t>4750-307</t>
+        </is>
+      </c>
+      <c r="I663" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atlasgatedistribution.com</t>
+        </is>
+      </c>
+      <c r="J663" s="2" t="inlineStr"/>
+      <c r="K663" s="2" t="inlineStr"/>
+      <c r="L663" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M663" s="2" t="inlineStr">
+        <is>
+          <t>27693</t>
+        </is>
+      </c>
+      <c r="N663" s="2" t="inlineStr">
+        <is>
+          <t>info@atlasgatedistribution.com</t>
+        </is>
+      </c>
+      <c r="O663" s="2" t="inlineStr"/>
+      <c r="P663" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q663" s="2" t="inlineStr">
+        <is>
+          <t>519047036</t>
+        </is>
+      </c>
+      <c r="R663" s="2" t="inlineStr"/>
+      <c r="S663" s="2" t="inlineStr"/>
+      <c r="T663" s="2" t="inlineStr"/>
+      <c r="U663" s="2" t="inlineStr"/>
+      <c r="V663" s="2" t="inlineStr"/>
+      <c r="W663" s="2" t="inlineStr">
+        <is>
+          <t>Carla Maria Lima Vasconcelos</t>
+        </is>
+      </c>
+      <c r="X663" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y663" s="2" t="inlineStr"/>
+      <c r="Z663" s="2" t="inlineStr"/>
+      <c r="AA663" s="2" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="inlineStr">
+        <is>
+          <t>RUI REIS FERREIRA, LDA</t>
+        </is>
+      </c>
+      <c r="B664" s="2" t="inlineStr">
+        <is>
+          <t>SABORES MONÁSTICOS</t>
+        </is>
+      </c>
+      <c r="C664" s="2" t="inlineStr">
+        <is>
+          <t>168659</t>
+        </is>
+      </c>
+      <c r="D664" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E664" s="2" t="inlineStr">
+        <is>
+          <t>Salzedas</t>
+        </is>
+      </c>
+      <c r="F664" s="2" t="inlineStr"/>
+      <c r="G664" s="2" t="inlineStr">
+        <is>
+          <t>Rua Da Ramada, 16</t>
+        </is>
+      </c>
+      <c r="H664" s="2" t="inlineStr">
+        <is>
+          <t>3610-073</t>
+        </is>
+      </c>
+      <c r="I664" s="2" t="inlineStr">
+        <is>
+          <t>https://www.saboresmonasticos.pt</t>
+        </is>
+      </c>
+      <c r="J664" s="2" t="inlineStr"/>
+      <c r="K664" s="2" t="inlineStr"/>
+      <c r="L664" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M664" s="2" t="inlineStr">
+        <is>
+          <t>235142</t>
+        </is>
+      </c>
+      <c r="N664" s="2" t="inlineStr">
+        <is>
+          <t>geral@saboresmonasticos.pt</t>
+        </is>
+      </c>
+      <c r="O664" s="2" t="inlineStr"/>
+      <c r="P664" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q664" s="2" t="inlineStr">
+        <is>
+          <t>510898033</t>
+        </is>
+      </c>
+      <c r="R664" s="2" t="inlineStr"/>
+      <c r="S664" s="2" t="inlineStr"/>
+      <c r="T664" s="2" t="inlineStr"/>
+      <c r="U664" s="2" t="inlineStr"/>
+      <c r="V664" s="2" t="inlineStr"/>
+      <c r="W664" s="2" t="inlineStr">
+        <is>
+          <t>Rui Ferreira</t>
+        </is>
+      </c>
+      <c r="X664" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y664" s="2" t="inlineStr"/>
+      <c r="Z664" s="2" t="inlineStr"/>
+      <c r="AA664" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sabores-monasticos-rui-ferreira-57b897112/</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="inlineStr">
+        <is>
+          <t>CASA DOS VINHOS 14 REGIÕES, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B665" s="2" t="inlineStr"/>
+      <c r="C665" s="2" t="inlineStr">
+        <is>
+          <t>168658</t>
+        </is>
+      </c>
+      <c r="D665" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E665" s="2" t="inlineStr">
+        <is>
+          <t>Maceira Lra</t>
+        </is>
+      </c>
+      <c r="F665" s="2" t="inlineStr"/>
+      <c r="G665" s="2" t="inlineStr">
+        <is>
+          <t>Estrada Nacional 356, 2</t>
+        </is>
+      </c>
+      <c r="H665" s="2" t="inlineStr">
+        <is>
+          <t>2405-026</t>
+        </is>
+      </c>
+      <c r="I665" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinhos14regioes.pt</t>
+        </is>
+      </c>
+      <c r="J665" s="2" t="inlineStr"/>
+      <c r="K665" s="2" t="inlineStr"/>
+      <c r="L665" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M665" s="2" t="inlineStr">
+        <is>
+          <t>152443</t>
+        </is>
+      </c>
+      <c r="N665" s="2" t="inlineStr">
+        <is>
+          <t>geral@vinhos14regioes.pt</t>
+        </is>
+      </c>
+      <c r="O665" s="2" t="inlineStr">
+        <is>
+          <t>+351 244 776 311</t>
+        </is>
+      </c>
+      <c r="P665" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q665" s="2" t="inlineStr">
+        <is>
+          <t>516985051</t>
+        </is>
+      </c>
+      <c r="R665" s="2" t="inlineStr"/>
+      <c r="S665" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinhos14Regioes</t>
+        </is>
+      </c>
+      <c r="T665" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinhos14regioes/</t>
+        </is>
+      </c>
+      <c r="U665" s="2" t="inlineStr"/>
+      <c r="V665" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCc0NWKrpTRXF8Pz_toH6g2Q</t>
+        </is>
+      </c>
+      <c r="W665" s="2" t="inlineStr">
+        <is>
+          <t>Belisa Cordeiro</t>
+        </is>
+      </c>
+      <c r="X665" s="2" t="inlineStr">
+        <is>
+          <t>Sales Department</t>
+        </is>
+      </c>
+      <c r="Y665" s="2" t="inlineStr"/>
+      <c r="Z665" s="2" t="inlineStr"/>
+      <c r="AA665" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/belisa-cordeiro-3316ba8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="inlineStr">
+        <is>
+          <t>MANUEL A.M.ALMEIDA, LDA</t>
+        </is>
+      </c>
+      <c r="B666" s="2" t="inlineStr"/>
+      <c r="C666" s="2" t="inlineStr">
+        <is>
+          <t>168657</t>
+        </is>
+      </c>
+      <c r="D666" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E666" s="2" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F666" s="2" t="inlineStr"/>
+      <c r="G666" s="2" t="inlineStr">
+        <is>
+          <t>Rua Zona Industrial 2ª Fase, Pavilhão 12</t>
+        </is>
+      </c>
+      <c r="H666" s="2" t="inlineStr">
+        <is>
+          <t>4935-250</t>
+        </is>
+      </c>
+      <c r="I666" s="2" t="inlineStr">
+        <is>
+          <t>https://www.garrafeiramanuelalmeida.pt</t>
+        </is>
+      </c>
+      <c r="J666" s="2" t="inlineStr"/>
+      <c r="K666" s="2" t="inlineStr"/>
+      <c r="L666" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M666" s="2" t="inlineStr">
+        <is>
+          <t>825002</t>
+        </is>
+      </c>
+      <c r="N666" s="2" t="inlineStr">
+        <is>
+          <t>m.almeida.lda@sapo.pt</t>
+        </is>
+      </c>
+      <c r="O666" s="2" t="inlineStr"/>
+      <c r="P666" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q666" s="2" t="inlineStr">
+        <is>
+          <t>506726630</t>
+        </is>
+      </c>
+      <c r="R666" s="2" t="inlineStr"/>
+      <c r="S666" s="2" t="inlineStr"/>
+      <c r="T666" s="2" t="inlineStr"/>
+      <c r="U666" s="2" t="inlineStr"/>
+      <c r="V666" s="2" t="inlineStr"/>
+      <c r="W666" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Almeida</t>
+        </is>
+      </c>
+      <c r="X666" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y666" s="2" t="inlineStr"/>
+      <c r="Z666" s="2" t="inlineStr"/>
+      <c r="AA666" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manuel-almeida-bbaa477b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="inlineStr">
+        <is>
+          <t>ARINTOURIGA, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B667" s="2" t="inlineStr"/>
+      <c r="C667" s="2" t="inlineStr">
+        <is>
+          <t>168656</t>
+        </is>
+      </c>
+      <c r="D667" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E667" s="2" t="inlineStr">
+        <is>
+          <t>Santarém</t>
+        </is>
+      </c>
+      <c r="F667" s="2" t="inlineStr"/>
+      <c r="G667" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Dom Afonso Henriques, 57 R/C</t>
+        </is>
+      </c>
+      <c r="H667" s="2" t="inlineStr">
+        <is>
+          <t>2000-179</t>
+        </is>
+      </c>
+      <c r="I667" s="2" t="inlineStr">
+        <is>
+          <t>https://www.arintoetouriga.pt</t>
+        </is>
+      </c>
+      <c r="J667" s="2" t="inlineStr"/>
+      <c r="K667" s="2" t="inlineStr"/>
+      <c r="L667" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M667" s="2" t="inlineStr">
+        <is>
+          <t>324483</t>
+        </is>
+      </c>
+      <c r="N667" s="2" t="inlineStr">
+        <is>
+          <t>garrafeira@arintoetouriga.pt</t>
+        </is>
+      </c>
+      <c r="O667" s="2" t="inlineStr">
+        <is>
+          <t>+351 243 110 230</t>
+        </is>
+      </c>
+      <c r="P667" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q667" s="2" t="inlineStr">
+        <is>
+          <t>517858770</t>
+        </is>
+      </c>
+      <c r="R667" s="2" t="inlineStr"/>
+      <c r="S667" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61561087984399</t>
+        </is>
+      </c>
+      <c r="T667" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/arintoetourigabyrenata</t>
+        </is>
+      </c>
+      <c r="U667" s="2" t="inlineStr"/>
+      <c r="V667" s="2" t="inlineStr"/>
+      <c r="W667" s="2" t="inlineStr">
+        <is>
+          <t>Renata Abreu</t>
+        </is>
+      </c>
+      <c r="X667" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y667" s="2" t="inlineStr"/>
+      <c r="Z667" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA667" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/renata-abreu-0b35359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="inlineStr">
+        <is>
+          <t>BIOCABAZ, LDA</t>
+        </is>
+      </c>
+      <c r="B668" s="2" t="inlineStr"/>
+      <c r="C668" s="2" t="inlineStr">
+        <is>
+          <t>168655</t>
+        </is>
+      </c>
+      <c r="D668" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E668" s="2" t="inlineStr">
+        <is>
+          <t>Carcavelos</t>
+        </is>
+      </c>
+      <c r="F668" s="2" t="inlineStr"/>
+      <c r="G668" s="2" t="inlineStr">
+        <is>
+          <t>Avenida De Portugal, 277 2ºdto.</t>
+        </is>
+      </c>
+      <c r="H668" s="2" t="inlineStr">
+        <is>
+          <t>2775-396</t>
+        </is>
+      </c>
+      <c r="I668" s="2" t="inlineStr">
+        <is>
+          <t>https://www.biocabaz.pt</t>
+        </is>
+      </c>
+      <c r="J668" s="2" t="inlineStr"/>
+      <c r="K668" s="2" t="inlineStr"/>
+      <c r="L668" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M668" s="2" t="inlineStr">
+        <is>
+          <t>418888</t>
+        </is>
+      </c>
+      <c r="N668" s="2" t="inlineStr">
+        <is>
+          <t>geral@biocabaz.pt</t>
+        </is>
+      </c>
+      <c r="O668" s="2" t="inlineStr"/>
+      <c r="P668" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q668" s="2" t="inlineStr">
+        <is>
+          <t>513800182</t>
+        </is>
+      </c>
+      <c r="R668" s="2" t="inlineStr"/>
+      <c r="S668" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/www.biocabaz.pt</t>
+        </is>
+      </c>
+      <c r="T668" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/biocabaz/</t>
+        </is>
+      </c>
+      <c r="U668" s="2" t="inlineStr"/>
+      <c r="V668" s="2" t="inlineStr"/>
+      <c r="W668" s="2" t="inlineStr">
+        <is>
+          <t>Sónia Alexandra Dias Vermelhudo</t>
+        </is>
+      </c>
+      <c r="X668" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y668" s="2" t="inlineStr"/>
+      <c r="Z668" s="2" t="inlineStr"/>
+      <c r="AA668" s="2" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="inlineStr">
+        <is>
+          <t>DAPAVAL - DISTRIBUIDORA DE PRODUTOS ALIMENTARES, AZEITES E REFRIGERANTES, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B669" s="2" t="inlineStr"/>
+      <c r="C669" s="2" t="inlineStr">
+        <is>
+          <t>168654</t>
+        </is>
+      </c>
+      <c r="D669" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E669" s="2" t="inlineStr">
+        <is>
+          <t>Figueira Da Foz</t>
+        </is>
+      </c>
+      <c r="F669" s="2" t="inlineStr"/>
+      <c r="G669" s="2" t="inlineStr">
+        <is>
+          <t>Rua Doutor Duarte Silva, 69/71</t>
+        </is>
+      </c>
+      <c r="H669" s="2" t="inlineStr">
+        <is>
+          <t>3080-040</t>
+        </is>
+      </c>
+      <c r="I669" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dapaval.pt</t>
+        </is>
+      </c>
+      <c r="J669" s="2" t="inlineStr"/>
+      <c r="K669" s="2" t="inlineStr"/>
+      <c r="L669" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M669" s="2" t="inlineStr">
+        <is>
+          <t>259862</t>
+        </is>
+      </c>
+      <c r="N669" s="2" t="inlineStr">
+        <is>
+          <t>geral@dapaval.pt</t>
+        </is>
+      </c>
+      <c r="O669" s="2" t="inlineStr">
+        <is>
+          <t>+351 233 422 794</t>
+        </is>
+      </c>
+      <c r="P669" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="Q669" s="2" t="inlineStr">
+        <is>
+          <t>501476792</t>
+        </is>
+      </c>
+      <c r="R669" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dapaval/</t>
+        </is>
+      </c>
+      <c r="S669" s="2" t="inlineStr"/>
+      <c r="T669" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lojasolengarrafado/?hl=en</t>
+        </is>
+      </c>
+      <c r="U669" s="2" t="inlineStr"/>
+      <c r="V669" s="2" t="inlineStr"/>
+      <c r="W669" s="2" t="inlineStr"/>
+      <c r="X669" s="2" t="inlineStr"/>
+      <c r="Y669" s="2" t="inlineStr"/>
+      <c r="Z669" s="2" t="inlineStr"/>
+      <c r="AA669" s="2" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="inlineStr">
+        <is>
+          <t>MERCEARIAS CRIATIVAS, LDA</t>
+        </is>
+      </c>
+      <c r="B670" s="2" t="inlineStr"/>
+      <c r="C670" s="2" t="inlineStr">
+        <is>
+          <t>168652</t>
+        </is>
+      </c>
+      <c r="D670" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E670" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F670" s="2" t="inlineStr"/>
+      <c r="G670" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Guerra Junqueiro, 4A</t>
+        </is>
+      </c>
+      <c r="H670" s="2" t="inlineStr">
+        <is>
+          <t>1000-167</t>
+        </is>
+      </c>
+      <c r="I670" s="2" t="inlineStr">
+        <is>
+          <t>https://www.merceariacriativa.com</t>
+        </is>
+      </c>
+      <c r="J670" s="2" t="inlineStr"/>
+      <c r="K670" s="2" t="inlineStr"/>
+      <c r="L670" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M670" s="2" t="inlineStr">
+        <is>
+          <t>330248</t>
+        </is>
+      </c>
+      <c r="N670" s="2" t="inlineStr">
+        <is>
+          <t>merceariacriativa@gmail.com</t>
+        </is>
+      </c>
+      <c r="O670" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 848 5198</t>
+        </is>
+      </c>
+      <c r="P670" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q670" s="2" t="inlineStr">
+        <is>
+          <t>509311504</t>
+        </is>
+      </c>
+      <c r="R670" s="2" t="inlineStr"/>
+      <c r="S670" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MerceariaCriativa</t>
+        </is>
+      </c>
+      <c r="T670" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/merceariacriativa</t>
+        </is>
+      </c>
+      <c r="U670" s="2" t="inlineStr"/>
+      <c r="V670" s="2" t="inlineStr"/>
+      <c r="W670" s="2" t="inlineStr">
+        <is>
+          <t>Catarina Nunes</t>
+        </is>
+      </c>
+      <c r="X670" s="2" t="inlineStr">
+        <is>
+          <t>Shop Assistant</t>
+        </is>
+      </c>
+      <c r="Y670" s="2" t="inlineStr"/>
+      <c r="Z670" s="2" t="inlineStr"/>
+      <c r="AA670" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/catarina-nunes-6610001b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="inlineStr">
+        <is>
+          <t>MERCEARIA MEIO PONTO, LDA</t>
+        </is>
+      </c>
+      <c r="B671" s="2" t="inlineStr"/>
+      <c r="C671" s="2" t="inlineStr">
+        <is>
+          <t>168651</t>
+        </is>
+      </c>
+      <c r="D671" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E671" s="2" t="inlineStr">
+        <is>
+          <t>Matosinhos</t>
+        </is>
+      </c>
+      <c r="F671" s="2" t="inlineStr"/>
+      <c r="G671" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Doutor Fernando Aroso, 1168 R/C</t>
+        </is>
+      </c>
+      <c r="H671" s="2" t="inlineStr">
+        <is>
+          <t>4450-664</t>
+        </is>
+      </c>
+      <c r="I671" s="2" t="inlineStr">
+        <is>
+          <t>https://www.garrafeirameioponto.com</t>
+        </is>
+      </c>
+      <c r="J671" s="2" t="inlineStr"/>
+      <c r="K671" s="2" t="inlineStr"/>
+      <c r="L671" s="2" t="inlineStr"/>
+      <c r="M671" s="2" t="inlineStr">
+        <is>
+          <t>345994</t>
+        </is>
+      </c>
+      <c r="N671" s="2" t="inlineStr">
+        <is>
+          <t>geral@garrafeirameioponto.com</t>
+        </is>
+      </c>
+      <c r="O671" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 996 2209</t>
+        </is>
+      </c>
+      <c r="P671" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q671" s="2" t="inlineStr">
+        <is>
+          <t>504042912</t>
+        </is>
+      </c>
+      <c r="R671" s="2" t="inlineStr"/>
+      <c r="S671" s="2" t="inlineStr"/>
+      <c r="T671" s="2" t="inlineStr"/>
+      <c r="U671" s="2" t="inlineStr"/>
+      <c r="V671" s="2" t="inlineStr"/>
+      <c r="W671" s="2" t="inlineStr"/>
+      <c r="X671" s="2" t="inlineStr"/>
+      <c r="Y671" s="2" t="inlineStr"/>
+      <c r="Z671" s="2" t="inlineStr"/>
+      <c r="AA671" s="2" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="inlineStr">
+        <is>
+          <t>PÉROLA DO ROCIO, LDA</t>
+        </is>
+      </c>
+      <c r="B672" s="2" t="inlineStr"/>
+      <c r="C672" s="2" t="inlineStr">
+        <is>
+          <t>168650</t>
+        </is>
+      </c>
+      <c r="D672" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E672" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F672" s="2" t="inlineStr"/>
+      <c r="G672" s="2" t="inlineStr">
+        <is>
+          <t>Praça Dom Pedro Iv, 105 Loja</t>
+        </is>
+      </c>
+      <c r="H672" s="2" t="inlineStr">
+        <is>
+          <t>1100-202</t>
+        </is>
+      </c>
+      <c r="I672" s="2" t="inlineStr">
+        <is>
+          <t>https://www.peroladorossio.pt</t>
+        </is>
+      </c>
+      <c r="J672" s="2" t="inlineStr"/>
+      <c r="K672" s="2" t="inlineStr"/>
+      <c r="L672" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M672" s="2" t="inlineStr">
+        <is>
+          <t>132250</t>
+        </is>
+      </c>
+      <c r="N672" s="2" t="inlineStr">
+        <is>
+          <t>geral@peroladorossio.pt</t>
+        </is>
+      </c>
+      <c r="O672" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 342 0744</t>
+        </is>
+      </c>
+      <c r="P672" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="Q672" s="2" t="inlineStr">
+        <is>
+          <t>500477310</t>
+        </is>
+      </c>
+      <c r="R672" s="2" t="inlineStr"/>
+      <c r="S672" s="2" t="inlineStr"/>
+      <c r="T672" s="2" t="inlineStr"/>
+      <c r="U672" s="2" t="inlineStr"/>
+      <c r="V672" s="2" t="inlineStr"/>
+      <c r="W672" s="2" t="inlineStr"/>
+      <c r="X672" s="2" t="inlineStr"/>
+      <c r="Y672" s="2" t="inlineStr"/>
+      <c r="Z672" s="2" t="inlineStr"/>
+      <c r="AA672" s="2" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="inlineStr">
+        <is>
+          <t>AROMAS REAIS, GOURMET, UNIPESSOAL, LDA</t>
+        </is>
+      </c>
+      <c r="B673" s="2" t="inlineStr"/>
+      <c r="C673" s="2" t="inlineStr">
+        <is>
+          <t>168649</t>
+        </is>
+      </c>
+      <c r="D673" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E673" s="2" t="inlineStr">
+        <is>
+          <t>Silveira</t>
+        </is>
+      </c>
+      <c r="F673" s="2" t="inlineStr"/>
+      <c r="G673" s="2" t="inlineStr">
+        <is>
+          <t>Rua De Santo Onofre, 10</t>
+        </is>
+      </c>
+      <c r="H673" s="2" t="inlineStr">
+        <is>
+          <t>2560-538</t>
+        </is>
+      </c>
+      <c r="I673" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aromas-reais-gourmet.pt</t>
+        </is>
+      </c>
+      <c r="J673" s="2" t="inlineStr"/>
+      <c r="K673" s="2" t="inlineStr"/>
+      <c r="L673" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M673" s="2" t="inlineStr">
+        <is>
+          <t>13083</t>
+        </is>
+      </c>
+      <c r="N673" s="2" t="inlineStr">
+        <is>
+          <t>geral@aromas-reais-gourmet.pt</t>
+        </is>
+      </c>
+      <c r="O673" s="2" t="inlineStr"/>
+      <c r="P673" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q673" s="2" t="inlineStr">
+        <is>
+          <t>513265848</t>
+        </is>
+      </c>
+      <c r="R673" s="2" t="inlineStr"/>
+      <c r="S673" s="2" t="inlineStr"/>
+      <c r="T673" s="2" t="inlineStr"/>
+      <c r="U673" s="2" t="inlineStr"/>
+      <c r="V673" s="2" t="inlineStr"/>
+      <c r="W673" s="2" t="inlineStr"/>
+      <c r="X673" s="2" t="inlineStr"/>
+      <c r="Y673" s="2" t="inlineStr"/>
+      <c r="Z673" s="2" t="inlineStr"/>
+      <c r="AA673" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA673"/>
+  <dimension ref="A1:AA674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -71263,6 +71263,83 @@
       <c r="Z673" s="2" t="inlineStr"/>
       <c r="AA673" s="2" t="inlineStr"/>
     </row>
+    <row r="674">
+      <c r="A674" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Grande Escolha</t>
+        </is>
+      </c>
+      <c r="B674" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Grande Escolha</t>
+        </is>
+      </c>
+      <c r="C674" s="2" t="inlineStr">
+        <is>
+          <t>97203</t>
+        </is>
+      </c>
+      <c r="D674" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E674" s="2" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F674" s="2" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G674" s="2" t="inlineStr">
+        <is>
+          <t>54 Avenida de São Lourenço</t>
+        </is>
+      </c>
+      <c r="H674" s="2" t="inlineStr">
+        <is>
+          <t>4705-442</t>
+        </is>
+      </c>
+      <c r="I674" s="2" t="inlineStr">
+        <is>
+          <t>https://garrafeiragrandeescolha.pt</t>
+        </is>
+      </c>
+      <c r="J674" s="2" t="inlineStr"/>
+      <c r="K674" s="2" t="inlineStr"/>
+      <c r="L674" s="2" t="inlineStr"/>
+      <c r="M674" s="2" t="inlineStr"/>
+      <c r="N674" s="2" t="inlineStr">
+        <is>
+          <t>garrafeiragescolha@gmail.com</t>
+        </is>
+      </c>
+      <c r="O674" s="2" t="inlineStr"/>
+      <c r="P674" s="2" t="inlineStr"/>
+      <c r="Q674" s="2" t="inlineStr"/>
+      <c r="R674" s="2" t="inlineStr"/>
+      <c r="S674" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/garrafeiragrandeescolha/</t>
+        </is>
+      </c>
+      <c r="T674" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeiragrandeescolha/</t>
+        </is>
+      </c>
+      <c r="U674" s="2" t="inlineStr"/>
+      <c r="V674" s="2" t="inlineStr"/>
+      <c r="W674" s="2" t="inlineStr"/>
+      <c r="X674" s="2" t="inlineStr"/>
+      <c r="Y674" s="2" t="inlineStr"/>
+      <c r="Z674" s="2" t="inlineStr"/>
+      <c r="AA674" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA674"/>
+  <dimension ref="A1:AA682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -71340,6 +71340,778 @@
       <c r="Z674" s="2" t="inlineStr"/>
       <c r="AA674" s="2" t="inlineStr"/>
     </row>
+    <row r="675">
+      <c r="A675" s="2" t="inlineStr">
+        <is>
+          <t>Creative Gourmet Lda.</t>
+        </is>
+      </c>
+      <c r="B675" s="2" t="inlineStr">
+        <is>
+          <t>Creative Gourmet Lda.</t>
+        </is>
+      </c>
+      <c r="C675" s="2" t="inlineStr">
+        <is>
+          <t>108841</t>
+        </is>
+      </c>
+      <c r="D675" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E675" s="2" t="inlineStr">
+        <is>
+          <t>Santo Tirso</t>
+        </is>
+      </c>
+      <c r="F675" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G675" s="2" t="inlineStr">
+        <is>
+          <t>164 Rua Zona Industrial Alto da Cruz</t>
+        </is>
+      </c>
+      <c r="H675" s="2" t="inlineStr">
+        <is>
+          <t>4780-739</t>
+        </is>
+      </c>
+      <c r="I675" s="2" t="inlineStr">
+        <is>
+          <t>https://www.creative-gourmet.com</t>
+        </is>
+      </c>
+      <c r="J675" s="2" t="inlineStr"/>
+      <c r="K675" s="2" t="inlineStr"/>
+      <c r="L675" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M675" s="2" t="inlineStr"/>
+      <c r="N675" s="2" t="inlineStr">
+        <is>
+          <t>hello@creative-gourmet.com</t>
+        </is>
+      </c>
+      <c r="O675" s="2" t="inlineStr">
+        <is>
+          <t>+351 252 891 290</t>
+        </is>
+      </c>
+      <c r="P675" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q675" s="2" t="inlineStr">
+        <is>
+          <t>510388701</t>
+        </is>
+      </c>
+      <c r="R675" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/creative-gourmet/</t>
+        </is>
+      </c>
+      <c r="S675" s="2" t="inlineStr"/>
+      <c r="T675" s="2" t="inlineStr"/>
+      <c r="U675" s="2" t="inlineStr"/>
+      <c r="V675" s="2" t="inlineStr"/>
+      <c r="W675" s="2" t="inlineStr">
+        <is>
+          <t>Rui Guedes</t>
+        </is>
+      </c>
+      <c r="X675" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/ Sales &amp; Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y675" s="2" t="inlineStr"/>
+      <c r="Z675" s="2" t="inlineStr"/>
+      <c r="AA675" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ruiguedespinto</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="inlineStr">
+        <is>
+          <t>Portugal Vineyards</t>
+        </is>
+      </c>
+      <c r="B676" s="2" t="inlineStr">
+        <is>
+          <t>Portugal Vineyards</t>
+        </is>
+      </c>
+      <c r="C676" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="D676" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E676" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F676" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G676" s="2" t="inlineStr">
+        <is>
+          <t>Rua Dr. Eduardo Santos Silva n º 261</t>
+        </is>
+      </c>
+      <c r="H676" s="2" t="inlineStr">
+        <is>
+          <t>4200-283</t>
+        </is>
+      </c>
+      <c r="I676" s="2" t="inlineStr">
+        <is>
+          <t>https://www.portugalvineyards.com</t>
+        </is>
+      </c>
+      <c r="J676" s="2" t="inlineStr"/>
+      <c r="K676" s="2" t="inlineStr"/>
+      <c r="L676" s="2" t="inlineStr"/>
+      <c r="M676" s="2" t="inlineStr"/>
+      <c r="N676" s="2" t="inlineStr">
+        <is>
+          <t>clients@portugalvineyards.com</t>
+        </is>
+      </c>
+      <c r="O676" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 096 4430</t>
+        </is>
+      </c>
+      <c r="P676" s="2" t="inlineStr"/>
+      <c r="Q676" s="2" t="inlineStr"/>
+      <c r="R676" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/portugalvineyards/</t>
+        </is>
+      </c>
+      <c r="S676" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Portugalvineyards</t>
+        </is>
+      </c>
+      <c r="T676" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/portugalvineyards</t>
+        </is>
+      </c>
+      <c r="U676" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/pvineyards</t>
+        </is>
+      </c>
+      <c r="V676" s="2" t="inlineStr"/>
+      <c r="W676" s="2" t="inlineStr">
+        <is>
+          <t>Daniela Costa</t>
+        </is>
+      </c>
+      <c r="X676" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y676" s="2" t="inlineStr"/>
+      <c r="Z676" s="2" t="inlineStr"/>
+      <c r="AA676" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniela-costa-0794a127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="inlineStr">
+        <is>
+          <t>Portugal Vineyards</t>
+        </is>
+      </c>
+      <c r="B677" s="2" t="inlineStr">
+        <is>
+          <t>Portugal Vineyards</t>
+        </is>
+      </c>
+      <c r="C677" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="D677" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E677" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F677" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G677" s="2" t="inlineStr">
+        <is>
+          <t>Rua Dr. Eduardo Santos Silva n º 261</t>
+        </is>
+      </c>
+      <c r="H677" s="2" t="inlineStr">
+        <is>
+          <t>4200-283</t>
+        </is>
+      </c>
+      <c r="I677" s="2" t="inlineStr">
+        <is>
+          <t>https://www.portugalvineyards.com</t>
+        </is>
+      </c>
+      <c r="J677" s="2" t="inlineStr"/>
+      <c r="K677" s="2" t="inlineStr"/>
+      <c r="L677" s="2" t="inlineStr"/>
+      <c r="M677" s="2" t="inlineStr"/>
+      <c r="N677" s="2" t="inlineStr">
+        <is>
+          <t>clients@portugalvineyards.com</t>
+        </is>
+      </c>
+      <c r="O677" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 096 4430</t>
+        </is>
+      </c>
+      <c r="P677" s="2" t="inlineStr"/>
+      <c r="Q677" s="2" t="inlineStr"/>
+      <c r="R677" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/portugalvineyards/</t>
+        </is>
+      </c>
+      <c r="S677" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Portugalvineyards</t>
+        </is>
+      </c>
+      <c r="T677" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/portugalvineyards</t>
+        </is>
+      </c>
+      <c r="U677" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/pvineyards</t>
+        </is>
+      </c>
+      <c r="V677" s="2" t="inlineStr"/>
+      <c r="W677" s="2" t="inlineStr">
+        <is>
+          <t>Daniela Costa</t>
+        </is>
+      </c>
+      <c r="X677" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y677" s="2" t="inlineStr"/>
+      <c r="Z677" s="2" t="inlineStr"/>
+      <c r="AA677" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniela-costa-0794a127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="inlineStr">
+        <is>
+          <t>Wine Castle, Lda</t>
+        </is>
+      </c>
+      <c r="B678" s="2" t="inlineStr">
+        <is>
+          <t>Wine Castle, Lda</t>
+        </is>
+      </c>
+      <c r="C678" s="2" t="inlineStr">
+        <is>
+          <t>50082</t>
+        </is>
+      </c>
+      <c r="D678" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E678" s="2" t="inlineStr">
+        <is>
+          <t>Estômbar e Parchal</t>
+        </is>
+      </c>
+      <c r="F678" s="2" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="G678" s="2" t="inlineStr">
+        <is>
+          <t>Rua Poeta António Aleixo</t>
+        </is>
+      </c>
+      <c r="H678" s="2" t="inlineStr">
+        <is>
+          <t>8400-061</t>
+        </is>
+      </c>
+      <c r="I678" s="2" t="inlineStr"/>
+      <c r="J678" s="2" t="inlineStr"/>
+      <c r="K678" s="2" t="inlineStr"/>
+      <c r="L678" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M678" s="2" t="inlineStr"/>
+      <c r="N678" s="2" t="inlineStr">
+        <is>
+          <t>info@winecastle.eu</t>
+        </is>
+      </c>
+      <c r="O678" s="2" t="inlineStr"/>
+      <c r="P678" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q678" s="2" t="inlineStr">
+        <is>
+          <t>515145700</t>
+        </is>
+      </c>
+      <c r="R678" s="2" t="inlineStr"/>
+      <c r="S678" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winecastledistribution/</t>
+        </is>
+      </c>
+      <c r="T678" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winecastlealgarve</t>
+        </is>
+      </c>
+      <c r="U678" s="2" t="inlineStr"/>
+      <c r="V678" s="2" t="inlineStr"/>
+      <c r="W678" s="2" t="inlineStr"/>
+      <c r="X678" s="2" t="inlineStr"/>
+      <c r="Y678" s="2" t="inlineStr"/>
+      <c r="Z678" s="2" t="inlineStr"/>
+      <c r="AA678" s="2" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="inlineStr">
+        <is>
+          <t>Ivin Lda.</t>
+        </is>
+      </c>
+      <c r="B679" s="2" t="inlineStr">
+        <is>
+          <t>Ivin Lda.</t>
+        </is>
+      </c>
+      <c r="C679" s="2" t="inlineStr">
+        <is>
+          <t>42118</t>
+        </is>
+      </c>
+      <c r="D679" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E679" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F679" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa, Santa Clara</t>
+        </is>
+      </c>
+      <c r="G679" s="2" t="inlineStr">
+        <is>
+          <t>1 Rua Jorge De Sena</t>
+        </is>
+      </c>
+      <c r="H679" s="2" t="inlineStr">
+        <is>
+          <t>1750-129</t>
+        </is>
+      </c>
+      <c r="I679" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ivin.pt</t>
+        </is>
+      </c>
+      <c r="J679" s="2" t="inlineStr"/>
+      <c r="K679" s="2" t="inlineStr"/>
+      <c r="L679" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M679" s="2" t="inlineStr"/>
+      <c r="N679" s="2" t="inlineStr">
+        <is>
+          <t>geral@ivin.pt</t>
+        </is>
+      </c>
+      <c r="O679" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 408 3488</t>
+        </is>
+      </c>
+      <c r="P679" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q679" s="2" t="inlineStr">
+        <is>
+          <t>509077072</t>
+        </is>
+      </c>
+      <c r="R679" s="2" t="inlineStr"/>
+      <c r="S679" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/www.ivin.pt</t>
+        </is>
+      </c>
+      <c r="T679" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ivin.pt/</t>
+        </is>
+      </c>
+      <c r="U679" s="2" t="inlineStr"/>
+      <c r="V679" s="2" t="inlineStr"/>
+      <c r="W679" s="2" t="inlineStr">
+        <is>
+          <t>Miguel Grijó</t>
+        </is>
+      </c>
+      <c r="X679" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Ceo</t>
+        </is>
+      </c>
+      <c r="Y679" s="2" t="inlineStr"/>
+      <c r="Z679" s="2" t="inlineStr"/>
+      <c r="AA679" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-grij%c3%b3-60363aa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="inlineStr">
+        <is>
+          <t>Ivin Lda.</t>
+        </is>
+      </c>
+      <c r="B680" s="2" t="inlineStr">
+        <is>
+          <t>Ivin Lda.</t>
+        </is>
+      </c>
+      <c r="C680" s="2" t="inlineStr">
+        <is>
+          <t>42118</t>
+        </is>
+      </c>
+      <c r="D680" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E680" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F680" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa, Santa Clara</t>
+        </is>
+      </c>
+      <c r="G680" s="2" t="inlineStr">
+        <is>
+          <t>1 Rua Jorge De Sena</t>
+        </is>
+      </c>
+      <c r="H680" s="2" t="inlineStr">
+        <is>
+          <t>1750-129</t>
+        </is>
+      </c>
+      <c r="I680" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ivin.pt</t>
+        </is>
+      </c>
+      <c r="J680" s="2" t="inlineStr"/>
+      <c r="K680" s="2" t="inlineStr"/>
+      <c r="L680" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M680" s="2" t="inlineStr"/>
+      <c r="N680" s="2" t="inlineStr">
+        <is>
+          <t>geral@ivin.pt</t>
+        </is>
+      </c>
+      <c r="O680" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 408 3488</t>
+        </is>
+      </c>
+      <c r="P680" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q680" s="2" t="inlineStr">
+        <is>
+          <t>509077072</t>
+        </is>
+      </c>
+      <c r="R680" s="2" t="inlineStr"/>
+      <c r="S680" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/www.ivin.pt</t>
+        </is>
+      </c>
+      <c r="T680" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ivin.pt/</t>
+        </is>
+      </c>
+      <c r="U680" s="2" t="inlineStr"/>
+      <c r="V680" s="2" t="inlineStr"/>
+      <c r="W680" s="2" t="inlineStr">
+        <is>
+          <t>Stephane Perrin</t>
+        </is>
+      </c>
+      <c r="X680" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y680" s="2" t="inlineStr"/>
+      <c r="Z680" s="2" t="inlineStr"/>
+      <c r="AA680" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stephane-perrin-3154a650/</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Farinha, Lda</t>
+        </is>
+      </c>
+      <c r="B681" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Farinha, Lda</t>
+        </is>
+      </c>
+      <c r="C681" s="2" t="inlineStr">
+        <is>
+          <t>26113</t>
+        </is>
+      </c>
+      <c r="D681" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E681" s="2" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="F681" s="2" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="G681" s="2" t="inlineStr">
+        <is>
+          <t>3 Rua Vieira da Silva</t>
+        </is>
+      </c>
+      <c r="H681" s="2" t="inlineStr">
+        <is>
+          <t>2910-741</t>
+        </is>
+      </c>
+      <c r="I681" s="2" t="inlineStr">
+        <is>
+          <t>https://garrafeirafarinha.com</t>
+        </is>
+      </c>
+      <c r="J681" s="2" t="inlineStr"/>
+      <c r="K681" s="2" t="inlineStr"/>
+      <c r="L681" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M681" s="2" t="inlineStr"/>
+      <c r="N681" s="2" t="inlineStr">
+        <is>
+          <t>garrafeirafarinha@sapo.pt</t>
+        </is>
+      </c>
+      <c r="O681" s="2" t="inlineStr">
+        <is>
+          <t>+351 265 741 152</t>
+        </is>
+      </c>
+      <c r="P681" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q681" s="2" t="inlineStr">
+        <is>
+          <t>513788689</t>
+        </is>
+      </c>
+      <c r="R681" s="2" t="inlineStr"/>
+      <c r="S681" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GarrafeiraFarinhaLda</t>
+        </is>
+      </c>
+      <c r="T681" s="2" t="inlineStr"/>
+      <c r="U681" s="2" t="inlineStr"/>
+      <c r="V681" s="2" t="inlineStr"/>
+      <c r="W681" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Farinha</t>
+        </is>
+      </c>
+      <c r="X681" s="2" t="inlineStr">
+        <is>
+          <t>Manager/ Responsible</t>
+        </is>
+      </c>
+      <c r="Y681" s="2" t="inlineStr"/>
+      <c r="Z681" s="2" t="inlineStr"/>
+      <c r="AA681" s="2" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Grande Escolha</t>
+        </is>
+      </c>
+      <c r="B682" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Grande Escolha</t>
+        </is>
+      </c>
+      <c r="C682" s="2" t="inlineStr">
+        <is>
+          <t>97203</t>
+        </is>
+      </c>
+      <c r="D682" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E682" s="2" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F682" s="2" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G682" s="2" t="inlineStr">
+        <is>
+          <t>54 Avenida de São Lourenço</t>
+        </is>
+      </c>
+      <c r="H682" s="2" t="inlineStr">
+        <is>
+          <t>4705-442</t>
+        </is>
+      </c>
+      <c r="I682" s="2" t="inlineStr">
+        <is>
+          <t>https://garrafeiragrandeescolha.pt</t>
+        </is>
+      </c>
+      <c r="J682" s="2" t="inlineStr"/>
+      <c r="K682" s="2" t="inlineStr"/>
+      <c r="L682" s="2" t="inlineStr"/>
+      <c r="M682" s="2" t="inlineStr"/>
+      <c r="N682" s="2" t="inlineStr">
+        <is>
+          <t>garrafeiragescolha@gmail.com</t>
+        </is>
+      </c>
+      <c r="O682" s="2" t="inlineStr"/>
+      <c r="P682" s="2" t="inlineStr"/>
+      <c r="Q682" s="2" t="inlineStr"/>
+      <c r="R682" s="2" t="inlineStr"/>
+      <c r="S682" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/garrafeiragrandeescolha/</t>
+        </is>
+      </c>
+      <c r="T682" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeiragrandeescolha/</t>
+        </is>
+      </c>
+      <c r="U682" s="2" t="inlineStr"/>
+      <c r="V682" s="2" t="inlineStr"/>
+      <c r="W682" s="2" t="inlineStr"/>
+      <c r="X682" s="2" t="inlineStr"/>
+      <c r="Y682" s="2" t="inlineStr"/>
+      <c r="Z682" s="2" t="inlineStr"/>
+      <c r="AA682" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA682"/>
+  <dimension ref="A1:AA691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -72112,6 +72112,855 @@
       <c r="Z682" s="2" t="inlineStr"/>
       <c r="AA682" s="2" t="inlineStr"/>
     </row>
+    <row r="683">
+      <c r="A683" s="2" t="inlineStr">
+        <is>
+          <t>Ptwraders, Lda</t>
+        </is>
+      </c>
+      <c r="B683" s="2" t="inlineStr">
+        <is>
+          <t>Pt Wine - Distribuição De Vinhos</t>
+        </is>
+      </c>
+      <c r="C683" s="2" t="inlineStr">
+        <is>
+          <t>28787</t>
+        </is>
+      </c>
+      <c r="D683" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E683" s="2" t="inlineStr">
+        <is>
+          <t>Aveiro</t>
+        </is>
+      </c>
+      <c r="F683" s="2" t="inlineStr">
+        <is>
+          <t>Aveiro, Vera Cruz</t>
+        </is>
+      </c>
+      <c r="G683" s="2" t="inlineStr">
+        <is>
+          <t>Rua Nova De Vilar  Armazém A, Nº 74</t>
+        </is>
+      </c>
+      <c r="H683" s="2" t="inlineStr">
+        <is>
+          <t>3810-196</t>
+        </is>
+      </c>
+      <c r="I683" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ptwine.pt</t>
+        </is>
+      </c>
+      <c r="J683" s="2" t="inlineStr"/>
+      <c r="K683" s="2" t="inlineStr"/>
+      <c r="L683" s="2" t="inlineStr"/>
+      <c r="M683" s="2" t="inlineStr"/>
+      <c r="N683" s="2" t="inlineStr">
+        <is>
+          <t>info@ptwine.pt</t>
+        </is>
+      </c>
+      <c r="O683" s="2" t="inlineStr"/>
+      <c r="P683" s="2" t="inlineStr"/>
+      <c r="Q683" s="2" t="inlineStr"/>
+      <c r="R683" s="2" t="inlineStr"/>
+      <c r="S683" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PTwineCashAndCarry/</t>
+        </is>
+      </c>
+      <c r="T683" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ptwine_distribuicao</t>
+        </is>
+      </c>
+      <c r="U683" s="2" t="inlineStr"/>
+      <c r="V683" s="2" t="inlineStr"/>
+      <c r="W683" s="2" t="inlineStr"/>
+      <c r="X683" s="2" t="inlineStr"/>
+      <c r="Y683" s="2" t="inlineStr"/>
+      <c r="Z683" s="2" t="inlineStr"/>
+      <c r="AA683" s="2" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="inlineStr">
+        <is>
+          <t>Creative Gourmet Lda.</t>
+        </is>
+      </c>
+      <c r="B684" s="2" t="inlineStr">
+        <is>
+          <t>Creative Gourmet Lda.</t>
+        </is>
+      </c>
+      <c r="C684" s="2" t="inlineStr">
+        <is>
+          <t>108841</t>
+        </is>
+      </c>
+      <c r="D684" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E684" s="2" t="inlineStr">
+        <is>
+          <t>Santo Tirso</t>
+        </is>
+      </c>
+      <c r="F684" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G684" s="2" t="inlineStr">
+        <is>
+          <t>164 Rua Zona Industrial Alto da Cruz</t>
+        </is>
+      </c>
+      <c r="H684" s="2" t="inlineStr">
+        <is>
+          <t>4780-739</t>
+        </is>
+      </c>
+      <c r="I684" s="2" t="inlineStr">
+        <is>
+          <t>https://www.creative-gourmet.com</t>
+        </is>
+      </c>
+      <c r="J684" s="2" t="inlineStr"/>
+      <c r="K684" s="2" t="inlineStr"/>
+      <c r="L684" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M684" s="2" t="inlineStr"/>
+      <c r="N684" s="2" t="inlineStr">
+        <is>
+          <t>hello@creative-gourmet.com</t>
+        </is>
+      </c>
+      <c r="O684" s="2" t="inlineStr">
+        <is>
+          <t>+351 252 891 290</t>
+        </is>
+      </c>
+      <c r="P684" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q684" s="2" t="inlineStr">
+        <is>
+          <t>510388701</t>
+        </is>
+      </c>
+      <c r="R684" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/creative-gourmet/</t>
+        </is>
+      </c>
+      <c r="S684" s="2" t="inlineStr"/>
+      <c r="T684" s="2" t="inlineStr"/>
+      <c r="U684" s="2" t="inlineStr"/>
+      <c r="V684" s="2" t="inlineStr"/>
+      <c r="W684" s="2" t="inlineStr">
+        <is>
+          <t>Rui Guedes</t>
+        </is>
+      </c>
+      <c r="X684" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/ Sales &amp; Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y684" s="2" t="inlineStr"/>
+      <c r="Z684" s="2" t="inlineStr"/>
+      <c r="AA684" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ruiguedespinto</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="inlineStr">
+        <is>
+          <t>Portugal Vineyards</t>
+        </is>
+      </c>
+      <c r="B685" s="2" t="inlineStr">
+        <is>
+          <t>Portugal Vineyards</t>
+        </is>
+      </c>
+      <c r="C685" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="D685" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E685" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F685" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G685" s="2" t="inlineStr">
+        <is>
+          <t>Rua Dr. Eduardo Santos Silva n º 261</t>
+        </is>
+      </c>
+      <c r="H685" s="2" t="inlineStr">
+        <is>
+          <t>4200-283</t>
+        </is>
+      </c>
+      <c r="I685" s="2" t="inlineStr">
+        <is>
+          <t>https://www.portugalvineyards.com</t>
+        </is>
+      </c>
+      <c r="J685" s="2" t="inlineStr"/>
+      <c r="K685" s="2" t="inlineStr"/>
+      <c r="L685" s="2" t="inlineStr"/>
+      <c r="M685" s="2" t="inlineStr"/>
+      <c r="N685" s="2" t="inlineStr">
+        <is>
+          <t>clients@portugalvineyards.com</t>
+        </is>
+      </c>
+      <c r="O685" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 096 4430</t>
+        </is>
+      </c>
+      <c r="P685" s="2" t="inlineStr"/>
+      <c r="Q685" s="2" t="inlineStr"/>
+      <c r="R685" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/portugalvineyards/</t>
+        </is>
+      </c>
+      <c r="S685" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Portugalvineyards</t>
+        </is>
+      </c>
+      <c r="T685" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/portugalvineyards</t>
+        </is>
+      </c>
+      <c r="U685" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/pvineyards</t>
+        </is>
+      </c>
+      <c r="V685" s="2" t="inlineStr"/>
+      <c r="W685" s="2" t="inlineStr">
+        <is>
+          <t>Daniela Costa</t>
+        </is>
+      </c>
+      <c r="X685" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y685" s="2" t="inlineStr"/>
+      <c r="Z685" s="2" t="inlineStr"/>
+      <c r="AA685" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniela-costa-0794a127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="inlineStr">
+        <is>
+          <t>Portugal Vineyards</t>
+        </is>
+      </c>
+      <c r="B686" s="2" t="inlineStr">
+        <is>
+          <t>Portugal Vineyards</t>
+        </is>
+      </c>
+      <c r="C686" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="D686" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E686" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F686" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G686" s="2" t="inlineStr">
+        <is>
+          <t>Rua Dr. Eduardo Santos Silva n º 261</t>
+        </is>
+      </c>
+      <c r="H686" s="2" t="inlineStr">
+        <is>
+          <t>4200-283</t>
+        </is>
+      </c>
+      <c r="I686" s="2" t="inlineStr">
+        <is>
+          <t>https://www.portugalvineyards.com</t>
+        </is>
+      </c>
+      <c r="J686" s="2" t="inlineStr"/>
+      <c r="K686" s="2" t="inlineStr"/>
+      <c r="L686" s="2" t="inlineStr"/>
+      <c r="M686" s="2" t="inlineStr"/>
+      <c r="N686" s="2" t="inlineStr">
+        <is>
+          <t>clients@portugalvineyards.com</t>
+        </is>
+      </c>
+      <c r="O686" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 096 4430</t>
+        </is>
+      </c>
+      <c r="P686" s="2" t="inlineStr"/>
+      <c r="Q686" s="2" t="inlineStr"/>
+      <c r="R686" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/portugalvineyards/</t>
+        </is>
+      </c>
+      <c r="S686" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Portugalvineyards</t>
+        </is>
+      </c>
+      <c r="T686" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/portugalvineyards</t>
+        </is>
+      </c>
+      <c r="U686" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/pvineyards</t>
+        </is>
+      </c>
+      <c r="V686" s="2" t="inlineStr"/>
+      <c r="W686" s="2" t="inlineStr">
+        <is>
+          <t>Daniela Costa</t>
+        </is>
+      </c>
+      <c r="X686" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="Y686" s="2" t="inlineStr"/>
+      <c r="Z686" s="2" t="inlineStr"/>
+      <c r="AA686" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniela-costa-0794a127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="inlineStr">
+        <is>
+          <t>Wine Castle, Lda</t>
+        </is>
+      </c>
+      <c r="B687" s="2" t="inlineStr">
+        <is>
+          <t>Wine Castle, Lda</t>
+        </is>
+      </c>
+      <c r="C687" s="2" t="inlineStr">
+        <is>
+          <t>50082</t>
+        </is>
+      </c>
+      <c r="D687" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E687" s="2" t="inlineStr">
+        <is>
+          <t>Estômbar e Parchal</t>
+        </is>
+      </c>
+      <c r="F687" s="2" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="G687" s="2" t="inlineStr">
+        <is>
+          <t>Rua Poeta António Aleixo</t>
+        </is>
+      </c>
+      <c r="H687" s="2" t="inlineStr">
+        <is>
+          <t>8400-061</t>
+        </is>
+      </c>
+      <c r="I687" s="2" t="inlineStr"/>
+      <c r="J687" s="2" t="inlineStr"/>
+      <c r="K687" s="2" t="inlineStr"/>
+      <c r="L687" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M687" s="2" t="inlineStr"/>
+      <c r="N687" s="2" t="inlineStr">
+        <is>
+          <t>info@winecastle.eu</t>
+        </is>
+      </c>
+      <c r="O687" s="2" t="inlineStr"/>
+      <c r="P687" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q687" s="2" t="inlineStr">
+        <is>
+          <t>515145700</t>
+        </is>
+      </c>
+      <c r="R687" s="2" t="inlineStr"/>
+      <c r="S687" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winecastledistribution/</t>
+        </is>
+      </c>
+      <c r="T687" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winecastlealgarve</t>
+        </is>
+      </c>
+      <c r="U687" s="2" t="inlineStr"/>
+      <c r="V687" s="2" t="inlineStr"/>
+      <c r="W687" s="2" t="inlineStr"/>
+      <c r="X687" s="2" t="inlineStr"/>
+      <c r="Y687" s="2" t="inlineStr"/>
+      <c r="Z687" s="2" t="inlineStr"/>
+      <c r="AA687" s="2" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="inlineStr">
+        <is>
+          <t>Ivin Lda.</t>
+        </is>
+      </c>
+      <c r="B688" s="2" t="inlineStr">
+        <is>
+          <t>Ivin Lda.</t>
+        </is>
+      </c>
+      <c r="C688" s="2" t="inlineStr">
+        <is>
+          <t>42118</t>
+        </is>
+      </c>
+      <c r="D688" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E688" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F688" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa, Santa Clara</t>
+        </is>
+      </c>
+      <c r="G688" s="2" t="inlineStr">
+        <is>
+          <t>1 Rua Jorge De Sena</t>
+        </is>
+      </c>
+      <c r="H688" s="2" t="inlineStr">
+        <is>
+          <t>1750-129</t>
+        </is>
+      </c>
+      <c r="I688" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ivin.pt</t>
+        </is>
+      </c>
+      <c r="J688" s="2" t="inlineStr"/>
+      <c r="K688" s="2" t="inlineStr"/>
+      <c r="L688" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M688" s="2" t="inlineStr"/>
+      <c r="N688" s="2" t="inlineStr">
+        <is>
+          <t>geral@ivin.pt</t>
+        </is>
+      </c>
+      <c r="O688" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 408 3488</t>
+        </is>
+      </c>
+      <c r="P688" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q688" s="2" t="inlineStr">
+        <is>
+          <t>509077072</t>
+        </is>
+      </c>
+      <c r="R688" s="2" t="inlineStr"/>
+      <c r="S688" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/www.ivin.pt</t>
+        </is>
+      </c>
+      <c r="T688" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ivin.pt/</t>
+        </is>
+      </c>
+      <c r="U688" s="2" t="inlineStr"/>
+      <c r="V688" s="2" t="inlineStr"/>
+      <c r="W688" s="2" t="inlineStr">
+        <is>
+          <t>Miguel Grijó</t>
+        </is>
+      </c>
+      <c r="X688" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Ceo</t>
+        </is>
+      </c>
+      <c r="Y688" s="2" t="inlineStr"/>
+      <c r="Z688" s="2" t="inlineStr"/>
+      <c r="AA688" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/miguel-grij%c3%b3-60363aa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2" t="inlineStr">
+        <is>
+          <t>Ivin Lda.</t>
+        </is>
+      </c>
+      <c r="B689" s="2" t="inlineStr">
+        <is>
+          <t>Ivin Lda.</t>
+        </is>
+      </c>
+      <c r="C689" s="2" t="inlineStr">
+        <is>
+          <t>42118</t>
+        </is>
+      </c>
+      <c r="D689" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E689" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa</t>
+        </is>
+      </c>
+      <c r="F689" s="2" t="inlineStr">
+        <is>
+          <t>Lisboa, Santa Clara</t>
+        </is>
+      </c>
+      <c r="G689" s="2" t="inlineStr">
+        <is>
+          <t>1 Rua Jorge De Sena</t>
+        </is>
+      </c>
+      <c r="H689" s="2" t="inlineStr">
+        <is>
+          <t>1750-129</t>
+        </is>
+      </c>
+      <c r="I689" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ivin.pt</t>
+        </is>
+      </c>
+      <c r="J689" s="2" t="inlineStr"/>
+      <c r="K689" s="2" t="inlineStr"/>
+      <c r="L689" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M689" s="2" t="inlineStr"/>
+      <c r="N689" s="2" t="inlineStr">
+        <is>
+          <t>geral@ivin.pt</t>
+        </is>
+      </c>
+      <c r="O689" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 408 3488</t>
+        </is>
+      </c>
+      <c r="P689" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q689" s="2" t="inlineStr">
+        <is>
+          <t>509077072</t>
+        </is>
+      </c>
+      <c r="R689" s="2" t="inlineStr"/>
+      <c r="S689" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/www.ivin.pt</t>
+        </is>
+      </c>
+      <c r="T689" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ivin.pt/</t>
+        </is>
+      </c>
+      <c r="U689" s="2" t="inlineStr"/>
+      <c r="V689" s="2" t="inlineStr"/>
+      <c r="W689" s="2" t="inlineStr">
+        <is>
+          <t>Stephane Perrin</t>
+        </is>
+      </c>
+      <c r="X689" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y689" s="2" t="inlineStr"/>
+      <c r="Z689" s="2" t="inlineStr"/>
+      <c r="AA689" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stephane-perrin-3154a650/</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Farinha, Lda</t>
+        </is>
+      </c>
+      <c r="B690" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Farinha, Lda</t>
+        </is>
+      </c>
+      <c r="C690" s="2" t="inlineStr">
+        <is>
+          <t>26113</t>
+        </is>
+      </c>
+      <c r="D690" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E690" s="2" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="F690" s="2" t="inlineStr">
+        <is>
+          <t>Setúbal</t>
+        </is>
+      </c>
+      <c r="G690" s="2" t="inlineStr">
+        <is>
+          <t>3 Rua Vieira da Silva</t>
+        </is>
+      </c>
+      <c r="H690" s="2" t="inlineStr">
+        <is>
+          <t>2910-741</t>
+        </is>
+      </c>
+      <c r="I690" s="2" t="inlineStr">
+        <is>
+          <t>https://garrafeirafarinha.com</t>
+        </is>
+      </c>
+      <c r="J690" s="2" t="inlineStr"/>
+      <c r="K690" s="2" t="inlineStr"/>
+      <c r="L690" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M690" s="2" t="inlineStr"/>
+      <c r="N690" s="2" t="inlineStr">
+        <is>
+          <t>garrafeirafarinha@sapo.pt</t>
+        </is>
+      </c>
+      <c r="O690" s="2" t="inlineStr">
+        <is>
+          <t>+351 265 741 152</t>
+        </is>
+      </c>
+      <c r="P690" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q690" s="2" t="inlineStr">
+        <is>
+          <t>513788689</t>
+        </is>
+      </c>
+      <c r="R690" s="2" t="inlineStr"/>
+      <c r="S690" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GarrafeiraFarinhaLda</t>
+        </is>
+      </c>
+      <c r="T690" s="2" t="inlineStr"/>
+      <c r="U690" s="2" t="inlineStr"/>
+      <c r="V690" s="2" t="inlineStr"/>
+      <c r="W690" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Farinha</t>
+        </is>
+      </c>
+      <c r="X690" s="2" t="inlineStr">
+        <is>
+          <t>Manager/ Responsible</t>
+        </is>
+      </c>
+      <c r="Y690" s="2" t="inlineStr"/>
+      <c r="Z690" s="2" t="inlineStr"/>
+      <c r="AA690" s="2" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Grande Escolha</t>
+        </is>
+      </c>
+      <c r="B691" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Grande Escolha</t>
+        </is>
+      </c>
+      <c r="C691" s="2" t="inlineStr">
+        <is>
+          <t>97203</t>
+        </is>
+      </c>
+      <c r="D691" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E691" s="2" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F691" s="2" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G691" s="2" t="inlineStr">
+        <is>
+          <t>54 Avenida de São Lourenço</t>
+        </is>
+      </c>
+      <c r="H691" s="2" t="inlineStr">
+        <is>
+          <t>4705-442</t>
+        </is>
+      </c>
+      <c r="I691" s="2" t="inlineStr">
+        <is>
+          <t>https://garrafeiragrandeescolha.pt</t>
+        </is>
+      </c>
+      <c r="J691" s="2" t="inlineStr"/>
+      <c r="K691" s="2" t="inlineStr"/>
+      <c r="L691" s="2" t="inlineStr"/>
+      <c r="M691" s="2" t="inlineStr"/>
+      <c r="N691" s="2" t="inlineStr">
+        <is>
+          <t>garrafeiragescolha@gmail.com</t>
+        </is>
+      </c>
+      <c r="O691" s="2" t="inlineStr"/>
+      <c r="P691" s="2" t="inlineStr"/>
+      <c r="Q691" s="2" t="inlineStr"/>
+      <c r="R691" s="2" t="inlineStr"/>
+      <c r="S691" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/garrafeiragrandeescolha/</t>
+        </is>
+      </c>
+      <c r="T691" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeiragrandeescolha/</t>
+        </is>
+      </c>
+      <c r="U691" s="2" t="inlineStr"/>
+      <c r="V691" s="2" t="inlineStr"/>
+      <c r="W691" s="2" t="inlineStr"/>
+      <c r="X691" s="2" t="inlineStr"/>
+      <c r="Y691" s="2" t="inlineStr"/>
+      <c r="Z691" s="2" t="inlineStr"/>
+      <c r="AA691" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
